--- a/estattis_automação.xlsx
+++ b/estattis_automação.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="24000" windowHeight="9510" tabRatio="874" firstSheet="1" activeTab="8" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="24000" windowHeight="9510" tabRatio="874" firstSheet="5" activeTab="8" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CAPA DO LAUDO" sheetId="1" state="visible" r:id="rId1"/>
@@ -458,14 +458,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFFFFFFF"/>
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00B050"/>
-        <bgColor rgb="FF00B050"/>
+        <fgColor rgb="0000B050"/>
+        <bgColor rgb="0000B050"/>
       </patternFill>
     </fill>
   </fills>
@@ -1715,9 +1715,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="38" fillId="3" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="35" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1747,12 +1744,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="37" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="168" fontId="38" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="37" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1765,12 +1762,12 @@
     <xf numFmtId="0" fontId="37" fillId="3" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="37" fillId="3" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="2" fontId="37" fillId="3" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="3" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="168" fontId="38" fillId="3" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -1783,11 +1780,14 @@
     <xf numFmtId="0" fontId="38" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="2" fontId="37" fillId="3" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="168" fontId="38" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="37" fillId="3" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="38" fillId="3" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="37" fillId="3" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -2043,10 +2043,10 @@
     <xf numFmtId="0" fontId="16" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -2295,7 +2295,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="38" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="57" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -2481,6 +2481,39 @@
     </comment>
   </commentList>
 </comments>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>10</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5572125" cy="3810000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2778,7 +2811,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="12.75"/>
   <sheetData>
     <row r="3">
-      <c r="B3" s="243" t="inlineStr">
+      <c r="B3" s="242" t="inlineStr">
         <is>
           <t>LAUDO DE AVALIAÇÃO Nº 435420</t>
         </is>
@@ -2796,18 +2829,18 @@
       <c r="M3" s="239" t="n"/>
     </row>
     <row r="4">
-      <c r="B4" s="255" t="n"/>
-      <c r="C4" s="252" t="n"/>
-      <c r="D4" s="252" t="n"/>
-      <c r="E4" s="252" t="n"/>
-      <c r="F4" s="252" t="n"/>
-      <c r="G4" s="252" t="n"/>
-      <c r="H4" s="252" t="n"/>
-      <c r="I4" s="252" t="n"/>
-      <c r="J4" s="252" t="n"/>
-      <c r="K4" s="252" t="n"/>
-      <c r="L4" s="252" t="n"/>
-      <c r="M4" s="254" t="n"/>
+      <c r="B4" s="254" t="n"/>
+      <c r="C4" s="251" t="n"/>
+      <c r="D4" s="251" t="n"/>
+      <c r="E4" s="251" t="n"/>
+      <c r="F4" s="251" t="n"/>
+      <c r="G4" s="251" t="n"/>
+      <c r="H4" s="251" t="n"/>
+      <c r="I4" s="251" t="n"/>
+      <c r="J4" s="251" t="n"/>
+      <c r="K4" s="251" t="n"/>
+      <c r="L4" s="251" t="n"/>
+      <c r="M4" s="253" t="n"/>
     </row>
     <row r="5" ht="19.5" customHeight="1" s="236">
       <c r="B5" s="92" t="n"/>
@@ -2948,7 +2981,7 @@
       <c r="M16" s="92" t="n"/>
     </row>
     <row r="17" ht="20.25" customHeight="1" s="236">
-      <c r="B17" s="247" t="inlineStr">
+      <c r="B17" s="246" t="inlineStr">
         <is>
           <t>QUADRO RESUMO DA AVALIAÇÃO</t>
         </is>
@@ -2969,7 +3002,7 @@
       <c r="M18" s="82" t="n"/>
     </row>
     <row r="19" ht="17.25" customHeight="1" s="236">
-      <c r="B19" s="249" t="inlineStr">
+      <c r="B19" s="248" t="inlineStr">
         <is>
           <t>Proponente:</t>
         </is>
@@ -3005,76 +3038,76 @@
       <c r="M21" s="241" t="n"/>
     </row>
     <row r="22" ht="17.25" customHeight="1" s="236">
-      <c r="B22" s="266" t="inlineStr">
+      <c r="B22" s="265" t="inlineStr">
         <is>
           <t>Município:</t>
         </is>
       </c>
-      <c r="C22" s="252" t="n"/>
-      <c r="D22" s="252" t="n"/>
-      <c r="E22" s="258" t="n"/>
-      <c r="F22" s="252" t="n"/>
-      <c r="G22" s="252" t="n"/>
-      <c r="H22" s="252" t="n"/>
-      <c r="I22" s="252" t="n"/>
-      <c r="J22" s="252" t="n"/>
+      <c r="C22" s="251" t="n"/>
+      <c r="D22" s="251" t="n"/>
+      <c r="E22" s="257" t="n"/>
+      <c r="F22" s="251" t="n"/>
+      <c r="G22" s="251" t="n"/>
+      <c r="H22" s="251" t="n"/>
+      <c r="I22" s="251" t="n"/>
+      <c r="J22" s="251" t="n"/>
       <c r="K22" s="162" t="n"/>
-      <c r="L22" s="261" t="n"/>
-      <c r="M22" s="254" t="n"/>
+      <c r="L22" s="260" t="n"/>
+      <c r="M22" s="253" t="n"/>
     </row>
     <row r="23" ht="20.25" customHeight="1" s="236">
-      <c r="B23" s="243" t="inlineStr">
+      <c r="B23" s="242" t="inlineStr">
         <is>
           <t>IMÓVEL</t>
         </is>
       </c>
-      <c r="C23" s="244" t="n"/>
-      <c r="D23" s="244" t="n"/>
-      <c r="E23" s="244" t="n"/>
-      <c r="F23" s="244" t="n"/>
-      <c r="G23" s="244" t="n"/>
-      <c r="H23" s="244" t="n"/>
-      <c r="I23" s="244" t="n"/>
-      <c r="J23" s="244" t="n"/>
-      <c r="K23" s="244" t="n"/>
-      <c r="L23" s="244" t="n"/>
-      <c r="M23" s="245" t="n"/>
+      <c r="C23" s="243" t="n"/>
+      <c r="D23" s="243" t="n"/>
+      <c r="E23" s="243" t="n"/>
+      <c r="F23" s="243" t="n"/>
+      <c r="G23" s="243" t="n"/>
+      <c r="H23" s="243" t="n"/>
+      <c r="I23" s="243" t="n"/>
+      <c r="J23" s="243" t="n"/>
+      <c r="K23" s="243" t="n"/>
+      <c r="L23" s="243" t="n"/>
+      <c r="M23" s="244" t="n"/>
     </row>
     <row r="24" ht="15" customHeight="1" s="236">
-      <c r="B24" s="250" t="inlineStr">
+      <c r="B24" s="249" t="inlineStr">
         <is>
           <t>Nº Matrícula</t>
         </is>
       </c>
-      <c r="C24" s="244" t="n"/>
-      <c r="D24" s="245" t="n"/>
-      <c r="E24" s="250" t="inlineStr">
+      <c r="C24" s="243" t="n"/>
+      <c r="D24" s="244" t="n"/>
+      <c r="E24" s="249" t="inlineStr">
         <is>
           <t>Identificação</t>
         </is>
       </c>
-      <c r="F24" s="244" t="n"/>
-      <c r="G24" s="245" t="n"/>
-      <c r="H24" s="250" t="inlineStr">
+      <c r="F24" s="243" t="n"/>
+      <c r="G24" s="244" t="n"/>
+      <c r="H24" s="249" t="inlineStr">
         <is>
           <t>Área Superficial há</t>
         </is>
       </c>
-      <c r="I24" s="244" t="n"/>
-      <c r="J24" s="245" t="n"/>
-      <c r="K24" s="250" t="inlineStr">
+      <c r="I24" s="243" t="n"/>
+      <c r="J24" s="244" t="n"/>
+      <c r="K24" s="249" t="inlineStr">
         <is>
           <t>Área Construída m²</t>
         </is>
       </c>
-      <c r="L24" s="244" t="n"/>
-      <c r="M24" s="245" t="n"/>
+      <c r="L24" s="243" t="n"/>
+      <c r="M24" s="244" t="n"/>
     </row>
     <row r="25" ht="17.25" customHeight="1" s="236">
-      <c r="B25" s="263" t="n"/>
+      <c r="B25" s="261" t="n"/>
       <c r="C25" s="238" t="n"/>
       <c r="D25" s="239" t="n"/>
-      <c r="E25" s="257" t="n"/>
+      <c r="E25" s="255" t="n"/>
       <c r="H25" s="270" t="n"/>
       <c r="I25" s="238" t="n"/>
       <c r="J25" s="239" t="n"/>
@@ -3083,36 +3116,36 @@
       <c r="M25" s="239" t="n"/>
     </row>
     <row r="26" ht="17.25" customHeight="1" s="236">
-      <c r="B26" s="259" t="n"/>
-      <c r="C26" s="252" t="n"/>
-      <c r="D26" s="254" t="n"/>
-      <c r="E26" s="251" t="n"/>
-      <c r="F26" s="252" t="n"/>
-      <c r="G26" s="252" t="n"/>
-      <c r="H26" s="260" t="n"/>
-      <c r="I26" s="252" t="n"/>
-      <c r="J26" s="254" t="n"/>
-      <c r="K26" s="269" t="n"/>
-      <c r="L26" s="252" t="n"/>
-      <c r="M26" s="254" t="n"/>
+      <c r="B26" s="258" t="n"/>
+      <c r="C26" s="251" t="n"/>
+      <c r="D26" s="253" t="n"/>
+      <c r="E26" s="250" t="n"/>
+      <c r="F26" s="251" t="n"/>
+      <c r="G26" s="251" t="n"/>
+      <c r="H26" s="259" t="n"/>
+      <c r="I26" s="251" t="n"/>
+      <c r="J26" s="253" t="n"/>
+      <c r="K26" s="267" t="n"/>
+      <c r="L26" s="251" t="n"/>
+      <c r="M26" s="253" t="n"/>
     </row>
     <row r="27" ht="20.25" customHeight="1" s="236">
-      <c r="B27" s="243" t="inlineStr">
+      <c r="B27" s="242" t="inlineStr">
         <is>
           <t>CROQUI</t>
         </is>
       </c>
-      <c r="C27" s="244" t="n"/>
-      <c r="D27" s="244" t="n"/>
-      <c r="E27" s="244" t="n"/>
-      <c r="F27" s="244" t="n"/>
-      <c r="G27" s="244" t="n"/>
-      <c r="H27" s="244" t="n"/>
-      <c r="I27" s="244" t="n"/>
-      <c r="J27" s="244" t="n"/>
-      <c r="K27" s="244" t="n"/>
-      <c r="L27" s="244" t="n"/>
-      <c r="M27" s="245" t="n"/>
+      <c r="C27" s="243" t="n"/>
+      <c r="D27" s="243" t="n"/>
+      <c r="E27" s="243" t="n"/>
+      <c r="F27" s="243" t="n"/>
+      <c r="G27" s="243" t="n"/>
+      <c r="H27" s="243" t="n"/>
+      <c r="I27" s="243" t="n"/>
+      <c r="J27" s="243" t="n"/>
+      <c r="K27" s="243" t="n"/>
+      <c r="L27" s="243" t="n"/>
+      <c r="M27" s="244" t="n"/>
     </row>
     <row r="28" ht="17.25" customHeight="1" s="236">
       <c r="B28" s="83" t="n"/>
@@ -3199,104 +3232,104 @@
       <c r="M33" s="91" t="n"/>
     </row>
     <row r="34" ht="20.25" customHeight="1" s="236">
-      <c r="B34" s="243" t="inlineStr">
+      <c r="B34" s="242" t="inlineStr">
         <is>
           <t>VALORES</t>
         </is>
       </c>
-      <c r="C34" s="244" t="n"/>
-      <c r="D34" s="244" t="n"/>
-      <c r="E34" s="244" t="n"/>
-      <c r="F34" s="244" t="n"/>
-      <c r="G34" s="244" t="n"/>
-      <c r="H34" s="244" t="n"/>
-      <c r="I34" s="244" t="n"/>
-      <c r="J34" s="244" t="n"/>
-      <c r="K34" s="244" t="n"/>
-      <c r="L34" s="244" t="n"/>
-      <c r="M34" s="245" t="n"/>
+      <c r="C34" s="243" t="n"/>
+      <c r="D34" s="243" t="n"/>
+      <c r="E34" s="243" t="n"/>
+      <c r="F34" s="243" t="n"/>
+      <c r="G34" s="243" t="n"/>
+      <c r="H34" s="243" t="n"/>
+      <c r="I34" s="243" t="n"/>
+      <c r="J34" s="243" t="n"/>
+      <c r="K34" s="243" t="n"/>
+      <c r="L34" s="243" t="n"/>
+      <c r="M34" s="244" t="n"/>
     </row>
     <row r="35" ht="15" customHeight="1" s="236">
-      <c r="B35" s="250" t="inlineStr">
+      <c r="B35" s="249" t="inlineStr">
         <is>
           <t>MATRÍCULA</t>
         </is>
       </c>
-      <c r="C35" s="244" t="n"/>
-      <c r="D35" s="244" t="n"/>
-      <c r="E35" s="245" t="n"/>
-      <c r="F35" s="250" t="inlineStr">
+      <c r="C35" s="243" t="n"/>
+      <c r="D35" s="243" t="n"/>
+      <c r="E35" s="244" t="n"/>
+      <c r="F35" s="249" t="inlineStr">
         <is>
           <t>MERCADO R$</t>
         </is>
       </c>
-      <c r="G35" s="244" t="n"/>
-      <c r="H35" s="244" t="n"/>
-      <c r="I35" s="245" t="n"/>
-      <c r="J35" s="250" t="inlineStr">
+      <c r="G35" s="243" t="n"/>
+      <c r="H35" s="243" t="n"/>
+      <c r="I35" s="244" t="n"/>
+      <c r="J35" s="249" t="inlineStr">
         <is>
           <t>LIQUIDAÇÃO FORÇADA R$</t>
         </is>
       </c>
-      <c r="K35" s="244" t="n"/>
-      <c r="L35" s="244" t="n"/>
-      <c r="M35" s="245" t="n"/>
+      <c r="K35" s="243" t="n"/>
+      <c r="L35" s="243" t="n"/>
+      <c r="M35" s="244" t="n"/>
     </row>
     <row r="36" ht="15" customHeight="1" s="236">
-      <c r="B36" s="248" t="n"/>
+      <c r="B36" s="247" t="n"/>
       <c r="C36" s="238" t="n"/>
       <c r="D36" s="238" t="n"/>
       <c r="E36" s="238" t="n"/>
-      <c r="F36" s="264" t="n"/>
+      <c r="F36" s="263" t="n"/>
       <c r="G36" s="238" t="n"/>
       <c r="H36" s="238" t="n"/>
       <c r="I36" s="238" t="n"/>
-      <c r="J36" s="265" t="n"/>
+      <c r="J36" s="264" t="n"/>
       <c r="K36" s="238" t="n"/>
       <c r="L36" s="238" t="n"/>
       <c r="M36" s="239" t="n"/>
     </row>
     <row r="37" ht="15" customHeight="1" s="236">
-      <c r="B37" s="242" t="n"/>
-      <c r="F37" s="246" t="n"/>
+      <c r="B37" s="269" t="n"/>
+      <c r="F37" s="245" t="n"/>
       <c r="J37" s="256" t="n"/>
       <c r="M37" s="241" t="n"/>
     </row>
     <row r="38" ht="15" customHeight="1" s="236">
-      <c r="B38" s="267" t="inlineStr">
+      <c r="B38" s="266" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C38" s="252" t="n"/>
-      <c r="D38" s="252" t="n"/>
-      <c r="E38" s="252" t="n"/>
+      <c r="C38" s="251" t="n"/>
+      <c r="D38" s="251" t="n"/>
+      <c r="E38" s="251" t="n"/>
       <c r="F38" s="268" t="n"/>
-      <c r="G38" s="252" t="n"/>
-      <c r="H38" s="252" t="n"/>
-      <c r="I38" s="252" t="n"/>
-      <c r="J38" s="253" t="n"/>
-      <c r="K38" s="252" t="n"/>
-      <c r="L38" s="252" t="n"/>
-      <c r="M38" s="254" t="n"/>
+      <c r="G38" s="251" t="n"/>
+      <c r="H38" s="251" t="n"/>
+      <c r="I38" s="251" t="n"/>
+      <c r="J38" s="252" t="n"/>
+      <c r="K38" s="251" t="n"/>
+      <c r="L38" s="251" t="n"/>
+      <c r="M38" s="253" t="n"/>
     </row>
     <row r="39" ht="20.25" customHeight="1" s="236">
-      <c r="B39" s="243" t="inlineStr">
+      <c r="B39" s="242" t="inlineStr">
         <is>
           <t>OBSERVAÇÕES</t>
         </is>
       </c>
-      <c r="C39" s="244" t="n"/>
-      <c r="D39" s="244" t="n"/>
-      <c r="E39" s="244" t="n"/>
-      <c r="F39" s="244" t="n"/>
-      <c r="G39" s="244" t="n"/>
-      <c r="H39" s="244" t="n"/>
-      <c r="I39" s="244" t="n"/>
-      <c r="J39" s="244" t="n"/>
-      <c r="K39" s="244" t="n"/>
-      <c r="L39" s="244" t="n"/>
-      <c r="M39" s="245" t="n"/>
+      <c r="C39" s="243" t="n"/>
+      <c r="D39" s="243" t="n"/>
+      <c r="E39" s="243" t="n"/>
+      <c r="F39" s="243" t="n"/>
+      <c r="G39" s="243" t="n"/>
+      <c r="H39" s="243" t="n"/>
+      <c r="I39" s="243" t="n"/>
+      <c r="J39" s="243" t="n"/>
+      <c r="K39" s="243" t="n"/>
+      <c r="L39" s="243" t="n"/>
+      <c r="M39" s="244" t="n"/>
     </row>
     <row r="40" ht="19.5" customHeight="1" s="236">
       <c r="B40" s="92" t="n"/>
@@ -3415,6 +3448,7 @@
     <mergeCell ref="B11:D11"/>
     <mergeCell ref="E19:M19"/>
     <mergeCell ref="E10:M10"/>
+    <mergeCell ref="B37:E37"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="B23:M23"/>
     <mergeCell ref="F37:I37"/>
@@ -3429,22 +3463,23 @@
     <mergeCell ref="B9:D9"/>
     <mergeCell ref="E26:G26"/>
     <mergeCell ref="J38:M38"/>
-    <mergeCell ref="B24:D24"/>
     <mergeCell ref="B3:M4"/>
+    <mergeCell ref="E25:G25"/>
     <mergeCell ref="B20:D20"/>
     <mergeCell ref="J37:M37"/>
-    <mergeCell ref="E25:G25"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="E20:M20"/>
     <mergeCell ref="E7:M7"/>
     <mergeCell ref="H24:J24"/>
     <mergeCell ref="E22:J22"/>
     <mergeCell ref="B26:D26"/>
+    <mergeCell ref="E21:M21"/>
+    <mergeCell ref="B7:D7"/>
     <mergeCell ref="H26:J26"/>
-    <mergeCell ref="E21:M21"/>
+    <mergeCell ref="E12:M12"/>
+    <mergeCell ref="L22:M22"/>
     <mergeCell ref="B25:D25"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="E12:M12"/>
     <mergeCell ref="K25:M25"/>
-    <mergeCell ref="L22:M22"/>
     <mergeCell ref="F36:I36"/>
     <mergeCell ref="E24:G24"/>
     <mergeCell ref="K24:M24"/>
@@ -3453,16 +3488,14 @@
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="J35:M35"/>
     <mergeCell ref="B38:E38"/>
-    <mergeCell ref="K26:M26"/>
-    <mergeCell ref="B39:M39"/>
     <mergeCell ref="F38:I38"/>
     <mergeCell ref="B21:D21"/>
+    <mergeCell ref="B27:M27"/>
+    <mergeCell ref="K26:M26"/>
+    <mergeCell ref="B12:D12"/>
     <mergeCell ref="E8:M8"/>
-    <mergeCell ref="B37:E37"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="B27:M27"/>
     <mergeCell ref="H25:J25"/>
-    <mergeCell ref="E20:M20"/>
+    <mergeCell ref="B39:M39"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.787401575" bottom="0.787401575" header="0.31496062" footer="0.31496062"/>
 </worksheet>
@@ -3485,8 +3518,8 @@
     <col width="15.7109375" customWidth="1" style="400" min="6" max="6"/>
     <col width="10.140625" customWidth="1" style="400" min="7" max="7"/>
     <col width="14.28515625" customWidth="1" style="400" min="8" max="8"/>
-    <col width="9.140625" customWidth="1" style="400" min="9" max="13"/>
-    <col width="9.140625" customWidth="1" style="400" min="14" max="16384"/>
+    <col width="9.140625" customWidth="1" style="400" min="9" max="36"/>
+    <col width="9.140625" customWidth="1" style="400" min="37" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="17.1" customHeight="1" s="236">
@@ -3579,8 +3612,8 @@
       <c r="B7" s="393" t="n"/>
       <c r="C7" s="391" t="n"/>
       <c r="D7" s="391" t="n"/>
-      <c r="E7" s="254" t="n"/>
-      <c r="F7" s="254" t="n"/>
+      <c r="E7" s="253" t="n"/>
+      <c r="F7" s="253" t="n"/>
       <c r="G7" s="164" t="inlineStr">
         <is>
           <t>UNITÁRIO</t>
@@ -3610,11 +3643,11 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C9" s="244" t="n"/>
-      <c r="D9" s="244" t="n"/>
-      <c r="E9" s="244" t="n"/>
-      <c r="F9" s="244" t="n"/>
-      <c r="G9" s="245" t="n"/>
+      <c r="C9" s="243" t="n"/>
+      <c r="D9" s="243" t="n"/>
+      <c r="E9" s="243" t="n"/>
+      <c r="F9" s="243" t="n"/>
+      <c r="G9" s="244" t="n"/>
       <c r="H9" s="438">
         <f>TRUNC(SUM(H8:H8),2)</f>
         <v/>
@@ -3670,8 +3703,8 @@
       <c r="B12" s="393" t="n"/>
       <c r="C12" s="391" t="n"/>
       <c r="D12" s="391" t="n"/>
-      <c r="E12" s="254" t="n"/>
-      <c r="F12" s="254" t="n"/>
+      <c r="E12" s="253" t="n"/>
+      <c r="F12" s="253" t="n"/>
       <c r="G12" s="164" t="inlineStr">
         <is>
           <t>UNITÁRIO</t>
@@ -3701,11 +3734,11 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C14" s="244" t="n"/>
-      <c r="D14" s="244" t="n"/>
-      <c r="E14" s="244" t="n"/>
-      <c r="F14" s="244" t="n"/>
-      <c r="G14" s="245" t="n"/>
+      <c r="C14" s="243" t="n"/>
+      <c r="D14" s="243" t="n"/>
+      <c r="E14" s="243" t="n"/>
+      <c r="F14" s="243" t="n"/>
+      <c r="G14" s="244" t="n"/>
       <c r="H14" s="440">
         <f>TRUNC(SUM(H13:H13),2)</f>
         <v/>
@@ -3761,8 +3794,8 @@
       <c r="B17" s="393" t="n"/>
       <c r="C17" s="391" t="n"/>
       <c r="D17" s="391" t="n"/>
-      <c r="E17" s="254" t="n"/>
-      <c r="F17" s="254" t="n"/>
+      <c r="E17" s="253" t="n"/>
+      <c r="F17" s="253" t="n"/>
       <c r="G17" s="394" t="inlineStr">
         <is>
           <t>UNITÁRIO</t>
@@ -3796,11 +3829,11 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C19" s="244" t="n"/>
-      <c r="D19" s="244" t="n"/>
-      <c r="E19" s="244" t="n"/>
-      <c r="F19" s="244" t="n"/>
-      <c r="G19" s="245" t="n"/>
+      <c r="C19" s="243" t="n"/>
+      <c r="D19" s="243" t="n"/>
+      <c r="E19" s="243" t="n"/>
+      <c r="F19" s="243" t="n"/>
+      <c r="G19" s="244" t="n"/>
       <c r="H19" s="442">
         <f>TRUNC(SUM(H18:H18),2)</f>
         <v/>
@@ -3856,8 +3889,8 @@
       <c r="B22" s="393" t="n"/>
       <c r="C22" s="391" t="n"/>
       <c r="D22" s="391" t="n"/>
-      <c r="E22" s="254" t="n"/>
-      <c r="F22" s="254" t="n"/>
+      <c r="E22" s="253" t="n"/>
+      <c r="F22" s="253" t="n"/>
       <c r="G22" s="164" t="inlineStr">
         <is>
           <t>UNITÁRIO</t>
@@ -3950,8 +3983,8 @@
     <col width="8.85546875" customWidth="1" style="24" min="5" max="5"/>
     <col width="10.140625" customWidth="1" style="24" min="6" max="6"/>
     <col width="12.7109375" customWidth="1" style="24" min="7" max="7"/>
-    <col width="9.140625" customWidth="1" style="24" min="8" max="12"/>
-    <col width="9.140625" customWidth="1" style="24" min="13" max="16384"/>
+    <col width="9.140625" customWidth="1" style="24" min="8" max="35"/>
+    <col width="9.140625" customWidth="1" style="24" min="36" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="17.1" customFormat="1" customHeight="1" s="400">
@@ -3988,11 +4021,11 @@
           <t>13 - BENFEITORIAS NÃO REPRODUTIVAS</t>
         </is>
       </c>
-      <c r="C4" s="244" t="n"/>
-      <c r="D4" s="244" t="n"/>
-      <c r="E4" s="244" t="n"/>
-      <c r="F4" s="244" t="n"/>
-      <c r="G4" s="245" t="n"/>
+      <c r="C4" s="243" t="n"/>
+      <c r="D4" s="243" t="n"/>
+      <c r="E4" s="243" t="n"/>
+      <c r="F4" s="243" t="n"/>
+      <c r="G4" s="244" t="n"/>
       <c r="H4" s="23" t="n"/>
     </row>
     <row r="5">
@@ -4021,11 +4054,11 @@
           <t>VALOR EM R$ REAIS</t>
         </is>
       </c>
-      <c r="G5" s="244" t="n"/>
+      <c r="G5" s="243" t="n"/>
       <c r="I5" s="25" t="n"/>
     </row>
     <row r="6">
-      <c r="B6" s="254" t="n"/>
+      <c r="B6" s="253" t="n"/>
       <c r="C6" s="391" t="n"/>
       <c r="D6" s="391" t="n"/>
       <c r="E6" s="391" t="n"/>
@@ -4082,11 +4115,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S20"/>
+  <dimension ref="A1:S39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="9.140625" customWidth="1" style="236" min="1" max="1"/>
-    <col width="9.140625" customWidth="1" style="236" min="72" max="72"/>
+    <col width="8.43" customWidth="1" style="236" min="1" max="1"/>
+    <col width="8.43" customWidth="1" style="236" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1" s="236">
@@ -4097,7 +4130,7 @@
       </c>
       <c r="O1" s="450" t="n"/>
     </row>
-    <row r="2" ht="17.25" customHeight="1" s="236">
+    <row r="2" ht="15" customHeight="1" s="236">
       <c r="A2" s="451" t="inlineStr">
         <is>
           <t>Proponente:</t>
@@ -4110,12 +4143,12 @@
       </c>
       <c r="J2" s="452" t="inlineStr">
         <is>
-          <t>#486: 32.251.489/5614-55</t>
+          <t>CPF: 713.254.791-79</t>
         </is>
       </c>
       <c r="O2" s="450" t="n"/>
     </row>
-    <row r="3" ht="15.75" customHeight="1" s="236">
+    <row r="3" ht="15" customHeight="1" s="236">
       <c r="A3" s="453" t="inlineStr">
         <is>
           <t>Proprietário:</t>
@@ -4132,7 +4165,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="15.75" customHeight="1" s="236">
+    <row r="4" ht="15" customHeight="1" s="236">
       <c r="A4" s="453" t="inlineStr">
         <is>
           <t>Proprietário:</t>
@@ -4149,302 +4182,259 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="15.75" customHeight="1" s="236">
+    <row r="5" ht="15" customHeight="1" s="236">
       <c r="A5" s="453" t="inlineStr">
         <is>
-          <t>Proprietário:</t>
+          <t xml:space="preserve">Agencia: </t>
         </is>
       </c>
       <c r="C5" s="453" t="inlineStr">
         <is>
-          <t>testando</t>
-        </is>
-      </c>
-      <c r="J5" s="453" t="inlineStr">
-        <is>
-          <t>CNPJ:58744</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="15.75" customHeight="1" s="236">
+          <t>ua porto nacional (14)</t>
+        </is>
+      </c>
+      <c r="J5" s="454" t="n"/>
+    </row>
+    <row r="6" ht="15" customHeight="1" s="236">
       <c r="A6" s="453" t="inlineStr">
         <is>
-          <t xml:space="preserve">Agencia: </t>
+          <t>Identificação:</t>
         </is>
       </c>
       <c r="C6" s="453" t="inlineStr">
         <is>
-          <t>ua porto nacional (14)</t>
+          <t>fazenda rancho diamante</t>
         </is>
       </c>
       <c r="J6" s="454" t="n"/>
     </row>
-    <row r="7" ht="15.75" customHeight="1" s="236">
+    <row r="7" ht="15" customHeight="1" s="236">
       <c r="A7" s="453" t="inlineStr">
         <is>
-          <t>Identificação:</t>
+          <t>Município:</t>
         </is>
       </c>
       <c r="C7" s="453" t="inlineStr">
         <is>
-          <t>fazenda rancho diamante</t>
-        </is>
-      </c>
-      <c r="J7" s="454" t="n"/>
-    </row>
-    <row r="8" ht="15.75" customHeight="1" s="236">
-      <c r="A8" s="453" t="inlineStr">
-        <is>
-          <t>Município:</t>
-        </is>
-      </c>
-      <c r="C8" s="453" t="inlineStr">
-        <is>
           <t>palmas</t>
         </is>
       </c>
-      <c r="J8" s="453" t="inlineStr">
+      <c r="J7" s="453" t="inlineStr">
         <is>
           <t>UF:  TO</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="455" t="inlineStr">
+    <row r="8" ht="15" customHeight="1" s="236">
+      <c r="A8" s="455" t="inlineStr">
         <is>
           <t>MAPA DA ÁREA</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" s="455" t="inlineStr">
+    <row r="9" ht="15" customHeight="1" s="236"/>
+    <row r="10" ht="15" customHeight="1" s="236"/>
+    <row r="11" ht="15" customHeight="1" s="236"/>
+    <row r="12" ht="15" customHeight="1" s="236"/>
+    <row r="13" ht="15" customHeight="1" s="236"/>
+    <row r="14" ht="15" customHeight="1" s="236"/>
+    <row r="15" ht="15" customHeight="1" s="236"/>
+    <row r="16" ht="15" customHeight="1" s="236"/>
+    <row r="17" ht="15" customHeight="1" s="236"/>
+    <row r="18" ht="15" customHeight="1" s="236"/>
+    <row r="19" ht="15" customHeight="1" s="236"/>
+    <row r="20" ht="15" customHeight="1" s="236"/>
+    <row r="21" ht="15" customHeight="1" s="236"/>
+    <row r="22" ht="15" customHeight="1" s="236"/>
+    <row r="23" ht="15" customHeight="1" s="236"/>
+    <row r="24" ht="15" customHeight="1" s="236"/>
+    <row r="25" ht="15" customHeight="1" s="236"/>
+    <row r="26" ht="15" customHeight="1" s="236"/>
+    <row r="27" ht="15" customHeight="1" s="236"/>
+    <row r="28" ht="15" customHeight="1" s="236"/>
+    <row r="29" ht="15" customHeight="1" s="236"/>
+    <row r="30" ht="15" customHeight="1" s="236"/>
+    <row r="31" ht="15" customHeight="1" s="236"/>
+    <row r="32" ht="15" customHeight="1" s="236">
+      <c r="A32" s="455" t="inlineStr">
         <is>
           <t>IMOVEL</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="456" t="inlineStr">
+    <row r="33" ht="15" customHeight="1" s="236">
+      <c r="A33" s="456" t="inlineStr">
         <is>
           <t>Nº Matrícula</t>
         </is>
       </c>
-      <c r="D12" s="456" t="inlineStr">
+      <c r="D33" s="456" t="inlineStr">
         <is>
           <t>Identificação</t>
         </is>
       </c>
-      <c r="G12" s="456" t="inlineStr">
+      <c r="G33" s="456" t="inlineStr">
         <is>
           <t>Área há</t>
         </is>
       </c>
-      <c r="J12" s="456" t="inlineStr">
+      <c r="J33" s="456" t="inlineStr">
         <is>
           <t>Área Construída m²</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="456" t="inlineStr">
+    <row r="34" ht="15" customHeight="1" s="236">
+      <c r="A34" s="456" t="inlineStr">
         <is>
           <t>1456.6547</t>
         </is>
       </c>
-      <c r="D13" s="456" t="inlineStr">
+      <c r="D34" s="456" t="inlineStr">
         <is>
           <t>fazenda</t>
         </is>
       </c>
-      <c r="G13" s="456" t="inlineStr">
+      <c r="G34" s="456" t="inlineStr">
         <is>
           <t>1234.5123</t>
         </is>
       </c>
-      <c r="J13" s="456" t="inlineStr">
+      <c r="J34" s="456" t="inlineStr">
         <is>
           <t>156.65</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="456" t="inlineStr">
+    <row r="35" ht="15" customHeight="1" s="236">
+      <c r="A35" s="456" t="inlineStr">
         <is>
           <t>184.096</t>
         </is>
       </c>
-      <c r="D14" s="456" t="inlineStr">
+      <c r="D35" s="456" t="inlineStr">
         <is>
           <t>fazenda</t>
         </is>
       </c>
-      <c r="G14" s="456" t="inlineStr">
+      <c r="G35" s="456" t="inlineStr">
         <is>
           <t>123.0921</t>
         </is>
       </c>
-      <c r="J14" s="456" t="inlineStr">
+      <c r="J35" s="456" t="inlineStr">
         <is>
           <t>15.65</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="456" t="inlineStr">
-        <is>
-          <t>saui</t>
-        </is>
-      </c>
-      <c r="D15" s="456" t="inlineStr">
-        <is>
-          <t>fazenda</t>
-        </is>
-      </c>
-      <c r="G15" s="456" t="inlineStr">
-        <is>
-          <t>marco</t>
-        </is>
-      </c>
-      <c r="J15" s="456" t="inlineStr">
-        <is>
-          <t>mara9-1</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="455" t="inlineStr">
+    <row r="36" ht="15" customHeight="1" s="236">
+      <c r="A36" s="455" t="inlineStr">
         <is>
           <t>VALORES</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="456" t="inlineStr">
+    <row r="37" ht="15" customHeight="1" s="236">
+      <c r="A37" s="456" t="inlineStr">
         <is>
           <t>Nº Matrícula</t>
         </is>
       </c>
-      <c r="F17" s="456" t="inlineStr">
+      <c r="F37" s="456" t="inlineStr">
         <is>
           <t>Valor de mercado</t>
         </is>
       </c>
-      <c r="K17" s="456" t="inlineStr">
+      <c r="K37" s="456" t="inlineStr">
         <is>
           <t>Liquidação forçada</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="456" t="inlineStr">
+    <row r="38" ht="15" customHeight="1" s="236">
+      <c r="A38" s="456" t="inlineStr">
         <is>
           <t>1456.6547</t>
         </is>
       </c>
-      <c r="F18" s="456" t="inlineStr">
+      <c r="F38" s="456" t="inlineStr">
         <is>
           <t>R$ 25.000.000,00</t>
         </is>
       </c>
-      <c r="K18" s="456" t="inlineStr">
+      <c r="K38" s="456" t="inlineStr">
         <is>
           <t>R$ 65.000.000,00</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="456" t="inlineStr">
+    <row r="39" ht="15" customHeight="1" s="236">
+      <c r="A39" s="456" t="inlineStr">
         <is>
           <t>184.096</t>
         </is>
       </c>
-      <c r="F19" s="456" t="inlineStr">
+      <c r="F39" s="456" t="inlineStr">
         <is>
           <t>R$ 100.000,00</t>
         </is>
       </c>
-      <c r="K19" s="456" t="inlineStr">
+      <c r="K39" s="456" t="inlineStr">
         <is>
           <t>R$ 1.000,00</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="456" t="inlineStr">
-        <is>
-          <t>saui</t>
-        </is>
-      </c>
-      <c r="F20" s="456" t="inlineStr">
-        <is>
-          <t>R$ 10.000,00</t>
-        </is>
-      </c>
-      <c r="K20" s="456" t="inlineStr">
-        <is>
-          <t>R$ 20.000,00</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="54">
-    <mergeCell ref="F20:H20"/>
-    <mergeCell ref="A9:N9"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="F18:H18"/>
-    <mergeCell ref="G13:I13"/>
+  <mergeCells count="44">
+    <mergeCell ref="A37:C37"/>
     <mergeCell ref="J5:N5"/>
-    <mergeCell ref="C8:I8"/>
-    <mergeCell ref="J12:M12"/>
-    <mergeCell ref="A18:C18"/>
     <mergeCell ref="C7:I7"/>
-    <mergeCell ref="A11:N11"/>
-    <mergeCell ref="F17:H17"/>
-    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="G34:I34"/>
+    <mergeCell ref="J2:M2"/>
+    <mergeCell ref="A36:N36"/>
     <mergeCell ref="A6:B6"/>
-    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J33:M33"/>
+    <mergeCell ref="G33:I33"/>
     <mergeCell ref="A1:N1"/>
-    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="F38:H38"/>
+    <mergeCell ref="A33:C33"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="C3:I3"/>
-    <mergeCell ref="A14:C14"/>
     <mergeCell ref="J6:N6"/>
-    <mergeCell ref="A16:N16"/>
     <mergeCell ref="O1:S1"/>
-    <mergeCell ref="D12:F12"/>
-    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="K39:M39"/>
     <mergeCell ref="C6:I6"/>
-    <mergeCell ref="K17:M17"/>
-    <mergeCell ref="J14:M14"/>
-    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="A35:C35"/>
     <mergeCell ref="A3:B3"/>
+    <mergeCell ref="D33:F33"/>
     <mergeCell ref="C5:I5"/>
-    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="F37:H37"/>
+    <mergeCell ref="A38:C38"/>
     <mergeCell ref="J4:N4"/>
+    <mergeCell ref="F39:H39"/>
+    <mergeCell ref="K38:M38"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="J2:L2"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="J13:M13"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="K19:M19"/>
     <mergeCell ref="J7:N7"/>
+    <mergeCell ref="K37:M37"/>
     <mergeCell ref="C4:I4"/>
     <mergeCell ref="A5:B5"/>
-    <mergeCell ref="K18:M18"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="J15:M15"/>
-    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="J34:M34"/>
+    <mergeCell ref="D35:F35"/>
+    <mergeCell ref="A39:C39"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="A32:N32"/>
+    <mergeCell ref="D34:F34"/>
     <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A8:N8"/>
     <mergeCell ref="J3:N3"/>
-    <mergeCell ref="F19:H19"/>
+    <mergeCell ref="J35:M35"/>
     <mergeCell ref="C2:I2"/>
-    <mergeCell ref="K20:M20"/>
-    <mergeCell ref="J8:N8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -4460,8 +4450,8 @@
     <col width="9.140625" customWidth="1" style="272" min="1" max="3"/>
     <col width="29.85546875" customWidth="1" style="272" min="4" max="4"/>
     <col width="16.5703125" customWidth="1" style="272" min="5" max="5"/>
-    <col width="9.140625" customWidth="1" style="272" min="6" max="10"/>
-    <col width="9.140625" customWidth="1" style="272" min="11" max="16384"/>
+    <col width="9.140625" customWidth="1" style="272" min="6" max="33"/>
+    <col width="9.140625" customWidth="1" style="272" min="34" max="16384"/>
   </cols>
   <sheetData>
     <row r="8" ht="13.5" customHeight="1" s="236" thickBot="1"/>
@@ -4801,8 +4791,8 @@
     <col width="8.28515625" bestFit="1" customWidth="1" style="272" min="7" max="7"/>
     <col width="9.140625" customWidth="1" style="272" min="8" max="9"/>
     <col width="14.42578125" customWidth="1" style="272" min="10" max="10"/>
-    <col width="9.140625" customWidth="1" style="272" min="11" max="15"/>
-    <col width="9.140625" customWidth="1" style="272" min="16" max="16384"/>
+    <col width="9.140625" customWidth="1" style="272" min="11" max="38"/>
+    <col width="9.140625" customWidth="1" style="272" min="39" max="16384"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -4864,25 +4854,25 @@
           <t>AREA TOTAL</t>
         </is>
       </c>
-      <c r="D5" s="254" t="n"/>
+      <c r="D5" s="253" t="n"/>
       <c r="E5" s="278" t="inlineStr">
         <is>
           <t>AREA DE RESERVA LEGAL</t>
         </is>
       </c>
-      <c r="F5" s="254" t="n"/>
+      <c r="F5" s="253" t="n"/>
       <c r="G5" s="278" t="inlineStr">
         <is>
           <t>AREA DE APP</t>
         </is>
       </c>
-      <c r="H5" s="254" t="n"/>
+      <c r="H5" s="253" t="n"/>
       <c r="I5" s="286" t="inlineStr">
         <is>
           <t>ÁREA CONSTRUÍDA</t>
         </is>
       </c>
-      <c r="J5" s="254" t="n"/>
+      <c r="J5" s="253" t="n"/>
       <c r="L5" s="142" t="n"/>
       <c r="M5" s="142" t="n"/>
       <c r="N5" s="142" t="inlineStr">
@@ -4902,25 +4892,25 @@
         <f>AMOSTRAS!E6</f>
         <v/>
       </c>
-      <c r="D6" s="245" t="n"/>
+      <c r="D6" s="244" t="n"/>
       <c r="E6" s="273" t="inlineStr">
         <is>
           <t xml:space="preserve"> -</t>
         </is>
       </c>
-      <c r="F6" s="245" t="n"/>
+      <c r="F6" s="244" t="n"/>
       <c r="G6" s="274" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H6" s="245" t="n"/>
+      <c r="H6" s="244" t="n"/>
       <c r="I6" s="275" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J6" s="245" t="n"/>
+      <c r="J6" s="244" t="n"/>
       <c r="L6" s="142" t="n">
         <v>231.63</v>
       </c>
@@ -4945,13 +4935,13 @@
           <t>CERTIFICADO DE CADASTRO DE IMÓVEL RURAL - CCIR</t>
         </is>
       </c>
-      <c r="D7" s="244" t="n"/>
-      <c r="E7" s="244" t="n"/>
-      <c r="F7" s="244" t="n"/>
-      <c r="G7" s="244" t="n"/>
-      <c r="H7" s="244" t="n"/>
-      <c r="I7" s="244" t="n"/>
-      <c r="J7" s="245" t="n"/>
+      <c r="D7" s="243" t="n"/>
+      <c r="E7" s="243" t="n"/>
+      <c r="F7" s="243" t="n"/>
+      <c r="G7" s="243" t="n"/>
+      <c r="H7" s="243" t="n"/>
+      <c r="I7" s="243" t="n"/>
+      <c r="J7" s="244" t="n"/>
       <c r="L7" s="142" t="n"/>
       <c r="M7" s="142" t="n"/>
       <c r="N7" s="142" t="n"/>
@@ -4975,25 +4965,25 @@
           <t>AREA TOTAL</t>
         </is>
       </c>
-      <c r="D8" s="245" t="n"/>
+      <c r="D8" s="244" t="n"/>
       <c r="E8" s="279" t="inlineStr">
         <is>
           <t>CLASSIFICAÇÃO FUNDIÁRIA</t>
         </is>
       </c>
-      <c r="F8" s="245" t="n"/>
+      <c r="F8" s="244" t="n"/>
       <c r="G8" s="279" t="inlineStr">
         <is>
           <t>MÓDULO RURAL</t>
         </is>
       </c>
-      <c r="H8" s="245" t="n"/>
+      <c r="H8" s="244" t="n"/>
       <c r="I8" s="280" t="inlineStr">
         <is>
           <t>Nº DE MÓDULOS RURAIS</t>
         </is>
       </c>
-      <c r="J8" s="245" t="n"/>
+      <c r="J8" s="244" t="n"/>
       <c r="L8" s="142" t="n"/>
       <c r="M8" s="142" t="n"/>
       <c r="N8" s="142" t="n"/>
@@ -5008,21 +4998,21 @@
       <c r="C9" s="273" t="n">
         <v>387.2</v>
       </c>
-      <c r="D9" s="245" t="n"/>
+      <c r="D9" s="244" t="n"/>
       <c r="E9" s="273" t="inlineStr">
         <is>
           <t>Média Propriedade Proditova</t>
         </is>
       </c>
-      <c r="F9" s="245" t="n"/>
+      <c r="F9" s="244" t="n"/>
       <c r="G9" s="273" t="n">
         <v>80</v>
       </c>
-      <c r="H9" s="245" t="n"/>
+      <c r="H9" s="244" t="n"/>
       <c r="I9" s="273" t="n">
         <v>4.84</v>
       </c>
-      <c r="J9" s="245" t="n"/>
+      <c r="J9" s="244" t="n"/>
       <c r="L9" s="142" t="n"/>
       <c r="M9" s="142" t="n"/>
       <c r="N9" s="142" t="n"/>
@@ -5039,13 +5029,13 @@
           <t>CADASTRO AMBIENTAL RURAL - CAR</t>
         </is>
       </c>
-      <c r="D10" s="244" t="n"/>
-      <c r="E10" s="244" t="n"/>
-      <c r="F10" s="244" t="n"/>
-      <c r="G10" s="244" t="n"/>
-      <c r="H10" s="244" t="n"/>
-      <c r="I10" s="244" t="n"/>
-      <c r="J10" s="245" t="n"/>
+      <c r="D10" s="243" t="n"/>
+      <c r="E10" s="243" t="n"/>
+      <c r="F10" s="243" t="n"/>
+      <c r="G10" s="243" t="n"/>
+      <c r="H10" s="243" t="n"/>
+      <c r="I10" s="243" t="n"/>
+      <c r="J10" s="244" t="n"/>
       <c r="L10" s="142" t="n"/>
       <c r="M10" s="142" t="n"/>
       <c r="N10" s="142" t="n"/>
@@ -5062,45 +5052,45 @@
           <t>AREA TOTAL</t>
         </is>
       </c>
-      <c r="D11" s="245" t="n"/>
+      <c r="D11" s="244" t="n"/>
       <c r="E11" s="279" t="inlineStr">
         <is>
           <t>AREA DE RESERVA LEGAL</t>
         </is>
       </c>
-      <c r="F11" s="245" t="n"/>
+      <c r="F11" s="244" t="n"/>
       <c r="G11" s="279" t="inlineStr">
         <is>
           <t>AREA DE APP</t>
         </is>
       </c>
-      <c r="H11" s="245" t="n"/>
+      <c r="H11" s="244" t="n"/>
       <c r="I11" s="280" t="inlineStr">
         <is>
           <t>ÁREA CONSOLIDADA</t>
         </is>
       </c>
-      <c r="J11" s="245" t="n"/>
+      <c r="J11" s="244" t="n"/>
     </row>
     <row r="12">
       <c r="C12" s="273" t="n">
         <v>769.477</v>
       </c>
-      <c r="D12" s="245" t="n"/>
+      <c r="D12" s="244" t="n"/>
       <c r="E12" s="273" t="n">
         <v>271.2444</v>
       </c>
-      <c r="F12" s="245" t="n"/>
+      <c r="F12" s="244" t="n"/>
       <c r="G12" s="274" t="n">
         <v>23.6993</v>
       </c>
-      <c r="H12" s="245" t="n"/>
+      <c r="H12" s="244" t="n"/>
       <c r="I12" s="284" t="inlineStr">
         <is>
           <t xml:space="preserve"> -</t>
         </is>
       </c>
-      <c r="J12" s="245" t="n"/>
+      <c r="J12" s="244" t="n"/>
     </row>
     <row r="13">
       <c r="C13" s="279" t="inlineStr">
@@ -5108,37 +5098,37 @@
           <t>SITUAÇÃO</t>
         </is>
       </c>
-      <c r="D13" s="245" t="n"/>
+      <c r="D13" s="244" t="n"/>
       <c r="E13" s="274" t="inlineStr">
         <is>
           <t>Ativo</t>
         </is>
       </c>
-      <c r="F13" s="245" t="n"/>
+      <c r="F13" s="244" t="n"/>
       <c r="G13" s="279" t="inlineStr">
         <is>
           <t>CONDIÇÃO</t>
         </is>
       </c>
-      <c r="H13" s="245" t="n"/>
+      <c r="H13" s="244" t="n"/>
       <c r="I13" s="275" t="inlineStr">
         <is>
           <t>Aguardando Análise</t>
         </is>
       </c>
-      <c r="J13" s="245" t="n"/>
+      <c r="J13" s="244" t="n"/>
     </row>
     <row r="16">
       <c r="C16" s="287">
         <f>C4</f>
         <v/>
       </c>
-      <c r="D16" s="244" t="n"/>
-      <c r="E16" s="244" t="n"/>
-      <c r="F16" s="244" t="n"/>
-      <c r="G16" s="244" t="n"/>
-      <c r="H16" s="244" t="n"/>
-      <c r="I16" s="245" t="n"/>
+      <c r="D16" s="243" t="n"/>
+      <c r="E16" s="243" t="n"/>
+      <c r="F16" s="243" t="n"/>
+      <c r="G16" s="243" t="n"/>
+      <c r="H16" s="243" t="n"/>
+      <c r="I16" s="244" t="n"/>
     </row>
     <row r="17">
       <c r="C17" s="282" t="inlineStr">
@@ -5146,20 +5136,20 @@
           <t>USO DA TERRA</t>
         </is>
       </c>
-      <c r="D17" s="244" t="n"/>
-      <c r="E17" s="245" t="n"/>
+      <c r="D17" s="243" t="n"/>
+      <c r="E17" s="244" t="n"/>
       <c r="F17" s="282" t="inlineStr">
         <is>
           <t>ÁREA (ha)</t>
         </is>
       </c>
-      <c r="G17" s="245" t="n"/>
+      <c r="G17" s="244" t="n"/>
       <c r="H17" s="282" t="inlineStr">
         <is>
           <t>% ÁREA</t>
         </is>
       </c>
-      <c r="I17" s="245" t="n"/>
+      <c r="I17" s="244" t="n"/>
     </row>
     <row r="18">
       <c r="C18" s="285" t="inlineStr">
@@ -5167,18 +5157,18 @@
           <t>Área de Vegetação Remanescente</t>
         </is>
       </c>
-      <c r="D18" s="244" t="n"/>
-      <c r="E18" s="245" t="n"/>
+      <c r="D18" s="243" t="n"/>
+      <c r="E18" s="244" t="n"/>
       <c r="F18" s="283">
         <f>AMOSTRAS!E11</f>
         <v/>
       </c>
-      <c r="G18" s="245" t="n"/>
+      <c r="G18" s="244" t="n"/>
       <c r="H18" s="288">
         <f>AMOSTRAS!F11</f>
         <v/>
       </c>
-      <c r="I18" s="245" t="n"/>
+      <c r="I18" s="244" t="n"/>
     </row>
     <row r="19">
       <c r="C19" s="285" t="inlineStr">
@@ -5186,18 +5176,18 @@
           <t>Área De Reserva Legal e APP</t>
         </is>
       </c>
-      <c r="D19" s="244" t="n"/>
-      <c r="E19" s="245" t="n"/>
+      <c r="D19" s="243" t="n"/>
+      <c r="E19" s="244" t="n"/>
       <c r="F19" s="277">
         <f>AMOSTRAS!E12</f>
         <v/>
       </c>
-      <c r="G19" s="245" t="n"/>
+      <c r="G19" s="244" t="n"/>
       <c r="H19" s="276">
         <f>F19/C6</f>
         <v/>
       </c>
-      <c r="I19" s="245" t="n"/>
+      <c r="I19" s="244" t="n"/>
     </row>
     <row r="20">
       <c r="C20" s="289" t="inlineStr">
@@ -5205,18 +5195,18 @@
           <t>SOMATÓRIA</t>
         </is>
       </c>
-      <c r="D20" s="244" t="n"/>
-      <c r="E20" s="245" t="n"/>
+      <c r="D20" s="243" t="n"/>
+      <c r="E20" s="244" t="n"/>
       <c r="F20" s="277">
         <f>SUM(F18:G19)</f>
         <v/>
       </c>
-      <c r="G20" s="245" t="n"/>
+      <c r="G20" s="244" t="n"/>
       <c r="H20" s="276">
         <f>SUM(H18:I19)</f>
         <v/>
       </c>
-      <c r="I20" s="245" t="n"/>
+      <c r="I20" s="244" t="n"/>
       <c r="J20" s="140" t="n"/>
     </row>
   </sheetData>
@@ -5291,8 +5281,8 @@
     <col width="9.140625" customWidth="1" style="272" min="12" max="12"/>
     <col width="14.28515625" customWidth="1" style="272" min="13" max="13"/>
     <col width="14.42578125" customWidth="1" style="272" min="14" max="14"/>
-    <col width="9.140625" customWidth="1" style="272" min="15" max="19"/>
-    <col width="9.140625" customWidth="1" style="272" min="20" max="16384"/>
+    <col width="9.140625" customWidth="1" style="272" min="15" max="42"/>
+    <col width="9.140625" customWidth="1" style="272" min="43" max="16384"/>
   </cols>
   <sheetData>
     <row r="3" ht="15" customHeight="1" s="236">
@@ -5313,7 +5303,7 @@
           <t>MÉDIA DAS AMOSTRAS</t>
         </is>
       </c>
-      <c r="M3" s="245" t="n"/>
+      <c r="M3" s="244" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1" s="236">
       <c r="B4" s="149" t="n"/>
@@ -5545,8 +5535,8 @@
           <t>SOMATÓRIA</t>
         </is>
       </c>
-      <c r="C13" s="252" t="n"/>
-      <c r="D13" s="252" t="n"/>
+      <c r="C13" s="251" t="n"/>
+      <c r="D13" s="251" t="n"/>
       <c r="E13" s="172">
         <f>SUM(E11:E12)</f>
         <v/>
@@ -5559,7 +5549,7 @@
         <f>F12*G12+F11*G11</f>
         <v/>
       </c>
-      <c r="H13" s="252" t="n"/>
+      <c r="H13" s="251" t="n"/>
       <c r="I13" s="124" t="n"/>
       <c r="J13" s="173" t="n"/>
       <c r="K13" s="170" t="n"/>
@@ -5806,8 +5796,8 @@
           <t>SOMATÓRIA</t>
         </is>
       </c>
-      <c r="C26" s="252" t="n"/>
-      <c r="D26" s="252" t="n"/>
+      <c r="C26" s="251" t="n"/>
+      <c r="D26" s="251" t="n"/>
       <c r="E26" s="308">
         <f>SUM(E24:E25)</f>
         <v/>
@@ -5818,7 +5808,7 @@
       <c r="G26" s="308" t="n">
         <v>0.7333333333333329</v>
       </c>
-      <c r="H26" s="252" t="n"/>
+      <c r="H26" s="251" t="n"/>
       <c r="I26" s="156" t="n"/>
     </row>
     <row r="27" ht="15" customHeight="1" s="236">
@@ -6055,8 +6045,8 @@
           <t>SOMATÓRIA</t>
         </is>
       </c>
-      <c r="C39" s="252" t="n"/>
-      <c r="D39" s="252" t="n"/>
+      <c r="C39" s="251" t="n"/>
+      <c r="D39" s="251" t="n"/>
       <c r="E39" s="172" t="n">
         <v>4035</v>
       </c>
@@ -6066,7 +6056,7 @@
       <c r="G39" s="308" t="n">
         <v>0.6272614622057001</v>
       </c>
-      <c r="H39" s="252" t="n"/>
+      <c r="H39" s="251" t="n"/>
       <c r="I39" s="156" t="n"/>
     </row>
     <row r="40" ht="15" customHeight="1" s="236">
@@ -6303,8 +6293,8 @@
           <t>SOMATÓRIA</t>
         </is>
       </c>
-      <c r="C52" s="252" t="n"/>
-      <c r="D52" s="252" t="n"/>
+      <c r="C52" s="251" t="n"/>
+      <c r="D52" s="251" t="n"/>
       <c r="E52" s="172" t="n">
         <v>1326.16</v>
       </c>
@@ -6314,7 +6304,7 @@
       <c r="G52" s="308" t="n">
         <v>0.6904868190866864</v>
       </c>
-      <c r="H52" s="252" t="n"/>
+      <c r="H52" s="251" t="n"/>
       <c r="I52" s="156" t="n"/>
     </row>
     <row r="53" ht="15" customHeight="1" s="236">
@@ -6554,8 +6544,8 @@
           <t>SOMATÓRIA</t>
         </is>
       </c>
-      <c r="C65" s="252" t="n"/>
-      <c r="D65" s="252" t="n"/>
+      <c r="C65" s="251" t="n"/>
+      <c r="D65" s="251" t="n"/>
       <c r="E65" s="172" t="n">
         <v>416.27</v>
       </c>
@@ -6565,7 +6555,7 @@
       <c r="G65" s="308" t="n">
         <v>0.8600000000000001</v>
       </c>
-      <c r="H65" s="252" t="n"/>
+      <c r="H65" s="251" t="n"/>
       <c r="I65" s="156" t="n"/>
     </row>
     <row r="66" ht="15" customHeight="1" s="236">
@@ -6809,8 +6799,8 @@
           <t>SOMATÓRIA</t>
         </is>
       </c>
-      <c r="C78" s="252" t="n"/>
-      <c r="D78" s="252" t="n"/>
+      <c r="C78" s="251" t="n"/>
+      <c r="D78" s="251" t="n"/>
       <c r="E78" s="172" t="n">
         <v>1839</v>
       </c>
@@ -6820,7 +6810,7 @@
       <c r="G78" s="308" t="n">
         <v>0.8599999999999999</v>
       </c>
-      <c r="H78" s="252" t="n"/>
+      <c r="H78" s="251" t="n"/>
       <c r="I78" s="156" t="n"/>
     </row>
     <row r="79" ht="15" customHeight="1" s="236">
@@ -7062,8 +7052,8 @@
           <t>SOMATÓRIA</t>
         </is>
       </c>
-      <c r="C91" s="252" t="n"/>
-      <c r="D91" s="252" t="n"/>
+      <c r="C91" s="251" t="n"/>
+      <c r="D91" s="251" t="n"/>
       <c r="E91" s="172" t="n">
         <v>6098.4</v>
       </c>
@@ -7073,7 +7063,7 @@
       <c r="G91" s="308" t="n">
         <v>0.86</v>
       </c>
-      <c r="H91" s="252" t="n"/>
+      <c r="H91" s="251" t="n"/>
       <c r="I91" s="156" t="n"/>
       <c r="L91" s="142" t="n"/>
     </row>
@@ -7144,8 +7134,8 @@
     <mergeCell ref="C47:D47"/>
     <mergeCell ref="G38:H38"/>
     <mergeCell ref="B68:D68"/>
+    <mergeCell ref="B83:D83"/>
     <mergeCell ref="H85:I85"/>
-    <mergeCell ref="B83:D83"/>
     <mergeCell ref="G62:H62"/>
     <mergeCell ref="G49:H49"/>
     <mergeCell ref="H69:I69"/>
@@ -7188,21 +7178,21 @@
     <mergeCell ref="E44:F44"/>
     <mergeCell ref="G39:H39"/>
     <mergeCell ref="C20:D20"/>
+    <mergeCell ref="H21:I21"/>
     <mergeCell ref="E20:F20"/>
-    <mergeCell ref="H21:I21"/>
     <mergeCell ref="C85:D85"/>
     <mergeCell ref="H73:I73"/>
     <mergeCell ref="E29:F29"/>
+    <mergeCell ref="B49:D49"/>
     <mergeCell ref="H60:I60"/>
-    <mergeCell ref="B49:D49"/>
     <mergeCell ref="G37:H37"/>
     <mergeCell ref="C84:D84"/>
     <mergeCell ref="E69:F69"/>
     <mergeCell ref="E84:F84"/>
+    <mergeCell ref="B65:D65"/>
+    <mergeCell ref="B61:I61"/>
+    <mergeCell ref="B67:I67"/>
     <mergeCell ref="G13:H13"/>
-    <mergeCell ref="B61:I61"/>
-    <mergeCell ref="B65:D65"/>
-    <mergeCell ref="B67:I67"/>
     <mergeCell ref="G78:H78"/>
     <mergeCell ref="B51:D51"/>
     <mergeCell ref="E31:F31"/>
@@ -7211,10 +7201,10 @@
     <mergeCell ref="E6:F6"/>
     <mergeCell ref="C46:D46"/>
     <mergeCell ref="C21:D21"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="E46:F46"/>
+    <mergeCell ref="E86:F86"/>
     <mergeCell ref="B63:D63"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="E86:F86"/>
-    <mergeCell ref="E46:F46"/>
     <mergeCell ref="B50:D50"/>
     <mergeCell ref="H57:I57"/>
     <mergeCell ref="G89:H89"/>
@@ -7242,17 +7232,17 @@
     <mergeCell ref="E43:F43"/>
     <mergeCell ref="H20:I20"/>
     <mergeCell ref="G52:H52"/>
+    <mergeCell ref="C33:D33"/>
     <mergeCell ref="H29:I29"/>
-    <mergeCell ref="C33:D33"/>
     <mergeCell ref="E33:F33"/>
     <mergeCell ref="E42:F42"/>
     <mergeCell ref="B3:I3"/>
     <mergeCell ref="G36:H36"/>
     <mergeCell ref="H4:I4"/>
-    <mergeCell ref="H44:I44"/>
+    <mergeCell ref="B29:D29"/>
     <mergeCell ref="E17:F17"/>
     <mergeCell ref="B69:D69"/>
-    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="H44:I44"/>
     <mergeCell ref="B38:D38"/>
     <mergeCell ref="E82:F82"/>
     <mergeCell ref="H59:I59"/>
@@ -7318,8 +7308,8 @@
     <col width="10.7109375" customWidth="1" style="272" min="10" max="10"/>
     <col width="30.7109375" customWidth="1" style="272" min="11" max="11"/>
     <col width="17.42578125" bestFit="1" customWidth="1" style="272" min="12" max="12"/>
-    <col width="9.140625" customWidth="1" style="272" min="13" max="17"/>
-    <col width="9.140625" customWidth="1" style="272" min="18" max="16384"/>
+    <col width="9.140625" customWidth="1" style="272" min="13" max="40"/>
+    <col width="9.140625" customWidth="1" style="272" min="41" max="16384"/>
   </cols>
   <sheetData>
     <row r="3" ht="13.5" customHeight="1" s="236">
@@ -7661,8 +7651,8 @@
     <col width="20.7109375" customWidth="1" style="331" min="16" max="16"/>
     <col width="19.140625" bestFit="1" customWidth="1" style="331" min="17" max="17"/>
     <col width="15.85546875" bestFit="1" customWidth="1" style="331" min="18" max="18"/>
-    <col width="9.140625" customWidth="1" style="331" min="19" max="23"/>
-    <col width="9.140625" customWidth="1" style="331" min="24" max="16384"/>
+    <col width="9.140625" customWidth="1" style="331" min="19" max="46"/>
+    <col width="9.140625" customWidth="1" style="331" min="47" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1" s="236">
@@ -8271,7 +8261,7 @@
           <t>CCU Indexado¹</t>
         </is>
       </c>
-      <c r="B12" s="245" t="n"/>
+      <c r="B12" s="244" t="n"/>
       <c r="C12" s="333" t="inlineStr">
         <is>
           <t>obtido da seguinte forma = (CCU imóvel Avaliando - CCU elmento da amostra) + 1</t>
@@ -8298,7 +8288,7 @@
           <t>Situação Indexado ²</t>
         </is>
       </c>
-      <c r="B13" s="245" t="n"/>
+      <c r="B13" s="244" t="n"/>
       <c r="C13" s="333" t="inlineStr">
         <is>
           <t>obtido da seguinte forma = (Situação imóvel Avaliando - Situação elmento da amostra) + 1</t>
@@ -8324,7 +8314,7 @@
         <f>L3</f>
         <v/>
       </c>
-      <c r="B14" s="245" t="n"/>
+      <c r="B14" s="244" t="n"/>
       <c r="C14" s="333" t="inlineStr">
         <is>
           <t>obtido da seguinte forma = (Distância imóvel Avaliando - Distância elmento da amostra) + 1</t>
@@ -8351,7 +8341,7 @@
           <t>Hidrografia Indexado 4</t>
         </is>
       </c>
-      <c r="B15" s="245" t="n"/>
+      <c r="B15" s="244" t="n"/>
       <c r="C15" s="333" t="inlineStr">
         <is>
           <t>obtido da seguinte forma = (Hidrografia imóvel Avaliando - Hidrografia elmento da amostra) + 1</t>
@@ -8378,7 +8368,7 @@
           <t>Fator Homogeneização Total (FHT) 6</t>
         </is>
       </c>
-      <c r="B16" s="245" t="n"/>
+      <c r="B16" s="244" t="n"/>
       <c r="C16" s="330" t="inlineStr">
         <is>
           <t xml:space="preserve">Obtido pela multiplicação do CCU Indexado, da Situação Indexado, Distância Indexado, Hidrografia Indexado e Fator Oferta </t>
@@ -8398,7 +8388,7 @@
           <t>VT/ha homogeneizado 7</t>
         </is>
       </c>
-      <c r="B17" s="245" t="n"/>
+      <c r="B17" s="244" t="n"/>
       <c r="C17" s="330" t="inlineStr">
         <is>
           <t>Resultado da multiplicação do VT / ha do elementdo da amostra pelo seu FHT</t>
@@ -8431,7 +8421,7 @@
           <t>Limite Superior</t>
         </is>
       </c>
-      <c r="B18" s="245" t="n"/>
+      <c r="B18" s="244" t="n"/>
       <c r="C18" s="330" t="inlineStr">
         <is>
           <t>Limite superior de valor de VT/ha homogeneizado</t>
@@ -8457,7 +8447,7 @@
           <t>Limite Inferior</t>
         </is>
       </c>
-      <c r="B19" s="245" t="n"/>
+      <c r="B19" s="244" t="n"/>
       <c r="C19" s="330" t="inlineStr">
         <is>
           <t>Limite Inferior de valor de VT/ha homogeneizado</t>
@@ -8484,7 +8474,7 @@
           <t>Amostra Saneada</t>
         </is>
       </c>
-      <c r="B20" s="245" t="n"/>
+      <c r="B20" s="244" t="n"/>
       <c r="C20" s="330" t="inlineStr">
         <is>
           <t>Elemento que apresente seu VT/ ha homogeneizado maior que o limite superior ou menor que o limite inferior</t>
@@ -8511,7 +8501,7 @@
           <t>Média após Saneamento</t>
         </is>
       </c>
-      <c r="B21" s="245" t="n"/>
+      <c r="B21" s="244" t="n"/>
       <c r="C21" s="330" t="inlineStr">
         <is>
           <t>Média de Valor calculado após eliminação dos elementos saneados</t>
@@ -8538,7 +8528,7 @@
           <t>Fator para I.C.</t>
         </is>
       </c>
-      <c r="B22" s="245" t="n"/>
+      <c r="B22" s="244" t="n"/>
       <c r="C22" s="337" t="inlineStr">
         <is>
           <t>= t*(Desvio padrão saneado/ √ do numero de elementos utilizado), onde "t" é percentil da distribuição de Student, com grau de liberdade ( V = n-1) e 80% de confiança</t>
@@ -8562,7 +8552,7 @@
           <t>I.C. Superior</t>
         </is>
       </c>
-      <c r="B23" s="245" t="n"/>
+      <c r="B23" s="244" t="n"/>
       <c r="C23" s="330" t="inlineStr">
         <is>
           <t>Média Saneada + Fator para I.C.</t>
@@ -8588,7 +8578,7 @@
           <t>I.C. Inferior</t>
         </is>
       </c>
-      <c r="B24" s="245" t="n"/>
+      <c r="B24" s="244" t="n"/>
       <c r="C24" s="330" t="inlineStr">
         <is>
           <t>Média Saneada - Fator para I.C.</t>
@@ -8614,7 +8604,7 @@
           <t>Amplitude</t>
         </is>
       </c>
-      <c r="B25" s="245" t="n"/>
+      <c r="B25" s="244" t="n"/>
       <c r="C25" s="330" t="inlineStr">
         <is>
           <t>I.C. Superior - I.C. Inferior</t>
@@ -8687,8 +8677,8 @@
     <mergeCell ref="C13:K13"/>
     <mergeCell ref="C18:K18"/>
     <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A17:B17"/>
     <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A17:B17"/>
     <mergeCell ref="A22:B22"/>
     <mergeCell ref="E1:N1"/>
     <mergeCell ref="A20:B20"/>
@@ -8881,15 +8871,15 @@
           <t xml:space="preserve">Valor médio apurado (R$/ha) </t>
         </is>
       </c>
-      <c r="D14" s="244" t="n"/>
-      <c r="E14" s="244" t="n"/>
+      <c r="D14" s="243" t="n"/>
+      <c r="E14" s="243" t="n"/>
       <c r="F14" s="340">
         <f>'PLANILHA HOMOG'!Q17</f>
         <v/>
       </c>
-      <c r="G14" s="244" t="n"/>
-      <c r="H14" s="245" t="n"/>
-      <c r="J14" s="356">
+      <c r="G14" s="243" t="n"/>
+      <c r="H14" s="244" t="n"/>
+      <c r="J14" s="357">
         <f>F14*4.84</f>
         <v/>
       </c>
@@ -8946,14 +8936,14 @@
           <t>Valor adotado</t>
         </is>
       </c>
-      <c r="D20" s="244" t="n"/>
-      <c r="E20" s="244" t="n"/>
+      <c r="D20" s="243" t="n"/>
+      <c r="E20" s="243" t="n"/>
       <c r="F20" s="340">
         <f>F19</f>
         <v/>
       </c>
-      <c r="G20" s="244" t="n"/>
-      <c r="H20" s="245" t="n"/>
+      <c r="G20" s="243" t="n"/>
+      <c r="H20" s="244" t="n"/>
     </row>
     <row r="21">
       <c r="C21" s="344" t="n"/>
@@ -8968,7 +8958,7 @@
       <c r="F23" s="348" t="n"/>
     </row>
     <row r="24">
-      <c r="C24" s="357" t="inlineStr">
+      <c r="C24" s="356" t="inlineStr">
         <is>
           <t>VALOR DE BENFEITORIAS - PIVÔ CENTRAL + hidraulico</t>
         </is>
@@ -9014,14 +9004,14 @@
           <t>Valor adotado</t>
         </is>
       </c>
-      <c r="D28" s="244" t="n"/>
-      <c r="E28" s="244" t="n"/>
+      <c r="D28" s="243" t="n"/>
+      <c r="E28" s="243" t="n"/>
       <c r="F28" s="350">
         <f>F27</f>
         <v/>
       </c>
-      <c r="G28" s="244" t="n"/>
-      <c r="H28" s="245" t="n"/>
+      <c r="G28" s="243" t="n"/>
+      <c r="H28" s="244" t="n"/>
     </row>
     <row r="31">
       <c r="C31" s="341" t="inlineStr">
@@ -9060,14 +9050,14 @@
           <t>Valor Total</t>
         </is>
       </c>
-      <c r="D34" s="244" t="n"/>
-      <c r="E34" s="244" t="n"/>
+      <c r="D34" s="243" t="n"/>
+      <c r="E34" s="243" t="n"/>
       <c r="F34" s="340">
         <f>F32+F33</f>
         <v/>
       </c>
-      <c r="G34" s="244" t="n"/>
-      <c r="H34" s="245" t="n"/>
+      <c r="G34" s="243" t="n"/>
+      <c r="H34" s="244" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="53">
@@ -9087,9 +9077,9 @@
     <mergeCell ref="C12:E12"/>
     <mergeCell ref="F23:H23"/>
     <mergeCell ref="C11:E11"/>
-    <mergeCell ref="F22:H22"/>
     <mergeCell ref="C27:E27"/>
     <mergeCell ref="F28:H28"/>
+    <mergeCell ref="F22:H22"/>
     <mergeCell ref="F13:H13"/>
     <mergeCell ref="C23:E23"/>
     <mergeCell ref="F27:H27"/>
@@ -9110,8 +9100,8 @@
     <mergeCell ref="F34:H34"/>
     <mergeCell ref="C15:H15"/>
     <mergeCell ref="F10:H10"/>
+    <mergeCell ref="C33:E33"/>
     <mergeCell ref="C24:H24"/>
-    <mergeCell ref="C33:E33"/>
     <mergeCell ref="J14:L14"/>
     <mergeCell ref="F19:H19"/>
     <mergeCell ref="F6:H6"/>
@@ -9209,14 +9199,14 @@
           <t>Valor de Liquidação Forçada</t>
         </is>
       </c>
-      <c r="D11" s="244" t="n"/>
-      <c r="E11" s="244" t="n"/>
+      <c r="D11" s="243" t="n"/>
+      <c r="E11" s="243" t="n"/>
       <c r="F11" s="340">
         <f>F10/((1+F7)^(F8/12))</f>
         <v/>
       </c>
-      <c r="G11" s="244" t="n"/>
-      <c r="H11" s="245" t="n"/>
+      <c r="G11" s="243" t="n"/>
+      <c r="H11" s="244" t="n"/>
       <c r="K11" s="133" t="n"/>
       <c r="M11" s="414" t="n"/>
     </row>
@@ -9285,14 +9275,14 @@
           <t>Valor de Liquidação Forçada</t>
         </is>
       </c>
-      <c r="D18" s="244" t="n"/>
-      <c r="E18" s="244" t="n"/>
+      <c r="D18" s="243" t="n"/>
+      <c r="E18" s="243" t="n"/>
       <c r="F18" s="340">
         <f>F17/((1+F14)^(F15/12))</f>
         <v/>
       </c>
-      <c r="G18" s="244" t="n"/>
-      <c r="H18" s="245" t="n"/>
+      <c r="G18" s="243" t="n"/>
+      <c r="H18" s="244" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="23">
@@ -9358,8 +9348,8 @@
     <col width="12.85546875" customWidth="1" style="364" min="33" max="33"/>
     <col width="3.7109375" customWidth="1" style="364" min="34" max="34"/>
     <col width="3" customWidth="1" style="364" min="35" max="36"/>
-    <col width="9.140625" customWidth="1" style="364" min="37" max="41"/>
-    <col width="9.140625" customWidth="1" style="364" min="42" max="16384"/>
+    <col width="9.140625" customWidth="1" style="364" min="37" max="64"/>
+    <col width="9.140625" customWidth="1" style="364" min="65" max="16384"/>
   </cols>
   <sheetData>
     <row r="2" ht="17.1" customFormat="1" customHeight="1" s="375">

--- a/estattis_automação.xlsx
+++ b/estattis_automação.xlsx
@@ -1744,12 +1744,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="38" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="37" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="38" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="37" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1759,11 +1759,11 @@
     <xf numFmtId="167" fontId="37" fillId="3" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="37" fillId="3" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="37" fillId="3" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="3" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="37" fillId="3" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -1802,19 +1802,19 @@
     <xf numFmtId="0" fontId="43" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="10" fontId="42" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="40" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="42" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="43" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="42" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="42" fillId="3" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="43" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="44" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -2001,40 +2001,40 @@
     <xf numFmtId="0" fontId="16" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="34" fillId="6" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="168" fontId="34" fillId="4" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="168" fontId="34" fillId="4" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="168" fontId="0" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="6" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
@@ -2070,12 +2070,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="25" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="14" fontId="27" fillId="3" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
       <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="170" fontId="25" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="171" fontId="26" fillId="3" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center"/>
@@ -3052,7 +3052,7 @@
       <c r="I22" s="251" t="n"/>
       <c r="J22" s="251" t="n"/>
       <c r="K22" s="162" t="n"/>
-      <c r="L22" s="260" t="n"/>
+      <c r="L22" s="261" t="n"/>
       <c r="M22" s="253" t="n"/>
     </row>
     <row r="23" ht="20.25" customHeight="1" s="236">
@@ -3104,10 +3104,10 @@
       <c r="M24" s="244" t="n"/>
     </row>
     <row r="25" ht="17.25" customHeight="1" s="236">
-      <c r="B25" s="261" t="n"/>
+      <c r="B25" s="260" t="n"/>
       <c r="C25" s="238" t="n"/>
       <c r="D25" s="239" t="n"/>
-      <c r="E25" s="255" t="n"/>
+      <c r="E25" s="256" t="n"/>
       <c r="H25" s="270" t="n"/>
       <c r="I25" s="238" t="n"/>
       <c r="J25" s="239" t="n"/>
@@ -3292,7 +3292,7 @@
     <row r="37" ht="15" customHeight="1" s="236">
       <c r="B37" s="269" t="n"/>
       <c r="F37" s="245" t="n"/>
-      <c r="J37" s="256" t="n"/>
+      <c r="J37" s="255" t="n"/>
       <c r="M37" s="241" t="n"/>
     </row>
     <row r="38" ht="15" customHeight="1" s="236">
@@ -3463,22 +3463,22 @@
     <mergeCell ref="B9:D9"/>
     <mergeCell ref="E26:G26"/>
     <mergeCell ref="J38:M38"/>
+    <mergeCell ref="B24:D24"/>
     <mergeCell ref="B3:M4"/>
-    <mergeCell ref="E25:G25"/>
     <mergeCell ref="B20:D20"/>
     <mergeCell ref="J37:M37"/>
-    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="E25:G25"/>
     <mergeCell ref="E20:M20"/>
     <mergeCell ref="E7:M7"/>
     <mergeCell ref="H24:J24"/>
     <mergeCell ref="E22:J22"/>
     <mergeCell ref="B26:D26"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="B7:D7"/>
     <mergeCell ref="E21:M21"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="B25:D25"/>
     <mergeCell ref="E12:M12"/>
     <mergeCell ref="L22:M22"/>
-    <mergeCell ref="B25:D25"/>
     <mergeCell ref="K25:M25"/>
     <mergeCell ref="F36:I36"/>
     <mergeCell ref="E24:G24"/>
@@ -3518,8 +3518,8 @@
     <col width="15.7109375" customWidth="1" style="400" min="6" max="6"/>
     <col width="10.140625" customWidth="1" style="400" min="7" max="7"/>
     <col width="14.28515625" customWidth="1" style="400" min="8" max="8"/>
-    <col width="9.140625" customWidth="1" style="400" min="9" max="36"/>
-    <col width="9.140625" customWidth="1" style="400" min="37" max="16384"/>
+    <col width="9.140625" customWidth="1" style="400" min="9" max="53"/>
+    <col width="9.140625" customWidth="1" style="400" min="54" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="17.1" customHeight="1" s="236">
@@ -3983,8 +3983,8 @@
     <col width="8.85546875" customWidth="1" style="24" min="5" max="5"/>
     <col width="10.140625" customWidth="1" style="24" min="6" max="6"/>
     <col width="12.7109375" customWidth="1" style="24" min="7" max="7"/>
-    <col width="9.140625" customWidth="1" style="24" min="8" max="35"/>
-    <col width="9.140625" customWidth="1" style="24" min="36" max="16384"/>
+    <col width="9.140625" customWidth="1" style="24" min="8" max="52"/>
+    <col width="9.140625" customWidth="1" style="24" min="53" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="17.1" customFormat="1" customHeight="1" s="400">
@@ -4136,7 +4136,7 @@
           <t>Proponente:</t>
         </is>
       </c>
-      <c r="C2" s="450" t="inlineStr">
+      <c r="C2" s="451" t="inlineStr">
         <is>
           <t>marco antonio feitosa</t>
         </is>
@@ -4450,8 +4450,8 @@
     <col width="9.140625" customWidth="1" style="272" min="1" max="3"/>
     <col width="29.85546875" customWidth="1" style="272" min="4" max="4"/>
     <col width="16.5703125" customWidth="1" style="272" min="5" max="5"/>
-    <col width="9.140625" customWidth="1" style="272" min="6" max="33"/>
-    <col width="9.140625" customWidth="1" style="272" min="34" max="16384"/>
+    <col width="9.140625" customWidth="1" style="272" min="6" max="50"/>
+    <col width="9.140625" customWidth="1" style="272" min="51" max="16384"/>
   </cols>
   <sheetData>
     <row r="8" ht="13.5" customHeight="1" s="236" thickBot="1"/>
@@ -4791,8 +4791,8 @@
     <col width="8.28515625" bestFit="1" customWidth="1" style="272" min="7" max="7"/>
     <col width="9.140625" customWidth="1" style="272" min="8" max="9"/>
     <col width="14.42578125" customWidth="1" style="272" min="10" max="10"/>
-    <col width="9.140625" customWidth="1" style="272" min="11" max="38"/>
-    <col width="9.140625" customWidth="1" style="272" min="39" max="16384"/>
+    <col width="9.140625" customWidth="1" style="272" min="11" max="55"/>
+    <col width="9.140625" customWidth="1" style="272" min="56" max="16384"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -4905,7 +4905,7 @@
         </is>
       </c>
       <c r="H6" s="244" t="n"/>
-      <c r="I6" s="275" t="inlineStr">
+      <c r="I6" s="276" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4960,19 +4960,19 @@
       <c r="T7" s="142" t="n"/>
     </row>
     <row r="8">
-      <c r="C8" s="279" t="inlineStr">
+      <c r="C8" s="277" t="inlineStr">
         <is>
           <t>AREA TOTAL</t>
         </is>
       </c>
       <c r="D8" s="244" t="n"/>
-      <c r="E8" s="279" t="inlineStr">
+      <c r="E8" s="277" t="inlineStr">
         <is>
           <t>CLASSIFICAÇÃO FUNDIÁRIA</t>
         </is>
       </c>
       <c r="F8" s="244" t="n"/>
-      <c r="G8" s="279" t="inlineStr">
+      <c r="G8" s="277" t="inlineStr">
         <is>
           <t>MÓDULO RURAL</t>
         </is>
@@ -5047,19 +5047,19 @@
       <c r="T10" s="142" t="n"/>
     </row>
     <row r="11">
-      <c r="C11" s="279" t="inlineStr">
+      <c r="C11" s="277" t="inlineStr">
         <is>
           <t>AREA TOTAL</t>
         </is>
       </c>
       <c r="D11" s="244" t="n"/>
-      <c r="E11" s="279" t="inlineStr">
+      <c r="E11" s="277" t="inlineStr">
         <is>
           <t>AREA DE RESERVA LEGAL</t>
         </is>
       </c>
       <c r="F11" s="244" t="n"/>
-      <c r="G11" s="279" t="inlineStr">
+      <c r="G11" s="277" t="inlineStr">
         <is>
           <t>AREA DE APP</t>
         </is>
@@ -5093,7 +5093,7 @@
       <c r="J12" s="244" t="n"/>
     </row>
     <row r="13">
-      <c r="C13" s="279" t="inlineStr">
+      <c r="C13" s="277" t="inlineStr">
         <is>
           <t>SITUAÇÃO</t>
         </is>
@@ -5105,13 +5105,13 @@
         </is>
       </c>
       <c r="F13" s="244" t="n"/>
-      <c r="G13" s="279" t="inlineStr">
+      <c r="G13" s="277" t="inlineStr">
         <is>
           <t>CONDIÇÃO</t>
         </is>
       </c>
       <c r="H13" s="244" t="n"/>
-      <c r="I13" s="275" t="inlineStr">
+      <c r="I13" s="276" t="inlineStr">
         <is>
           <t>Aguardando Análise</t>
         </is>
@@ -5178,12 +5178,12 @@
       </c>
       <c r="D19" s="243" t="n"/>
       <c r="E19" s="244" t="n"/>
-      <c r="F19" s="277">
+      <c r="F19" s="279">
         <f>AMOSTRAS!E12</f>
         <v/>
       </c>
       <c r="G19" s="244" t="n"/>
-      <c r="H19" s="276">
+      <c r="H19" s="275">
         <f>F19/C6</f>
         <v/>
       </c>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="D20" s="243" t="n"/>
       <c r="E20" s="244" t="n"/>
-      <c r="F20" s="277">
+      <c r="F20" s="279">
         <f>SUM(F18:G19)</f>
         <v/>
       </c>
       <c r="G20" s="244" t="n"/>
-      <c r="H20" s="276">
+      <c r="H20" s="275">
         <f>SUM(H18:I19)</f>
         <v/>
       </c>
@@ -5214,18 +5214,18 @@
     <mergeCell ref="E12:F12"/>
     <mergeCell ref="G12:H12"/>
     <mergeCell ref="C6:D6"/>
+    <mergeCell ref="I6:J6"/>
     <mergeCell ref="H20:I20"/>
-    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C5:D5"/>
     <mergeCell ref="G11:H11"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="F19:G19"/>
     <mergeCell ref="I11:J11"/>
     <mergeCell ref="E5:F5"/>
     <mergeCell ref="G8:H8"/>
     <mergeCell ref="E8:F8"/>
     <mergeCell ref="C4:J4"/>
+    <mergeCell ref="F20:G20"/>
     <mergeCell ref="C10:J10"/>
-    <mergeCell ref="F20:G20"/>
     <mergeCell ref="F18:G18"/>
     <mergeCell ref="C17:E17"/>
     <mergeCell ref="E13:F13"/>
@@ -5281,8 +5281,8 @@
     <col width="9.140625" customWidth="1" style="272" min="12" max="12"/>
     <col width="14.28515625" customWidth="1" style="272" min="13" max="13"/>
     <col width="14.42578125" customWidth="1" style="272" min="14" max="14"/>
-    <col width="9.140625" customWidth="1" style="272" min="15" max="42"/>
-    <col width="9.140625" customWidth="1" style="272" min="43" max="16384"/>
+    <col width="9.140625" customWidth="1" style="272" min="15" max="59"/>
+    <col width="9.140625" customWidth="1" style="272" min="60" max="16384"/>
   </cols>
   <sheetData>
     <row r="3" ht="15" customHeight="1" s="236">
@@ -7134,9 +7134,9 @@
     <mergeCell ref="C47:D47"/>
     <mergeCell ref="G38:H38"/>
     <mergeCell ref="B68:D68"/>
-    <mergeCell ref="B83:D83"/>
     <mergeCell ref="H85:I85"/>
     <mergeCell ref="G62:H62"/>
+    <mergeCell ref="B83:D83"/>
     <mergeCell ref="G49:H49"/>
     <mergeCell ref="H69:I69"/>
     <mergeCell ref="B5:D5"/>
@@ -7158,8 +7158,8 @@
     <mergeCell ref="G25:H25"/>
     <mergeCell ref="G90:H90"/>
     <mergeCell ref="H5:I5"/>
+    <mergeCell ref="B41:I41"/>
     <mergeCell ref="B39:D39"/>
-    <mergeCell ref="B41:I41"/>
     <mergeCell ref="E18:F18"/>
     <mergeCell ref="E58:F58"/>
     <mergeCell ref="B35:I35"/>
@@ -7201,10 +7201,10 @@
     <mergeCell ref="E6:F6"/>
     <mergeCell ref="C46:D46"/>
     <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E46:F46"/>
+    <mergeCell ref="B63:D63"/>
+    <mergeCell ref="E86:F86"/>
     <mergeCell ref="H16:I16"/>
-    <mergeCell ref="E46:F46"/>
-    <mergeCell ref="E86:F86"/>
-    <mergeCell ref="B63:D63"/>
     <mergeCell ref="B50:D50"/>
     <mergeCell ref="H57:I57"/>
     <mergeCell ref="G89:H89"/>
@@ -7308,8 +7308,8 @@
     <col width="10.7109375" customWidth="1" style="272" min="10" max="10"/>
     <col width="30.7109375" customWidth="1" style="272" min="11" max="11"/>
     <col width="17.42578125" bestFit="1" customWidth="1" style="272" min="12" max="12"/>
-    <col width="9.140625" customWidth="1" style="272" min="13" max="40"/>
-    <col width="9.140625" customWidth="1" style="272" min="41" max="16384"/>
+    <col width="9.140625" customWidth="1" style="272" min="13" max="57"/>
+    <col width="9.140625" customWidth="1" style="272" min="58" max="16384"/>
   </cols>
   <sheetData>
     <row r="3" ht="13.5" customHeight="1" s="236">
@@ -7370,7 +7370,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="279" t="n">
+      <c r="B4" s="277" t="n">
         <v>1</v>
       </c>
       <c r="C4" s="178">
@@ -7412,7 +7412,7 @@
       <c r="M4" s="141" t="n"/>
     </row>
     <row r="5">
-      <c r="B5" s="279" t="n">
+      <c r="B5" s="277" t="n">
         <v>2</v>
       </c>
       <c r="C5" s="178">
@@ -7454,7 +7454,7 @@
       <c r="M5" s="141" t="n"/>
     </row>
     <row r="6">
-      <c r="B6" s="279" t="n">
+      <c r="B6" s="277" t="n">
         <v>3</v>
       </c>
       <c r="C6" s="178">
@@ -7496,7 +7496,7 @@
       <c r="M6" s="141" t="n"/>
     </row>
     <row r="7">
-      <c r="B7" s="279" t="n">
+      <c r="B7" s="277" t="n">
         <v>4</v>
       </c>
       <c r="C7" s="178">
@@ -7538,7 +7538,7 @@
       <c r="M7" s="141" t="n"/>
     </row>
     <row r="8">
-      <c r="B8" s="279" t="n">
+      <c r="B8" s="277" t="n">
         <v>5</v>
       </c>
       <c r="C8" s="178">
@@ -7580,7 +7580,7 @@
       <c r="M8" s="141" t="n"/>
     </row>
     <row r="9">
-      <c r="B9" s="279" t="n">
+      <c r="B9" s="277" t="n">
         <v>6</v>
       </c>
       <c r="C9" s="178">
@@ -7651,8 +7651,8 @@
     <col width="20.7109375" customWidth="1" style="331" min="16" max="16"/>
     <col width="19.140625" bestFit="1" customWidth="1" style="331" min="17" max="17"/>
     <col width="15.85546875" bestFit="1" customWidth="1" style="331" min="18" max="18"/>
-    <col width="9.140625" customWidth="1" style="331" min="19" max="46"/>
-    <col width="9.140625" customWidth="1" style="331" min="47" max="16384"/>
+    <col width="9.140625" customWidth="1" style="331" min="19" max="63"/>
+    <col width="9.140625" customWidth="1" style="331" min="64" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1" s="236">
@@ -8677,8 +8677,8 @@
     <mergeCell ref="C13:K13"/>
     <mergeCell ref="C18:K18"/>
     <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A23:B23"/>
     <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A23:B23"/>
     <mergeCell ref="A22:B22"/>
     <mergeCell ref="E1:N1"/>
     <mergeCell ref="A20:B20"/>
@@ -8866,7 +8866,7 @@
       <c r="H13" s="241" t="n"/>
     </row>
     <row r="14" ht="15" customHeight="1" s="236">
-      <c r="C14" s="353" t="inlineStr">
+      <c r="C14" s="342" t="inlineStr">
         <is>
           <t xml:space="preserve">Valor médio apurado (R$/ha) </t>
         </is>
@@ -8931,7 +8931,7 @@
       <c r="H19" s="241" t="n"/>
     </row>
     <row r="20" ht="15" customHeight="1" s="236">
-      <c r="C20" s="353" t="inlineStr">
+      <c r="C20" s="342" t="inlineStr">
         <is>
           <t>Valor adotado</t>
         </is>
@@ -8947,11 +8947,11 @@
     </row>
     <row r="21">
       <c r="C21" s="344" t="n"/>
-      <c r="F21" s="342" t="n"/>
+      <c r="F21" s="351" t="n"/>
     </row>
     <row r="22">
       <c r="C22" s="344" t="n"/>
-      <c r="F22" s="342" t="n"/>
+      <c r="F22" s="351" t="n"/>
     </row>
     <row r="23">
       <c r="C23" s="344" t="n"/>
@@ -8970,7 +8970,7 @@
           <t>Custo de de Formação (novo)</t>
         </is>
       </c>
-      <c r="F25" s="351" t="n">
+      <c r="F25" s="352" t="n">
         <v>2000000</v>
       </c>
       <c r="H25" s="241" t="n"/>
@@ -8992,14 +8992,14 @@
           <t>Valor depreciado</t>
         </is>
       </c>
-      <c r="F27" s="351">
+      <c r="F27" s="352">
         <f>F25*F26</f>
         <v/>
       </c>
       <c r="H27" s="241" t="n"/>
     </row>
     <row r="28" ht="15" customHeight="1" s="236">
-      <c r="C28" s="352" t="inlineStr">
+      <c r="C28" s="353" t="inlineStr">
         <is>
           <t>Valor adotado</t>
         </is>
@@ -9045,7 +9045,7 @@
       <c r="H33" s="241" t="n"/>
     </row>
     <row r="34" ht="15" customHeight="1" s="236">
-      <c r="C34" s="353" t="inlineStr">
+      <c r="C34" s="342" t="inlineStr">
         <is>
           <t>Valor Total</t>
         </is>
@@ -9063,15 +9063,15 @@
   <mergeCells count="53">
     <mergeCell ref="F20:H20"/>
     <mergeCell ref="C16:H16"/>
-    <mergeCell ref="C20:E20"/>
+    <mergeCell ref="F21:H21"/>
     <mergeCell ref="F18:H18"/>
     <mergeCell ref="F33:H33"/>
     <mergeCell ref="C22:E22"/>
-    <mergeCell ref="C31:H31"/>
+    <mergeCell ref="F32:H32"/>
     <mergeCell ref="C9:E9"/>
     <mergeCell ref="F8:H8"/>
     <mergeCell ref="F26:H26"/>
-    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="C31:H31"/>
     <mergeCell ref="F17:H17"/>
     <mergeCell ref="C21:E21"/>
     <mergeCell ref="C12:E12"/>
@@ -9101,17 +9101,17 @@
     <mergeCell ref="C15:H15"/>
     <mergeCell ref="F10:H10"/>
     <mergeCell ref="C33:E33"/>
-    <mergeCell ref="C24:H24"/>
+    <mergeCell ref="C14:E14"/>
     <mergeCell ref="J14:L14"/>
     <mergeCell ref="F19:H19"/>
     <mergeCell ref="F6:H6"/>
-    <mergeCell ref="C14:E14"/>
+    <mergeCell ref="C24:H24"/>
     <mergeCell ref="C5:H5"/>
     <mergeCell ref="C26:E26"/>
     <mergeCell ref="C4:H4"/>
     <mergeCell ref="F12:H12"/>
     <mergeCell ref="F7:H7"/>
-    <mergeCell ref="F21:H21"/>
+    <mergeCell ref="C20:E20"/>
     <mergeCell ref="C25:E25"/>
     <mergeCell ref="C10:E10"/>
   </mergeCells>
@@ -9194,7 +9194,7 @@
       <c r="H10" s="241" t="n"/>
     </row>
     <row r="11" ht="15" customHeight="1" s="236">
-      <c r="C11" s="353" t="inlineStr">
+      <c r="C11" s="342" t="inlineStr">
         <is>
           <t>Valor de Liquidação Forçada</t>
         </is>
@@ -9270,7 +9270,7 @@
       <c r="H17" s="241" t="n"/>
     </row>
     <row r="18" ht="15" customHeight="1" s="236">
-      <c r="C18" s="353" t="inlineStr">
+      <c r="C18" s="342" t="inlineStr">
         <is>
           <t>Valor de Liquidação Forçada</t>
         </is>
@@ -9348,8 +9348,8 @@
     <col width="12.85546875" customWidth="1" style="364" min="33" max="33"/>
     <col width="3.7109375" customWidth="1" style="364" min="34" max="34"/>
     <col width="3" customWidth="1" style="364" min="35" max="36"/>
-    <col width="9.140625" customWidth="1" style="364" min="37" max="64"/>
-    <col width="9.140625" customWidth="1" style="364" min="65" max="16384"/>
+    <col width="9.140625" customWidth="1" style="364" min="37" max="81"/>
+    <col width="9.140625" customWidth="1" style="364" min="82" max="16384"/>
   </cols>
   <sheetData>
     <row r="2" ht="17.1" customFormat="1" customHeight="1" s="375">
@@ -10169,7 +10169,7 @@
     </row>
     <row r="51" ht="11.25" customHeight="1" s="236"/>
     <row r="52" ht="14.25" customHeight="1" s="236">
-      <c r="H52" s="367" t="n"/>
+      <c r="H52" s="368" t="n"/>
       <c r="I52" s="292" t="n"/>
       <c r="J52" s="292" t="n"/>
       <c r="K52" s="292" t="n"/>
@@ -10194,7 +10194,7 @@
     </row>
     <row r="56" ht="4.5" customHeight="1" s="236"/>
     <row r="57" ht="14.25" customHeight="1" s="236">
-      <c r="H57" s="367" t="n"/>
+      <c r="H57" s="368" t="n"/>
       <c r="I57" s="292" t="n"/>
       <c r="J57" s="292" t="n"/>
       <c r="K57" s="292" t="n"/>
@@ -10210,8 +10210,8 @@
     <mergeCell ref="W27:Z27"/>
     <mergeCell ref="W17:Z17"/>
     <mergeCell ref="O33:V33"/>
+    <mergeCell ref="H52:P52"/>
     <mergeCell ref="W11:Z11"/>
-    <mergeCell ref="H52:P52"/>
     <mergeCell ref="W33:AD33"/>
     <mergeCell ref="W29:Z29"/>
     <mergeCell ref="W23:Z23"/>
@@ -10228,8 +10228,8 @@
     <mergeCell ref="B2:AD2"/>
     <mergeCell ref="R10:U10"/>
     <mergeCell ref="W24:Z24"/>
+    <mergeCell ref="B38:C38"/>
     <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B38:C38"/>
     <mergeCell ref="R16:U16"/>
     <mergeCell ref="W30:Z30"/>
     <mergeCell ref="W26:Z26"/>

--- a/estattis_automação.xlsx
+++ b/estattis_automação.xlsx
@@ -1387,9 +1387,6 @@
     <xf numFmtId="0" fontId="41" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="41" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="41" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1600,6 +1597,9 @@
     <xf numFmtId="168" fontId="40" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="2" fontId="41" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="40" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="43" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1612,34 +1612,34 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="34" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="167" fontId="34" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="41" fillId="6" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="40" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="6" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="33" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="32" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="33" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="27" fillId="3" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
       <protection locked="0" hidden="0"/>
     </xf>
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="22" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1759,13 +1759,13 @@
     <xf numFmtId="167" fontId="37" fillId="3" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="37" fillId="3" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="37" fillId="3" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="37" fillId="3" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="3" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="38" fillId="3" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1866,11 +1866,11 @@
     <xf numFmtId="168" fontId="7" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="34" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -3051,8 +3051,8 @@
       <c r="H22" s="251" t="n"/>
       <c r="I22" s="251" t="n"/>
       <c r="J22" s="251" t="n"/>
-      <c r="K22" s="162" t="n"/>
-      <c r="L22" s="260" t="n"/>
+      <c r="K22" s="161" t="n"/>
+      <c r="L22" s="261" t="n"/>
       <c r="M22" s="253" t="n"/>
     </row>
     <row r="23" ht="20.25" customHeight="1" s="236">
@@ -3104,14 +3104,14 @@
       <c r="M24" s="244" t="n"/>
     </row>
     <row r="25" ht="17.25" customHeight="1" s="236">
-      <c r="B25" s="262" t="n"/>
+      <c r="B25" s="260" t="n"/>
       <c r="C25" s="238" t="n"/>
       <c r="D25" s="239" t="n"/>
       <c r="E25" s="254" t="n"/>
       <c r="H25" s="270" t="n"/>
       <c r="I25" s="238" t="n"/>
       <c r="J25" s="239" t="n"/>
-      <c r="K25" s="261" t="n"/>
+      <c r="K25" s="262" t="n"/>
       <c r="L25" s="238" t="n"/>
       <c r="M25" s="239" t="n"/>
     </row>
@@ -3448,6 +3448,7 @@
     <mergeCell ref="B11:D11"/>
     <mergeCell ref="E19:M19"/>
     <mergeCell ref="E10:M10"/>
+    <mergeCell ref="B37:E37"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="B23:M23"/>
     <mergeCell ref="F37:I37"/>
@@ -3462,23 +3463,23 @@
     <mergeCell ref="B9:D9"/>
     <mergeCell ref="E26:G26"/>
     <mergeCell ref="J38:M38"/>
-    <mergeCell ref="E25:G25"/>
     <mergeCell ref="B3:M4"/>
+    <mergeCell ref="B24:D24"/>
     <mergeCell ref="B20:D20"/>
     <mergeCell ref="J37:M37"/>
-    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="E25:G25"/>
     <mergeCell ref="E20:M20"/>
     <mergeCell ref="E7:M7"/>
     <mergeCell ref="H24:J24"/>
     <mergeCell ref="E22:J22"/>
     <mergeCell ref="B26:D26"/>
+    <mergeCell ref="H26:J26"/>
     <mergeCell ref="E21:M21"/>
+    <mergeCell ref="B25:D25"/>
     <mergeCell ref="B7:D7"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="E12:M12"/>
     <mergeCell ref="L22:M22"/>
     <mergeCell ref="K25:M25"/>
-    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="E12:M12"/>
     <mergeCell ref="F36:I36"/>
     <mergeCell ref="E24:G24"/>
     <mergeCell ref="K24:M24"/>
@@ -3487,13 +3488,12 @@
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="J35:M35"/>
     <mergeCell ref="B38:E38"/>
-    <mergeCell ref="K26:M26"/>
     <mergeCell ref="F38:I38"/>
     <mergeCell ref="B21:D21"/>
+    <mergeCell ref="B27:M27"/>
+    <mergeCell ref="K26:M26"/>
+    <mergeCell ref="B12:D12"/>
     <mergeCell ref="E8:M8"/>
-    <mergeCell ref="B37:E37"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="B27:M27"/>
     <mergeCell ref="H25:J25"/>
     <mergeCell ref="B39:M39"/>
   </mergeCells>
@@ -3518,8 +3518,8 @@
     <col width="15.7109375" customWidth="1" style="400" min="6" max="6"/>
     <col width="10.140625" customWidth="1" style="400" min="7" max="7"/>
     <col width="14.28515625" customWidth="1" style="400" min="8" max="8"/>
-    <col width="9.140625" customWidth="1" style="400" min="9" max="76"/>
-    <col width="9.140625" customWidth="1" style="400" min="77" max="16384"/>
+    <col width="9.140625" customWidth="1" style="400" min="9" max="82"/>
+    <col width="9.140625" customWidth="1" style="400" min="83" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="17.1" customHeight="1" s="236">
@@ -3614,7 +3614,7 @@
       <c r="D7" s="391" t="n"/>
       <c r="E7" s="253" t="n"/>
       <c r="F7" s="253" t="n"/>
-      <c r="G7" s="164" t="inlineStr">
+      <c r="G7" s="163" t="inlineStr">
         <is>
           <t>UNITÁRIO</t>
         </is>
@@ -3705,7 +3705,7 @@
       <c r="D12" s="391" t="n"/>
       <c r="E12" s="253" t="n"/>
       <c r="F12" s="253" t="n"/>
-      <c r="G12" s="164" t="inlineStr">
+      <c r="G12" s="163" t="inlineStr">
         <is>
           <t>UNITÁRIO</t>
         </is>
@@ -3891,7 +3891,7 @@
       <c r="D22" s="391" t="n"/>
       <c r="E22" s="253" t="n"/>
       <c r="F22" s="253" t="n"/>
-      <c r="G22" s="164" t="inlineStr">
+      <c r="G22" s="163" t="inlineStr">
         <is>
           <t>UNITÁRIO</t>
         </is>
@@ -3941,9 +3941,9 @@
     <mergeCell ref="B9:G9"/>
     <mergeCell ref="C21:C22"/>
     <mergeCell ref="D16:D17"/>
-    <mergeCell ref="C11:C12"/>
     <mergeCell ref="E6:E7"/>
     <mergeCell ref="G6:H6"/>
+    <mergeCell ref="C11:C12"/>
     <mergeCell ref="E11:E12"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="B24:G24"/>
@@ -3983,8 +3983,8 @@
     <col width="8.85546875" customWidth="1" style="24" min="5" max="5"/>
     <col width="10.140625" customWidth="1" style="24" min="6" max="6"/>
     <col width="12.7109375" customWidth="1" style="24" min="7" max="7"/>
-    <col width="9.140625" customWidth="1" style="24" min="8" max="75"/>
-    <col width="9.140625" customWidth="1" style="24" min="76" max="16384"/>
+    <col width="9.140625" customWidth="1" style="24" min="8" max="81"/>
+    <col width="9.140625" customWidth="1" style="24" min="82" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="17.1" customFormat="1" customHeight="1" s="400">
@@ -4450,166 +4450,166 @@
     <col width="9.140625" customWidth="1" style="272" min="1" max="3"/>
     <col width="29.85546875" customWidth="1" style="272" min="4" max="4"/>
     <col width="16.5703125" customWidth="1" style="272" min="5" max="5"/>
-    <col width="9.140625" customWidth="1" style="272" min="6" max="73"/>
-    <col width="9.140625" customWidth="1" style="272" min="74" max="16384"/>
+    <col width="9.140625" customWidth="1" style="272" min="6" max="79"/>
+    <col width="9.140625" customWidth="1" style="272" min="80" max="16384"/>
   </cols>
   <sheetData>
     <row r="8" ht="13.5" customHeight="1" s="236" thickBot="1"/>
     <row r="9" ht="15.75" customHeight="1" s="236" thickBot="1">
-      <c r="D9" s="118" t="inlineStr">
+      <c r="D9" s="117" t="inlineStr">
         <is>
           <t>HIDROGRAFIA</t>
         </is>
       </c>
-      <c r="E9" s="119" t="inlineStr">
+      <c r="E9" s="118" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" s="236">
-      <c r="D10" s="113" t="inlineStr">
+      <c r="D10" s="112" t="inlineStr">
         <is>
           <t>1,30 a 1,50 - (MUITO BOM)</t>
         </is>
       </c>
-      <c r="E10" s="165" t="n">
+      <c r="E10" s="164" t="n">
         <v>1.2</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" s="236">
-      <c r="D11" s="113" t="inlineStr">
+      <c r="D11" s="112" t="inlineStr">
         <is>
           <t>1,15 a 1,29 - (BOM)</t>
         </is>
       </c>
-      <c r="E11" s="165" t="n">
+      <c r="E11" s="164" t="n">
         <v>1.1</v>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" s="236">
-      <c r="D12" s="113" t="inlineStr">
+      <c r="D12" s="112" t="inlineStr">
         <is>
           <t>1,01 a 1,14 - (NORMAL)</t>
         </is>
       </c>
-      <c r="E12" s="165" t="n">
+      <c r="E12" s="164" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="236">
-      <c r="D13" s="114" t="inlineStr">
+      <c r="D13" s="113" t="inlineStr">
         <is>
           <t>1,00 - (REGULAR)</t>
         </is>
       </c>
-      <c r="E13" s="165" t="n">
+      <c r="E13" s="164" t="n">
         <v>0.9</v>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1" s="236">
-      <c r="D14" s="113" t="inlineStr">
+      <c r="D14" s="112" t="inlineStr">
         <is>
           <t>0,80 a 0,99 - (RUIM)</t>
         </is>
       </c>
-      <c r="E14" s="165" t="n">
+      <c r="E14" s="164" t="n">
         <v>0.8</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1" s="236" thickBot="1">
-      <c r="D15" s="115" t="inlineStr">
+      <c r="D15" s="114" t="inlineStr">
         <is>
           <t>0,50 a 0,79 - (MUITO RUIM)</t>
         </is>
       </c>
-      <c r="E15" s="166" t="n">
+      <c r="E15" s="165" t="n">
         <v>0.7</v>
       </c>
     </row>
     <row r="17">
-      <c r="D17" s="116" t="inlineStr">
+      <c r="D17" s="115" t="inlineStr">
         <is>
           <t>FONTE: DESLANDES, CRISTIANO AUGUSTO - AVALIAÇÃO DE IMÓVEIS RURAIS (2002).</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="D18" s="116" t="inlineStr">
+      <c r="D18" s="115" t="inlineStr">
         <is>
           <t>FONTE: GLOSSÁRIO INTERNACIONAL DE HIDROLOGIA (UNESCO).</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1" s="236">
-      <c r="D21" s="117" t="inlineStr">
+      <c r="D21" s="116" t="inlineStr">
         <is>
           <t>BENFEITORIAS</t>
         </is>
       </c>
-      <c r="E21" s="117" t="inlineStr">
+      <c r="E21" s="116" t="inlineStr">
         <is>
           <t>Fatores</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1" s="236">
-      <c r="D22" s="112" t="inlineStr">
+      <c r="D22" s="111" t="inlineStr">
         <is>
           <t>MUITO ACIMA DA MÉDIA</t>
         </is>
       </c>
-      <c r="E22" s="167" t="n">
+      <c r="E22" s="166" t="n">
         <v>1.2</v>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1" s="236">
-      <c r="D23" s="112" t="inlineStr">
+      <c r="D23" s="111" t="inlineStr">
         <is>
           <t>ACIMA DA MÉDIA</t>
         </is>
       </c>
-      <c r="E23" s="167" t="n">
+      <c r="E23" s="166" t="n">
         <v>1.1</v>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1" s="236">
-      <c r="D24" s="112" t="inlineStr">
+      <c r="D24" s="111" t="inlineStr">
         <is>
           <t>MÉDIA</t>
         </is>
       </c>
-      <c r="E24" s="167" t="n">
+      <c r="E24" s="166" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1" s="236">
-      <c r="D25" s="112" t="inlineStr">
+      <c r="D25" s="111" t="inlineStr">
         <is>
           <t>ABAIXO DA MÉDIA</t>
         </is>
       </c>
-      <c r="E25" s="167" t="n">
+      <c r="E25" s="166" t="n">
         <v>0.9</v>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1" s="236">
-      <c r="D26" s="112" t="inlineStr">
+      <c r="D26" s="111" t="inlineStr">
         <is>
           <t>MUITO ABAIXO DA MÉDIA</t>
         </is>
       </c>
-      <c r="E26" s="167" t="n">
+      <c r="E26" s="166" t="n">
         <v>0.8</v>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1" s="236">
-      <c r="D27" s="112" t="inlineStr">
+      <c r="D27" s="111" t="inlineStr">
         <is>
           <t>SEM BENFEITORIA</t>
         </is>
       </c>
-      <c r="E27" s="167" t="n">
+      <c r="E27" s="166" t="n">
         <v>0.7</v>
       </c>
     </row>
@@ -4619,144 +4619,144 @@
           <t>Situação</t>
         </is>
       </c>
-      <c r="E32" s="135" t="inlineStr">
+      <c r="E32" s="134" t="inlineStr">
         <is>
           <t>CARACTERÍSTICA</t>
         </is>
       </c>
-      <c r="F32" s="135" t="n"/>
-      <c r="G32" s="135" t="n"/>
+      <c r="F32" s="134" t="n"/>
+      <c r="G32" s="134" t="n"/>
     </row>
     <row r="33" ht="30" customHeight="1" s="236">
-      <c r="E33" s="136" t="inlineStr">
+      <c r="E33" s="135" t="inlineStr">
         <is>
           <t>Tipo de Estrada</t>
         </is>
       </c>
-      <c r="F33" s="136" t="inlineStr">
+      <c r="F33" s="135" t="inlineStr">
         <is>
           <t>Trafegabilidade</t>
         </is>
       </c>
-      <c r="G33" s="136" t="inlineStr">
+      <c r="G33" s="135" t="inlineStr">
         <is>
           <t>Fatores</t>
         </is>
       </c>
     </row>
     <row r="34" ht="45" customHeight="1" s="236">
-      <c r="D34" s="137" t="inlineStr">
+      <c r="D34" s="136" t="inlineStr">
         <is>
           <t>Ótima</t>
         </is>
       </c>
-      <c r="E34" s="137" t="inlineStr">
+      <c r="E34" s="136" t="inlineStr">
         <is>
           <t>Pavimentada com asfalto/concreto</t>
         </is>
       </c>
-      <c r="F34" s="137" t="inlineStr">
+      <c r="F34" s="136" t="inlineStr">
         <is>
           <t>Permanente</t>
         </is>
       </c>
-      <c r="G34" s="138" t="n">
+      <c r="G34" s="137" t="n">
         <v>1.2</v>
       </c>
     </row>
     <row r="35" ht="60" customHeight="1" s="236">
-      <c r="D35" s="137" t="inlineStr">
+      <c r="D35" s="136" t="inlineStr">
         <is>
           <t>Muito Boa</t>
         </is>
       </c>
-      <c r="E35" s="137" t="inlineStr">
+      <c r="E35" s="136" t="inlineStr">
         <is>
           <t>Pavimentada com cascalhamento/intertravado</t>
         </is>
       </c>
-      <c r="F35" s="137" t="inlineStr">
+      <c r="F35" s="136" t="inlineStr">
         <is>
           <t>Permanente</t>
         </is>
       </c>
-      <c r="G35" s="138" t="n">
+      <c r="G35" s="137" t="n">
         <v>1.1</v>
       </c>
     </row>
     <row r="36" ht="30" customHeight="1" s="236">
-      <c r="D36" s="137" t="inlineStr">
+      <c r="D36" s="136" t="inlineStr">
         <is>
           <t>Boa</t>
         </is>
       </c>
-      <c r="E36" s="137" t="inlineStr">
+      <c r="E36" s="136" t="inlineStr">
         <is>
           <t>Não Pavimentada</t>
         </is>
       </c>
-      <c r="F36" s="137" t="inlineStr">
+      <c r="F36" s="136" t="inlineStr">
         <is>
           <t>Permanente</t>
         </is>
       </c>
-      <c r="G36" s="138" t="n">
+      <c r="G36" s="137" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="37" ht="75" customHeight="1" s="236">
-      <c r="D37" s="137" t="inlineStr">
+      <c r="D37" s="136" t="inlineStr">
         <is>
           <t>Desfavorável</t>
         </is>
       </c>
-      <c r="E37" s="137" t="inlineStr">
+      <c r="E37" s="136" t="inlineStr">
         <is>
           <t>Não Pavimentada e Servidões de Passagem</t>
         </is>
       </c>
-      <c r="F37" s="137" t="inlineStr">
+      <c r="F37" s="136" t="inlineStr">
         <is>
           <t>Problemas sérios nas Estações chuvosas</t>
         </is>
       </c>
-      <c r="G37" s="138" t="n">
+      <c r="G37" s="137" t="n">
         <v>0.9</v>
       </c>
     </row>
     <row r="38" ht="45" customHeight="1" s="236">
-      <c r="D38" s="137" t="inlineStr">
+      <c r="D38" s="136" t="inlineStr">
         <is>
           <t>Má</t>
         </is>
       </c>
-      <c r="E38" s="137" t="inlineStr">
+      <c r="E38" s="136" t="inlineStr">
         <is>
           <t>Servidões com a presença de fechos</t>
         </is>
       </c>
-      <c r="F38" s="137" t="n"/>
-      <c r="G38" s="138" t="n">
+      <c r="F38" s="136" t="n"/>
+      <c r="G38" s="137" t="n">
         <v>0.8</v>
       </c>
     </row>
     <row r="39" ht="60" customHeight="1" s="236">
-      <c r="D39" s="137" t="inlineStr">
+      <c r="D39" s="136" t="inlineStr">
         <is>
           <t>Péssima</t>
         </is>
       </c>
-      <c r="E39" s="137" t="inlineStr">
+      <c r="E39" s="136" t="inlineStr">
         <is>
           <t>Fechos e interceptados por córregos sem pontes</t>
         </is>
       </c>
-      <c r="F39" s="137" t="inlineStr">
+      <c r="F39" s="136" t="inlineStr">
         <is>
           <t>Problemas sérios mesmo nas secas</t>
         </is>
       </c>
-      <c r="G39" s="138" t="n">
+      <c r="G39" s="137" t="n">
         <v>0.7</v>
       </c>
     </row>
@@ -4791,39 +4791,39 @@
     <col width="8.28515625" bestFit="1" customWidth="1" style="272" min="7" max="7"/>
     <col width="9.140625" customWidth="1" style="272" min="8" max="9"/>
     <col width="14.42578125" customWidth="1" style="272" min="10" max="10"/>
-    <col width="9.140625" customWidth="1" style="272" min="11" max="78"/>
-    <col width="9.140625" customWidth="1" style="272" min="79" max="16384"/>
+    <col width="9.140625" customWidth="1" style="272" min="11" max="84"/>
+    <col width="9.140625" customWidth="1" style="272" min="85" max="16384"/>
   </cols>
   <sheetData>
     <row r="2">
-      <c r="L2" s="142" t="n"/>
-      <c r="M2" s="142" t="n"/>
-      <c r="N2" s="142" t="n"/>
-      <c r="O2" s="142" t="n"/>
-      <c r="P2" s="142" t="n"/>
-      <c r="Q2" s="142" t="n"/>
-      <c r="R2" s="142" t="n"/>
-      <c r="S2" s="142" t="n"/>
-      <c r="T2" s="142" t="n"/>
+      <c r="L2" s="141" t="n"/>
+      <c r="M2" s="141" t="n"/>
+      <c r="N2" s="141" t="n"/>
+      <c r="O2" s="141" t="n"/>
+      <c r="P2" s="141" t="n"/>
+      <c r="Q2" s="141" t="n"/>
+      <c r="R2" s="141" t="n"/>
+      <c r="S2" s="141" t="n"/>
+      <c r="T2" s="141" t="n"/>
     </row>
     <row r="3">
-      <c r="L3" s="142" t="n"/>
-      <c r="M3" s="142" t="n"/>
-      <c r="N3" s="142" t="n"/>
-      <c r="O3" s="142" t="inlineStr">
+      <c r="L3" s="141" t="n"/>
+      <c r="M3" s="141" t="n"/>
+      <c r="N3" s="141" t="n"/>
+      <c r="O3" s="141" t="inlineStr">
         <is>
           <t>APP</t>
         </is>
       </c>
-      <c r="P3" s="142" t="inlineStr">
+      <c r="P3" s="141" t="inlineStr">
         <is>
           <t>ARL</t>
         </is>
       </c>
-      <c r="Q3" s="142" t="n"/>
-      <c r="R3" s="142" t="n"/>
-      <c r="S3" s="142" t="n"/>
-      <c r="T3" s="142" t="n"/>
+      <c r="Q3" s="141" t="n"/>
+      <c r="R3" s="141" t="n"/>
+      <c r="S3" s="141" t="n"/>
+      <c r="T3" s="141" t="n"/>
     </row>
     <row r="4">
       <c r="C4" s="281" t="inlineStr">
@@ -4831,22 +4831,22 @@
           <t>MATRÍCULA 5.723</t>
         </is>
       </c>
-      <c r="L4" s="142" t="n"/>
-      <c r="M4" s="142" t="n"/>
-      <c r="N4" s="142" t="n"/>
-      <c r="O4" s="143" t="n">
+      <c r="L4" s="141" t="n"/>
+      <c r="M4" s="141" t="n"/>
+      <c r="N4" s="141" t="n"/>
+      <c r="O4" s="142" t="n">
         <v>13.6783</v>
       </c>
-      <c r="P4" s="143" t="n">
+      <c r="P4" s="142" t="n">
         <v>141.8504</v>
       </c>
-      <c r="Q4" s="142">
+      <c r="Q4" s="141">
         <f>P4+O4</f>
         <v/>
       </c>
-      <c r="R4" s="142" t="n"/>
-      <c r="S4" s="142" t="n"/>
-      <c r="T4" s="142" t="n"/>
+      <c r="R4" s="141" t="n"/>
+      <c r="S4" s="141" t="n"/>
+      <c r="T4" s="141" t="n"/>
     </row>
     <row r="5">
       <c r="C5" s="278" t="inlineStr">
@@ -4873,19 +4873,19 @@
         </is>
       </c>
       <c r="J5" s="253" t="n"/>
-      <c r="L5" s="142" t="n"/>
-      <c r="M5" s="142" t="n"/>
-      <c r="N5" s="142" t="inlineStr">
+      <c r="L5" s="141" t="n"/>
+      <c r="M5" s="141" t="n"/>
+      <c r="N5" s="141" t="inlineStr">
         <is>
           <t>AU</t>
         </is>
       </c>
-      <c r="O5" s="142" t="n"/>
-      <c r="P5" s="142" t="n"/>
-      <c r="Q5" s="142" t="n"/>
-      <c r="R5" s="142" t="n"/>
-      <c r="S5" s="142" t="n"/>
-      <c r="T5" s="142" t="n"/>
+      <c r="O5" s="141" t="n"/>
+      <c r="P5" s="141" t="n"/>
+      <c r="Q5" s="141" t="n"/>
+      <c r="R5" s="141" t="n"/>
+      <c r="S5" s="141" t="n"/>
+      <c r="T5" s="141" t="n"/>
     </row>
     <row r="6">
       <c r="C6" s="274">
@@ -4911,23 +4911,23 @@
         </is>
       </c>
       <c r="J6" s="244" t="n"/>
-      <c r="L6" s="142" t="n">
+      <c r="L6" s="141" t="n">
         <v>231.63</v>
       </c>
-      <c r="M6" s="142" t="n"/>
-      <c r="N6" s="142">
+      <c r="M6" s="141" t="n"/>
+      <c r="N6" s="141">
         <f>L6+7.12</f>
         <v/>
       </c>
-      <c r="O6" s="142" t="n"/>
-      <c r="P6" s="142" t="n"/>
-      <c r="Q6" s="142" t="n"/>
-      <c r="R6" s="142">
+      <c r="O6" s="141" t="n"/>
+      <c r="P6" s="141" t="n"/>
+      <c r="Q6" s="141" t="n"/>
+      <c r="R6" s="141">
         <f>P4+O4+N6</f>
         <v/>
       </c>
-      <c r="S6" s="142" t="n"/>
-      <c r="T6" s="142" t="n"/>
+      <c r="S6" s="141" t="n"/>
+      <c r="T6" s="141" t="n"/>
     </row>
     <row r="7">
       <c r="C7" s="282" t="inlineStr">
@@ -4942,22 +4942,22 @@
       <c r="H7" s="243" t="n"/>
       <c r="I7" s="243" t="n"/>
       <c r="J7" s="244" t="n"/>
-      <c r="L7" s="142" t="n"/>
-      <c r="M7" s="142" t="n"/>
-      <c r="N7" s="142" t="n"/>
-      <c r="O7" s="142" t="n"/>
-      <c r="P7" s="142" t="n"/>
-      <c r="Q7" s="142" t="n"/>
-      <c r="R7" s="142">
+      <c r="L7" s="141" t="n"/>
+      <c r="M7" s="141" t="n"/>
+      <c r="N7" s="141" t="n"/>
+      <c r="O7" s="141" t="n"/>
+      <c r="P7" s="141" t="n"/>
+      <c r="Q7" s="141" t="n"/>
+      <c r="R7" s="141">
         <f>C6-R6</f>
         <v/>
       </c>
-      <c r="S7" s="142" t="inlineStr">
+      <c r="S7" s="141" t="inlineStr">
         <is>
           <t>AR</t>
         </is>
       </c>
-      <c r="T7" s="142" t="n"/>
+      <c r="T7" s="141" t="n"/>
     </row>
     <row r="8">
       <c r="C8" s="277" t="inlineStr">
@@ -4984,15 +4984,15 @@
         </is>
       </c>
       <c r="J8" s="244" t="n"/>
-      <c r="L8" s="142" t="n"/>
-      <c r="M8" s="142" t="n"/>
-      <c r="N8" s="142" t="n"/>
-      <c r="O8" s="142" t="n"/>
-      <c r="P8" s="142" t="n"/>
-      <c r="Q8" s="142" t="n"/>
-      <c r="R8" s="142" t="n"/>
-      <c r="S8" s="142" t="n"/>
-      <c r="T8" s="142" t="n"/>
+      <c r="L8" s="141" t="n"/>
+      <c r="M8" s="141" t="n"/>
+      <c r="N8" s="141" t="n"/>
+      <c r="O8" s="141" t="n"/>
+      <c r="P8" s="141" t="n"/>
+      <c r="Q8" s="141" t="n"/>
+      <c r="R8" s="141" t="n"/>
+      <c r="S8" s="141" t="n"/>
+      <c r="T8" s="141" t="n"/>
     </row>
     <row r="9">
       <c r="C9" s="273" t="n">
@@ -5013,15 +5013,15 @@
         <v>4.84</v>
       </c>
       <c r="J9" s="244" t="n"/>
-      <c r="L9" s="142" t="n"/>
-      <c r="M9" s="142" t="n"/>
-      <c r="N9" s="142" t="n"/>
-      <c r="O9" s="142" t="n"/>
-      <c r="P9" s="142" t="n"/>
-      <c r="Q9" s="142" t="n"/>
-      <c r="R9" s="142" t="n"/>
-      <c r="S9" s="142" t="n"/>
-      <c r="T9" s="142" t="n"/>
+      <c r="L9" s="141" t="n"/>
+      <c r="M9" s="141" t="n"/>
+      <c r="N9" s="141" t="n"/>
+      <c r="O9" s="141" t="n"/>
+      <c r="P9" s="141" t="n"/>
+      <c r="Q9" s="141" t="n"/>
+      <c r="R9" s="141" t="n"/>
+      <c r="S9" s="141" t="n"/>
+      <c r="T9" s="141" t="n"/>
     </row>
     <row r="10">
       <c r="C10" s="282" t="inlineStr">
@@ -5036,15 +5036,15 @@
       <c r="H10" s="243" t="n"/>
       <c r="I10" s="243" t="n"/>
       <c r="J10" s="244" t="n"/>
-      <c r="L10" s="142" t="n"/>
-      <c r="M10" s="142" t="n"/>
-      <c r="N10" s="142" t="n"/>
-      <c r="O10" s="142" t="n"/>
-      <c r="P10" s="142" t="n"/>
-      <c r="Q10" s="142" t="n"/>
-      <c r="R10" s="142" t="n"/>
-      <c r="S10" s="142" t="n"/>
-      <c r="T10" s="142" t="n"/>
+      <c r="L10" s="141" t="n"/>
+      <c r="M10" s="141" t="n"/>
+      <c r="N10" s="141" t="n"/>
+      <c r="O10" s="141" t="n"/>
+      <c r="P10" s="141" t="n"/>
+      <c r="Q10" s="141" t="n"/>
+      <c r="R10" s="141" t="n"/>
+      <c r="S10" s="141" t="n"/>
+      <c r="T10" s="141" t="n"/>
     </row>
     <row r="11">
       <c r="C11" s="277" t="inlineStr">
@@ -5207,7 +5207,7 @@
         <v/>
       </c>
       <c r="I20" s="244" t="n"/>
-      <c r="J20" s="140" t="n"/>
+      <c r="J20" s="139" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="44">
@@ -5281,8 +5281,8 @@
     <col width="9.140625" customWidth="1" style="272" min="12" max="12"/>
     <col width="14.28515625" customWidth="1" style="272" min="13" max="13"/>
     <col width="14.42578125" customWidth="1" style="272" min="14" max="14"/>
-    <col width="9.140625" customWidth="1" style="272" min="15" max="82"/>
-    <col width="9.140625" customWidth="1" style="272" min="83" max="16384"/>
+    <col width="9.140625" customWidth="1" style="272" min="15" max="88"/>
+    <col width="9.140625" customWidth="1" style="272" min="89" max="16384"/>
   </cols>
   <sheetData>
     <row r="3" ht="15" customHeight="1" s="236">
@@ -5306,7 +5306,7 @@
       <c r="M3" s="244" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1" s="236">
-      <c r="B4" s="149" t="n"/>
+      <c r="B4" s="148" t="n"/>
       <c r="C4" s="312" t="inlineStr">
         <is>
           <t>Proprietário(s):</t>
@@ -5329,13 +5329,13 @@
         </is>
       </c>
       <c r="I4" s="241" t="n"/>
-      <c r="J4" s="131" t="n"/>
-      <c r="L4" s="112" t="inlineStr">
+      <c r="J4" s="130" t="n"/>
+      <c r="L4" s="111" t="inlineStr">
         <is>
           <t>R$/ ha =</t>
         </is>
       </c>
-      <c r="M4" s="168">
+      <c r="M4" s="167">
         <f>SUM(H19+H32+H45+H58+H71+H84)/6</f>
         <v/>
       </c>
@@ -5362,12 +5362,12 @@
         </is>
       </c>
       <c r="I5" s="241" t="n"/>
-      <c r="L5" s="112" t="inlineStr">
+      <c r="L5" s="111" t="inlineStr">
         <is>
           <t>Alq =</t>
         </is>
       </c>
-      <c r="M5" s="168">
+      <c r="M5" s="167">
         <f>M4*4.84</f>
         <v/>
       </c>
@@ -5394,7 +5394,7 @@
       <c r="I6" s="241" t="n"/>
     </row>
     <row r="7" ht="15" customHeight="1" s="236">
-      <c r="B7" s="120" t="n"/>
+      <c r="B7" s="119" t="n"/>
       <c r="C7" s="299" t="inlineStr">
         <is>
           <t>Hidrografia:</t>
@@ -5417,7 +5417,7 @@
       <c r="I7" s="241" t="n"/>
     </row>
     <row r="8" ht="15" customHeight="1" s="236">
-      <c r="B8" s="120" t="n"/>
+      <c r="B8" s="119" t="n"/>
       <c r="C8" s="299" t="inlineStr">
         <is>
           <t>Matrícula:</t>
@@ -5433,11 +5433,11 @@
       </c>
       <c r="H8" s="328" t="n"/>
       <c r="I8" s="241" t="n"/>
-      <c r="J8" s="147" t="n"/>
-      <c r="K8" s="147" t="n"/>
-      <c r="L8" s="147" t="n"/>
-      <c r="M8" s="147" t="n"/>
-      <c r="N8" s="147" t="n"/>
+      <c r="J8" s="146" t="n"/>
+      <c r="K8" s="146" t="n"/>
+      <c r="L8" s="146" t="n"/>
+      <c r="M8" s="146" t="n"/>
+      <c r="N8" s="146" t="n"/>
     </row>
     <row r="9" ht="15" customHeight="1" s="236">
       <c r="B9" s="302" t="inlineStr">
@@ -5446,11 +5446,11 @@
         </is>
       </c>
       <c r="I9" s="241" t="n"/>
-      <c r="J9" s="147" t="n"/>
-      <c r="K9" s="147" t="n"/>
-      <c r="L9" s="147" t="n"/>
-      <c r="M9" s="147" t="n"/>
-      <c r="N9" s="147" t="n"/>
+      <c r="J9" s="146" t="n"/>
+      <c r="K9" s="146" t="n"/>
+      <c r="L9" s="146" t="n"/>
+      <c r="M9" s="146" t="n"/>
+      <c r="N9" s="146" t="n"/>
     </row>
     <row r="10" ht="15" customHeight="1" s="236">
       <c r="B10" s="307" t="inlineStr">
@@ -5458,53 +5458,53 @@
           <t>Classe de Solo</t>
         </is>
       </c>
-      <c r="E10" s="296" t="inlineStr">
+      <c r="E10" s="297" t="inlineStr">
         <is>
           <t>Área (ha)</t>
         </is>
       </c>
-      <c r="F10" s="296" t="inlineStr">
+      <c r="F10" s="297" t="inlineStr">
         <is>
           <t>% do Imóvel</t>
         </is>
       </c>
-      <c r="G10" s="296" t="inlineStr">
+      <c r="G10" s="297" t="inlineStr">
         <is>
           <t>Nota Agronômica</t>
         </is>
       </c>
-      <c r="I10" s="121" t="n"/>
-      <c r="J10" s="147" t="n"/>
-      <c r="K10" s="147" t="n"/>
-      <c r="L10" s="147" t="n"/>
-      <c r="M10" s="147" t="n"/>
-      <c r="N10" s="147" t="n"/>
+      <c r="I10" s="120" t="n"/>
+      <c r="J10" s="146" t="n"/>
+      <c r="K10" s="146" t="n"/>
+      <c r="L10" s="146" t="n"/>
+      <c r="M10" s="146" t="n"/>
+      <c r="N10" s="146" t="n"/>
     </row>
     <row r="11" ht="15" customHeight="1" s="236">
-      <c r="B11" s="159" t="n"/>
-      <c r="C11" s="161" t="inlineStr">
+      <c r="B11" s="158" t="n"/>
+      <c r="C11" s="160" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
-      <c r="D11" s="160" t="n"/>
-      <c r="E11" s="169">
+      <c r="D11" s="159" t="n"/>
+      <c r="E11" s="168">
         <f>E6-E12</f>
         <v/>
       </c>
-      <c r="F11" s="122">
+      <c r="F11" s="121">
         <f>E11/E6</f>
         <v/>
       </c>
       <c r="G11" s="309" t="n">
         <v>0.9</v>
       </c>
-      <c r="I11" s="121" t="n"/>
-      <c r="J11" s="147" t="n"/>
-      <c r="K11" s="170" t="n"/>
-      <c r="L11" s="147" t="n"/>
-      <c r="M11" s="147" t="n"/>
-      <c r="N11" s="147" t="n"/>
+      <c r="I11" s="120" t="n"/>
+      <c r="J11" s="146" t="n"/>
+      <c r="K11" s="169" t="n"/>
+      <c r="L11" s="146" t="n"/>
+      <c r="M11" s="146" t="n"/>
+      <c r="N11" s="146" t="n"/>
     </row>
     <row r="12" ht="15" customHeight="1" s="236">
       <c r="B12" s="323" t="inlineStr">
@@ -5512,22 +5512,22 @@
           <t>VIII</t>
         </is>
       </c>
-      <c r="E12" s="171" t="n">
+      <c r="E12" s="170" t="n">
         <v>218.9</v>
       </c>
-      <c r="F12" s="122">
+      <c r="F12" s="121">
         <f>E12/E6</f>
         <v/>
       </c>
       <c r="G12" s="309" t="n">
         <v>0.6</v>
       </c>
-      <c r="I12" s="121" t="n"/>
-      <c r="J12" s="147" t="n"/>
-      <c r="K12" s="148" t="n"/>
-      <c r="L12" s="148" t="n"/>
-      <c r="M12" s="147" t="n"/>
-      <c r="N12" s="147" t="n"/>
+      <c r="I12" s="120" t="n"/>
+      <c r="J12" s="146" t="n"/>
+      <c r="K12" s="147" t="n"/>
+      <c r="L12" s="147" t="n"/>
+      <c r="M12" s="146" t="n"/>
+      <c r="N12" s="146" t="n"/>
     </row>
     <row r="13" ht="15" customHeight="1" s="236">
       <c r="B13" s="317" t="inlineStr">
@@ -5537,11 +5537,11 @@
       </c>
       <c r="C13" s="251" t="n"/>
       <c r="D13" s="251" t="n"/>
-      <c r="E13" s="172">
+      <c r="E13" s="171">
         <f>SUM(E11:E12)</f>
         <v/>
       </c>
-      <c r="F13" s="123">
+      <c r="F13" s="122">
         <f>SUM(F11:F12)</f>
         <v/>
       </c>
@@ -5550,27 +5550,27 @@
         <v/>
       </c>
       <c r="H13" s="251" t="n"/>
-      <c r="I13" s="124" t="n"/>
-      <c r="J13" s="173" t="n"/>
-      <c r="K13" s="170" t="n"/>
-      <c r="L13" s="147" t="n"/>
-      <c r="M13" s="147" t="n"/>
-      <c r="N13" s="147" t="n"/>
+      <c r="I13" s="123" t="n"/>
+      <c r="J13" s="172" t="n"/>
+      <c r="K13" s="169" t="n"/>
+      <c r="L13" s="146" t="n"/>
+      <c r="M13" s="146" t="n"/>
+      <c r="N13" s="146" t="n"/>
     </row>
     <row r="14" ht="15" customHeight="1" s="236">
-      <c r="B14" s="125" t="n"/>
-      <c r="C14" s="125" t="n"/>
-      <c r="D14" s="125" t="n"/>
-      <c r="E14" s="125" t="n"/>
-      <c r="F14" s="125" t="n"/>
-      <c r="G14" s="125" t="n"/>
-      <c r="H14" s="125" t="n"/>
-      <c r="I14" s="125" t="n"/>
-      <c r="J14" s="147" t="n"/>
-      <c r="K14" s="147" t="n"/>
-      <c r="L14" s="147" t="n"/>
-      <c r="M14" s="147" t="n"/>
-      <c r="N14" s="147" t="n"/>
+      <c r="B14" s="124" t="n"/>
+      <c r="C14" s="124" t="n"/>
+      <c r="D14" s="124" t="n"/>
+      <c r="E14" s="124" t="n"/>
+      <c r="F14" s="124" t="n"/>
+      <c r="G14" s="124" t="n"/>
+      <c r="H14" s="124" t="n"/>
+      <c r="I14" s="124" t="n"/>
+      <c r="J14" s="146" t="n"/>
+      <c r="K14" s="146" t="n"/>
+      <c r="L14" s="146" t="n"/>
+      <c r="M14" s="146" t="n"/>
+      <c r="N14" s="146" t="n"/>
     </row>
     <row r="15" ht="15" customHeight="1" s="236">
       <c r="B15" s="294" t="inlineStr">
@@ -5578,7 +5578,7 @@
           <t>Dado Amostral 01</t>
         </is>
       </c>
-      <c r="K15" s="139" t="n"/>
+      <c r="K15" s="138" t="n"/>
     </row>
     <row r="16" ht="15" customHeight="1" s="236">
       <c r="B16" s="291" t="inlineStr">
@@ -5598,13 +5598,13 @@
           <t>Contato:</t>
         </is>
       </c>
-      <c r="H16" s="297" t="inlineStr">
+      <c r="H16" s="296" t="inlineStr">
         <is>
           <t>(62) 4102-3282</t>
         </is>
       </c>
       <c r="I16" s="241" t="n"/>
-      <c r="K16" s="150" t="n"/>
+      <c r="K16" s="149" t="n"/>
     </row>
     <row r="17" ht="15" customHeight="1" s="236">
       <c r="B17" s="293" t="inlineStr">
@@ -5627,8 +5627,8 @@
           <t xml:space="preserve">Boa </t>
         </is>
       </c>
-      <c r="I17" s="297" t="n"/>
-      <c r="K17" s="151" t="n"/>
+      <c r="I17" s="296" t="n"/>
+      <c r="K17" s="150" t="n"/>
     </row>
     <row r="18" ht="15" customHeight="1" s="236">
       <c r="B18" s="293" t="inlineStr">
@@ -5651,10 +5651,10 @@
         </is>
       </c>
       <c r="I18" s="241" t="n"/>
-      <c r="K18" s="151" t="n"/>
+      <c r="K18" s="150" t="n"/>
     </row>
     <row r="19" ht="15" customHeight="1" s="236">
-      <c r="B19" s="152" t="n"/>
+      <c r="B19" s="151" t="n"/>
       <c r="C19" s="299" t="inlineStr">
         <is>
           <t>Valor venal:</t>
@@ -5673,13 +5673,13 @@
         <v/>
       </c>
       <c r="I19" s="241" t="n"/>
-      <c r="J19" s="174">
+      <c r="J19" s="173">
         <f>H19*4.84</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1" s="236">
-      <c r="B20" s="153" t="n"/>
+      <c r="B20" s="152" t="n"/>
       <c r="C20" s="299" t="inlineStr">
         <is>
           <t>Negociação:</t>
@@ -5699,10 +5699,10 @@
         <v>45566</v>
       </c>
       <c r="I20" s="241" t="n"/>
-      <c r="K20" s="158" t="n"/>
+      <c r="K20" s="157" t="n"/>
     </row>
     <row r="21" ht="15" customHeight="1" s="236">
-      <c r="B21" s="153" t="n"/>
+      <c r="B21" s="152" t="n"/>
       <c r="C21" s="299" t="inlineStr">
         <is>
           <t>Hidrografia:</t>
@@ -5718,7 +5718,7 @@
           <t>Outros:</t>
         </is>
       </c>
-      <c r="H21" s="297" t="n"/>
+      <c r="H21" s="296" t="n"/>
       <c r="I21" s="241" t="n"/>
     </row>
     <row r="22" ht="15" customHeight="1" s="236">
@@ -5735,22 +5735,22 @@
           <t>Classe de Solo</t>
         </is>
       </c>
-      <c r="E23" s="296" t="inlineStr">
+      <c r="E23" s="297" t="inlineStr">
         <is>
           <t>Área (ha)</t>
         </is>
       </c>
-      <c r="F23" s="296" t="inlineStr">
+      <c r="F23" s="297" t="inlineStr">
         <is>
           <t>% do Imóvel</t>
         </is>
       </c>
-      <c r="G23" s="296" t="inlineStr">
+      <c r="G23" s="297" t="inlineStr">
         <is>
           <t>Nota Agronômica</t>
         </is>
       </c>
-      <c r="I23" s="154" t="n"/>
+      <c r="I23" s="153" t="n"/>
     </row>
     <row r="24" ht="15" customHeight="1" s="236">
       <c r="B24" s="303" t="inlineStr">
@@ -5758,18 +5758,18 @@
           <t>IV</t>
         </is>
       </c>
-      <c r="E24" s="175">
+      <c r="E24" s="174">
         <f>E18*0.5</f>
         <v/>
       </c>
-      <c r="F24" s="155">
+      <c r="F24" s="154">
         <f>E24/E18</f>
         <v/>
       </c>
       <c r="G24" s="310" t="n">
         <v>1</v>
       </c>
-      <c r="I24" s="154" t="n"/>
+      <c r="I24" s="153" t="n"/>
     </row>
     <row r="25" ht="15" customHeight="1" s="236">
       <c r="B25" s="303" t="inlineStr">
@@ -5777,18 +5777,18 @@
           <t>VIII</t>
         </is>
       </c>
-      <c r="E25" s="176">
+      <c r="E25" s="175">
         <f>E18-E24</f>
         <v/>
       </c>
-      <c r="F25" s="155">
+      <c r="F25" s="154">
         <f>E25/E18</f>
         <v/>
       </c>
       <c r="G25" s="310" t="n">
         <v>0.6</v>
       </c>
-      <c r="I25" s="154" t="n"/>
+      <c r="I25" s="153" t="n"/>
     </row>
     <row r="26" ht="15" customHeight="1" s="236">
       <c r="B26" s="317" t="inlineStr">
@@ -5802,24 +5802,24 @@
         <f>SUM(E24:E25)</f>
         <v/>
       </c>
-      <c r="F26" s="123" t="n">
+      <c r="F26" s="122" t="n">
         <v>1</v>
       </c>
       <c r="G26" s="308" t="n">
         <v>0.7333333333333329</v>
       </c>
       <c r="H26" s="251" t="n"/>
-      <c r="I26" s="156" t="n"/>
+      <c r="I26" s="155" t="n"/>
     </row>
     <row r="27" ht="15" customHeight="1" s="236">
-      <c r="B27" s="157" t="n"/>
-      <c r="C27" s="157" t="n"/>
-      <c r="D27" s="157" t="n"/>
-      <c r="E27" s="157" t="n"/>
-      <c r="F27" s="157" t="n"/>
-      <c r="G27" s="157" t="n"/>
-      <c r="H27" s="157" t="n"/>
-      <c r="I27" s="157" t="n"/>
+      <c r="B27" s="156" t="n"/>
+      <c r="C27" s="156" t="n"/>
+      <c r="D27" s="156" t="n"/>
+      <c r="E27" s="156" t="n"/>
+      <c r="F27" s="156" t="n"/>
+      <c r="G27" s="156" t="n"/>
+      <c r="H27" s="156" t="n"/>
+      <c r="I27" s="156" t="n"/>
     </row>
     <row r="28" ht="15" customHeight="1" s="236">
       <c r="B28" s="294" t="inlineStr">
@@ -5846,14 +5846,14 @@
           <t>Contato:</t>
         </is>
       </c>
-      <c r="H29" s="297" t="inlineStr">
+      <c r="H29" s="296" t="inlineStr">
         <is>
           <t>(62) 4102-3282</t>
         </is>
       </c>
       <c r="I29" s="241" t="n"/>
-      <c r="J29" s="130" t="n"/>
-      <c r="K29" s="150" t="inlineStr">
+      <c r="J29" s="129" t="n"/>
+      <c r="K29" s="149" t="inlineStr">
         <is>
           <t>https://www.wimoveis.com.br/propriedades/fazenda-com-2-dormitorios-a-venda-40414000-m-sup2-2979429591.html</t>
         </is>
@@ -5880,8 +5880,8 @@
           <t xml:space="preserve">Boa </t>
         </is>
       </c>
-      <c r="I30" s="297" t="n"/>
-      <c r="K30" s="151" t="n"/>
+      <c r="I30" s="296" t="n"/>
+      <c r="K30" s="150" t="n"/>
     </row>
     <row r="31" ht="15" customHeight="1" s="236">
       <c r="B31" s="293" t="inlineStr">
@@ -5905,7 +5905,7 @@
       <c r="I31" s="241" t="n"/>
     </row>
     <row r="32" ht="15" customHeight="1" s="236">
-      <c r="B32" s="152" t="n"/>
+      <c r="B32" s="151" t="n"/>
       <c r="C32" s="299" t="inlineStr">
         <is>
           <t>Valor venal:</t>
@@ -5924,13 +5924,13 @@
         <v/>
       </c>
       <c r="I32" s="241" t="n"/>
-      <c r="J32" s="174">
+      <c r="J32" s="173">
         <f>H32*4.84</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1" s="236">
-      <c r="B33" s="153" t="n"/>
+      <c r="B33" s="152" t="n"/>
       <c r="C33" s="299" t="inlineStr">
         <is>
           <t>Negociação:</t>
@@ -5953,7 +5953,7 @@
       <c r="I33" s="241" t="n"/>
     </row>
     <row r="34" ht="15" customHeight="1" s="236">
-      <c r="B34" s="153" t="n"/>
+      <c r="B34" s="152" t="n"/>
       <c r="C34" s="299" t="inlineStr">
         <is>
           <t>Hidrografia:</t>
@@ -5969,7 +5969,7 @@
           <t>Outros:</t>
         </is>
       </c>
-      <c r="H34" s="297" t="n"/>
+      <c r="H34" s="296" t="n"/>
       <c r="I34" s="241" t="n"/>
     </row>
     <row r="35" ht="15" customHeight="1" s="236">
@@ -5986,22 +5986,22 @@
           <t>Classe de Solo</t>
         </is>
       </c>
-      <c r="E36" s="296" t="inlineStr">
+      <c r="E36" s="297" t="inlineStr">
         <is>
           <t>Área (ha)</t>
         </is>
       </c>
-      <c r="F36" s="296" t="inlineStr">
+      <c r="F36" s="297" t="inlineStr">
         <is>
           <t>% do Imóvel</t>
         </is>
       </c>
-      <c r="G36" s="296" t="inlineStr">
+      <c r="G36" s="297" t="inlineStr">
         <is>
           <t>Nota Agronômica</t>
         </is>
       </c>
-      <c r="I36" s="154" t="n"/>
+      <c r="I36" s="153" t="n"/>
     </row>
     <row r="37" ht="15" customHeight="1" s="236">
       <c r="B37" s="303" t="inlineStr">
@@ -6009,17 +6009,17 @@
           <t>IV</t>
         </is>
       </c>
-      <c r="E37" s="176" t="n">
+      <c r="E37" s="175" t="n">
         <v>275</v>
       </c>
-      <c r="F37" s="155">
+      <c r="F37" s="154">
         <f>E37/E31</f>
         <v/>
       </c>
       <c r="G37" s="310" t="n">
         <v>1</v>
       </c>
-      <c r="I37" s="154" t="n"/>
+      <c r="I37" s="153" t="n"/>
     </row>
     <row r="38" ht="15" customHeight="1" s="236">
       <c r="B38" s="303" t="inlineStr">
@@ -6027,17 +6027,17 @@
           <t>VIII</t>
         </is>
       </c>
-      <c r="E38" s="176" t="n">
+      <c r="E38" s="175" t="n">
         <v>3760</v>
       </c>
-      <c r="F38" s="155">
+      <c r="F38" s="154">
         <f>E38/E31</f>
         <v/>
       </c>
       <c r="G38" s="310" t="n">
         <v>0.6</v>
       </c>
-      <c r="I38" s="154" t="n"/>
+      <c r="I38" s="153" t="n"/>
     </row>
     <row r="39" ht="15" customHeight="1" s="236">
       <c r="B39" s="317" t="inlineStr">
@@ -6047,27 +6047,27 @@
       </c>
       <c r="C39" s="251" t="n"/>
       <c r="D39" s="251" t="n"/>
-      <c r="E39" s="172" t="n">
+      <c r="E39" s="171" t="n">
         <v>4035</v>
       </c>
-      <c r="F39" s="123" t="n">
+      <c r="F39" s="122" t="n">
         <v>1</v>
       </c>
       <c r="G39" s="308" t="n">
         <v>0.6272614622057001</v>
       </c>
       <c r="H39" s="251" t="n"/>
-      <c r="I39" s="156" t="n"/>
+      <c r="I39" s="155" t="n"/>
     </row>
     <row r="40" ht="15" customHeight="1" s="236">
-      <c r="B40" s="157" t="n"/>
-      <c r="C40" s="157" t="n"/>
-      <c r="D40" s="157" t="n"/>
-      <c r="E40" s="157" t="n"/>
-      <c r="F40" s="157" t="n"/>
-      <c r="G40" s="157" t="n"/>
-      <c r="H40" s="157" t="n"/>
-      <c r="I40" s="157" t="n"/>
+      <c r="B40" s="156" t="n"/>
+      <c r="C40" s="156" t="n"/>
+      <c r="D40" s="156" t="n"/>
+      <c r="E40" s="156" t="n"/>
+      <c r="F40" s="156" t="n"/>
+      <c r="G40" s="156" t="n"/>
+      <c r="H40" s="156" t="n"/>
+      <c r="I40" s="156" t="n"/>
     </row>
     <row r="41" ht="15" customHeight="1" s="236">
       <c r="B41" s="294" t="inlineStr">
@@ -6075,7 +6075,7 @@
           <t>Dado Amostral 03</t>
         </is>
       </c>
-      <c r="K41" s="139" t="inlineStr">
+      <c r="K41" s="138" t="inlineStr">
         <is>
           <t>https://www.wimoveis.com.br/propriedades/fazenda-a-venda-na-regiao-de-almas-to-2985494046.html</t>
         </is>
@@ -6099,13 +6099,13 @@
           <t>Contato:</t>
         </is>
       </c>
-      <c r="H42" s="297" t="inlineStr">
+      <c r="H42" s="296" t="inlineStr">
         <is>
           <t>(11) 41545889</t>
         </is>
       </c>
       <c r="I42" s="241" t="n"/>
-      <c r="K42" s="150" t="n"/>
+      <c r="K42" s="149" t="n"/>
     </row>
     <row r="43" ht="15" customHeight="1" s="236">
       <c r="B43" s="293" t="inlineStr">
@@ -6129,7 +6129,7 @@
         </is>
       </c>
       <c r="I43" s="241" t="n"/>
-      <c r="K43" s="151" t="n"/>
+      <c r="K43" s="150" t="n"/>
     </row>
     <row r="44" ht="15" customHeight="1" s="236">
       <c r="B44" s="293" t="inlineStr">
@@ -6153,7 +6153,7 @@
       <c r="I44" s="241" t="n"/>
     </row>
     <row r="45" ht="15" customHeight="1" s="236">
-      <c r="B45" s="152" t="n"/>
+      <c r="B45" s="151" t="n"/>
       <c r="C45" s="299" t="inlineStr">
         <is>
           <t>Valor venal:</t>
@@ -6172,13 +6172,13 @@
         <v/>
       </c>
       <c r="I45" s="241" t="n"/>
-      <c r="J45" s="174">
+      <c r="J45" s="173">
         <f>H45*4.84</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1" s="236">
-      <c r="B46" s="153" t="n"/>
+      <c r="B46" s="152" t="n"/>
       <c r="C46" s="299" t="inlineStr">
         <is>
           <t>Negociação:</t>
@@ -6201,7 +6201,7 @@
       <c r="I46" s="241" t="n"/>
     </row>
     <row r="47" ht="15" customHeight="1" s="236">
-      <c r="B47" s="153" t="n"/>
+      <c r="B47" s="152" t="n"/>
       <c r="C47" s="299" t="inlineStr">
         <is>
           <t>Hidrografia:</t>
@@ -6217,7 +6217,7 @@
           <t>Outros:</t>
         </is>
       </c>
-      <c r="H47" s="297" t="n"/>
+      <c r="H47" s="296" t="n"/>
       <c r="I47" s="241" t="n"/>
     </row>
     <row r="48" ht="15" customHeight="1" s="236">
@@ -6234,22 +6234,22 @@
           <t>Classe de Solo</t>
         </is>
       </c>
-      <c r="E49" s="296" t="inlineStr">
+      <c r="E49" s="297" t="inlineStr">
         <is>
           <t>Área (ha)</t>
         </is>
       </c>
-      <c r="F49" s="296" t="inlineStr">
+      <c r="F49" s="297" t="inlineStr">
         <is>
           <t>% do Imóvel</t>
         </is>
       </c>
-      <c r="G49" s="296" t="inlineStr">
+      <c r="G49" s="297" t="inlineStr">
         <is>
           <t>Nota Agronômica</t>
         </is>
       </c>
-      <c r="I49" s="154" t="n"/>
+      <c r="I49" s="153" t="n"/>
     </row>
     <row r="50" ht="15" customHeight="1" s="236">
       <c r="B50" s="303" t="inlineStr">
@@ -6257,17 +6257,17 @@
           <t>IV</t>
         </is>
       </c>
-      <c r="E50" s="176" t="n">
+      <c r="E50" s="175" t="n">
         <v>300</v>
       </c>
-      <c r="F50" s="155">
+      <c r="F50" s="154">
         <f>E50/E44</f>
         <v/>
       </c>
       <c r="G50" s="310" t="n">
         <v>1</v>
       </c>
-      <c r="I50" s="154" t="n"/>
+      <c r="I50" s="153" t="n"/>
     </row>
     <row r="51" ht="15" customHeight="1" s="236">
       <c r="B51" s="303" t="inlineStr">
@@ -6275,17 +6275,17 @@
           <t>VIII</t>
         </is>
       </c>
-      <c r="E51" s="176" t="n">
+      <c r="E51" s="175" t="n">
         <v>1026.16</v>
       </c>
-      <c r="F51" s="155">
+      <c r="F51" s="154">
         <f>E51/E44</f>
         <v/>
       </c>
       <c r="G51" s="310" t="n">
         <v>0.6</v>
       </c>
-      <c r="I51" s="154" t="n"/>
+      <c r="I51" s="153" t="n"/>
     </row>
     <row r="52" ht="15" customHeight="1" s="236">
       <c r="B52" s="317" t="inlineStr">
@@ -6295,27 +6295,27 @@
       </c>
       <c r="C52" s="251" t="n"/>
       <c r="D52" s="251" t="n"/>
-      <c r="E52" s="172" t="n">
+      <c r="E52" s="171" t="n">
         <v>1326.16</v>
       </c>
-      <c r="F52" s="123" t="n">
+      <c r="F52" s="122" t="n">
         <v>1</v>
       </c>
       <c r="G52" s="308" t="n">
         <v>0.6904868190866864</v>
       </c>
       <c r="H52" s="251" t="n"/>
-      <c r="I52" s="156" t="n"/>
+      <c r="I52" s="155" t="n"/>
     </row>
     <row r="53" ht="15" customHeight="1" s="236">
-      <c r="B53" s="157" t="n"/>
-      <c r="C53" s="157" t="n"/>
-      <c r="D53" s="157" t="n"/>
-      <c r="E53" s="157" t="n"/>
-      <c r="F53" s="157" t="n"/>
-      <c r="G53" s="157" t="n"/>
-      <c r="H53" s="157" t="n"/>
-      <c r="I53" s="157" t="n"/>
+      <c r="B53" s="156" t="n"/>
+      <c r="C53" s="156" t="n"/>
+      <c r="D53" s="156" t="n"/>
+      <c r="E53" s="156" t="n"/>
+      <c r="F53" s="156" t="n"/>
+      <c r="G53" s="156" t="n"/>
+      <c r="H53" s="156" t="n"/>
+      <c r="I53" s="156" t="n"/>
     </row>
     <row r="54" ht="15" customHeight="1" s="236">
       <c r="B54" s="294" t="inlineStr">
@@ -6342,13 +6342,13 @@
           <t>Contato:</t>
         </is>
       </c>
-      <c r="H55" s="297" t="inlineStr">
+      <c r="H55" s="296" t="inlineStr">
         <is>
           <t>(63) 9 8588-7530</t>
         </is>
       </c>
       <c r="I55" s="241" t="n"/>
-      <c r="K55" s="150" t="n"/>
+      <c r="K55" s="149" t="n"/>
     </row>
     <row r="56" ht="15" customHeight="1" s="236">
       <c r="B56" s="293" t="inlineStr">
@@ -6372,7 +6372,7 @@
         </is>
       </c>
       <c r="I56" s="241" t="n"/>
-      <c r="K56" s="150" t="inlineStr">
+      <c r="K56" s="149" t="inlineStr">
         <is>
           <t>https://www.wimoveis.com.br/propriedades/fazenda-dianopolis-tocantins-86-alqueires-2978510623.html</t>
         </is>
@@ -6398,10 +6398,10 @@
         </is>
       </c>
       <c r="I57" s="241" t="n"/>
-      <c r="K57" s="151" t="n"/>
+      <c r="K57" s="150" t="n"/>
     </row>
     <row r="58" ht="15" customHeight="1" s="236">
-      <c r="B58" s="152" t="n"/>
+      <c r="B58" s="151" t="n"/>
       <c r="C58" s="299" t="inlineStr">
         <is>
           <t>Valor venal:</t>
@@ -6420,14 +6420,14 @@
         <v/>
       </c>
       <c r="I58" s="241" t="n"/>
-      <c r="J58" s="174">
+      <c r="J58" s="173">
         <f>H58*4.84</f>
         <v/>
       </c>
-      <c r="K58" s="177" t="n"/>
+      <c r="K58" s="176" t="n"/>
     </row>
     <row r="59" ht="15" customHeight="1" s="236">
-      <c r="B59" s="153" t="n"/>
+      <c r="B59" s="152" t="n"/>
       <c r="C59" s="299" t="inlineStr">
         <is>
           <t>Negociação:</t>
@@ -6450,7 +6450,7 @@
       <c r="I59" s="241" t="n"/>
     </row>
     <row r="60" ht="15" customHeight="1" s="236">
-      <c r="B60" s="153" t="n"/>
+      <c r="B60" s="152" t="n"/>
       <c r="C60" s="299" t="inlineStr">
         <is>
           <t>Hidrografia:</t>
@@ -6466,7 +6466,7 @@
           <t>Outros:</t>
         </is>
       </c>
-      <c r="H60" s="297" t="n"/>
+      <c r="H60" s="296" t="n"/>
       <c r="I60" s="241" t="n"/>
     </row>
     <row r="61" ht="15" customHeight="1" s="236">
@@ -6483,22 +6483,22 @@
           <t>Classe de Solo</t>
         </is>
       </c>
-      <c r="E62" s="296" t="inlineStr">
+      <c r="E62" s="297" t="inlineStr">
         <is>
           <t>Área (ha)</t>
         </is>
       </c>
-      <c r="F62" s="296" t="inlineStr">
+      <c r="F62" s="297" t="inlineStr">
         <is>
           <t>% do Imóvel</t>
         </is>
       </c>
-      <c r="G62" s="296" t="inlineStr">
+      <c r="G62" s="297" t="inlineStr">
         <is>
           <t>Nota Agronômica</t>
         </is>
       </c>
-      <c r="I62" s="154" t="n"/>
+      <c r="I62" s="153" t="n"/>
     </row>
     <row r="63" ht="15" customHeight="1" s="236">
       <c r="B63" s="303" t="inlineStr">
@@ -6506,18 +6506,18 @@
           <t>IV</t>
         </is>
       </c>
-      <c r="E63" s="176">
+      <c r="E63" s="175">
         <f>E57*0.632141</f>
         <v/>
       </c>
-      <c r="F63" s="155">
+      <c r="F63" s="154">
         <f>E63/E57</f>
         <v/>
       </c>
       <c r="G63" s="310" t="n">
         <v>1</v>
       </c>
-      <c r="I63" s="154" t="n"/>
+      <c r="I63" s="153" t="n"/>
     </row>
     <row r="64" ht="15" customHeight="1" s="236">
       <c r="B64" s="303" t="inlineStr">
@@ -6525,18 +6525,18 @@
           <t>VIII</t>
         </is>
       </c>
-      <c r="E64" s="176">
+      <c r="E64" s="175">
         <f>E57-E63</f>
         <v/>
       </c>
-      <c r="F64" s="155">
+      <c r="F64" s="154">
         <f>E64/E57</f>
         <v/>
       </c>
       <c r="G64" s="310" t="n">
         <v>0.6</v>
       </c>
-      <c r="I64" s="154" t="n"/>
+      <c r="I64" s="153" t="n"/>
     </row>
     <row r="65" ht="15" customHeight="1" s="236">
       <c r="B65" s="317" t="inlineStr">
@@ -6546,27 +6546,27 @@
       </c>
       <c r="C65" s="251" t="n"/>
       <c r="D65" s="251" t="n"/>
-      <c r="E65" s="172" t="n">
+      <c r="E65" s="171" t="n">
         <v>416.27</v>
       </c>
-      <c r="F65" s="123" t="n">
+      <c r="F65" s="122" t="n">
         <v>1</v>
       </c>
       <c r="G65" s="308" t="n">
         <v>0.8600000000000001</v>
       </c>
       <c r="H65" s="251" t="n"/>
-      <c r="I65" s="156" t="n"/>
+      <c r="I65" s="155" t="n"/>
     </row>
     <row r="66" ht="15" customHeight="1" s="236">
-      <c r="B66" s="157" t="n"/>
-      <c r="C66" s="157" t="n"/>
-      <c r="D66" s="157" t="n"/>
-      <c r="E66" s="157" t="n"/>
-      <c r="F66" s="157" t="n"/>
-      <c r="G66" s="157" t="n"/>
-      <c r="H66" s="157" t="n"/>
-      <c r="I66" s="157" t="n"/>
+      <c r="B66" s="156" t="n"/>
+      <c r="C66" s="156" t="n"/>
+      <c r="D66" s="156" t="n"/>
+      <c r="E66" s="156" t="n"/>
+      <c r="F66" s="156" t="n"/>
+      <c r="G66" s="156" t="n"/>
+      <c r="H66" s="156" t="n"/>
+      <c r="I66" s="156" t="n"/>
     </row>
     <row r="67" ht="15" customHeight="1" s="236">
       <c r="B67" s="294" t="inlineStr">
@@ -6599,7 +6599,7 @@
         </is>
       </c>
       <c r="I68" s="241" t="n"/>
-      <c r="K68" s="150" t="inlineStr">
+      <c r="K68" s="149" t="inlineStr">
         <is>
           <t>https://www.zapimoveis.com.br/imovel/venda-fazenda-sitio-chacara-zona-rural-almas-to-2178000m2-id-2705465160/</t>
         </is>
@@ -6654,10 +6654,10 @@
         </is>
       </c>
       <c r="I70" s="241" t="n"/>
-      <c r="K70" s="151" t="n"/>
+      <c r="K70" s="150" t="n"/>
     </row>
     <row r="71" ht="15" customHeight="1" s="236">
-      <c r="B71" s="152" t="n"/>
+      <c r="B71" s="151" t="n"/>
       <c r="C71" s="299" t="inlineStr">
         <is>
           <t>Valor venal:</t>
@@ -6676,13 +6676,13 @@
         <v/>
       </c>
       <c r="I71" s="241" t="n"/>
-      <c r="J71" s="174">
+      <c r="J71" s="173">
         <f>H71*4.84</f>
         <v/>
       </c>
     </row>
     <row r="72" ht="15" customHeight="1" s="236">
-      <c r="B72" s="153" t="n"/>
+      <c r="B72" s="152" t="n"/>
       <c r="C72" s="299" t="inlineStr">
         <is>
           <t>Negociação:</t>
@@ -6705,7 +6705,7 @@
       <c r="I72" s="241" t="n"/>
     </row>
     <row r="73" ht="15" customHeight="1" s="236">
-      <c r="B73" s="153" t="n"/>
+      <c r="B73" s="152" t="n"/>
       <c r="C73" s="299" t="inlineStr">
         <is>
           <t>Hidrografia:</t>
@@ -6721,7 +6721,7 @@
           <t>Outros:</t>
         </is>
       </c>
-      <c r="H73" s="297" t="n"/>
+      <c r="H73" s="296" t="n"/>
       <c r="I73" s="241" t="n"/>
     </row>
     <row r="74" ht="15" customHeight="1" s="236">
@@ -6738,22 +6738,22 @@
           <t>Classe de Solo</t>
         </is>
       </c>
-      <c r="E75" s="296" t="inlineStr">
+      <c r="E75" s="297" t="inlineStr">
         <is>
           <t>Área (ha)</t>
         </is>
       </c>
-      <c r="F75" s="296" t="inlineStr">
+      <c r="F75" s="297" t="inlineStr">
         <is>
           <t>% do Imóvel</t>
         </is>
       </c>
-      <c r="G75" s="296" t="inlineStr">
+      <c r="G75" s="297" t="inlineStr">
         <is>
           <t>Nota Agronômica</t>
         </is>
       </c>
-      <c r="I75" s="154" t="n"/>
+      <c r="I75" s="153" t="n"/>
     </row>
     <row r="76" ht="15" customHeight="1" s="236">
       <c r="B76" s="303" t="inlineStr">
@@ -6761,18 +6761,18 @@
           <t>IV</t>
         </is>
       </c>
-      <c r="E76" s="176">
+      <c r="E76" s="175">
         <f>E70*0.621345</f>
         <v/>
       </c>
-      <c r="F76" s="155">
+      <c r="F76" s="154">
         <f>E76/E70</f>
         <v/>
       </c>
       <c r="G76" s="310" t="n">
         <v>1</v>
       </c>
-      <c r="I76" s="154" t="n"/>
+      <c r="I76" s="153" t="n"/>
     </row>
     <row r="77" ht="15" customHeight="1" s="236">
       <c r="B77" s="303" t="inlineStr">
@@ -6780,18 +6780,18 @@
           <t>VIII</t>
         </is>
       </c>
-      <c r="E77" s="176">
+      <c r="E77" s="175">
         <f>E70-E76</f>
         <v/>
       </c>
-      <c r="F77" s="155">
+      <c r="F77" s="154">
         <f>E77/E70</f>
         <v/>
       </c>
       <c r="G77" s="310" t="n">
         <v>0.6</v>
       </c>
-      <c r="I77" s="154" t="n"/>
+      <c r="I77" s="153" t="n"/>
     </row>
     <row r="78" ht="15" customHeight="1" s="236">
       <c r="B78" s="317" t="inlineStr">
@@ -6801,27 +6801,27 @@
       </c>
       <c r="C78" s="251" t="n"/>
       <c r="D78" s="251" t="n"/>
-      <c r="E78" s="172" t="n">
+      <c r="E78" s="171" t="n">
         <v>1839</v>
       </c>
-      <c r="F78" s="123" t="n">
+      <c r="F78" s="122" t="n">
         <v>0.9999999999999999</v>
       </c>
       <c r="G78" s="308" t="n">
         <v>0.8599999999999999</v>
       </c>
       <c r="H78" s="251" t="n"/>
-      <c r="I78" s="156" t="n"/>
+      <c r="I78" s="155" t="n"/>
     </row>
     <row r="79" ht="15" customHeight="1" s="236">
-      <c r="B79" s="157" t="n"/>
-      <c r="C79" s="157" t="n"/>
-      <c r="D79" s="157" t="n"/>
-      <c r="E79" s="157" t="n"/>
-      <c r="F79" s="157" t="n"/>
-      <c r="G79" s="157" t="n"/>
-      <c r="H79" s="157" t="n"/>
-      <c r="I79" s="157" t="n"/>
+      <c r="B79" s="156" t="n"/>
+      <c r="C79" s="156" t="n"/>
+      <c r="D79" s="156" t="n"/>
+      <c r="E79" s="156" t="n"/>
+      <c r="F79" s="156" t="n"/>
+      <c r="G79" s="156" t="n"/>
+      <c r="H79" s="156" t="n"/>
+      <c r="I79" s="156" t="n"/>
     </row>
     <row r="80" ht="15" customHeight="1" s="236">
       <c r="B80" s="294" t="inlineStr">
@@ -6848,12 +6848,12 @@
           <t>Contato:</t>
         </is>
       </c>
-      <c r="H81" s="297">
+      <c r="H81" s="296">
         <f>H68</f>
         <v/>
       </c>
       <c r="I81" s="241" t="n"/>
-      <c r="K81" s="150" t="inlineStr">
+      <c r="K81" s="149" t="inlineStr">
         <is>
           <t>https://www.vivareal.com.br/imovel/fazenda---sitio-2-quartos-zona-rural-bairros-dianopolis-12600000m2-venda-RS75600000-id-2655532548/</t>
         </is>
@@ -6907,10 +6907,10 @@
         </is>
       </c>
       <c r="I83" s="241" t="n"/>
-      <c r="K83" s="151" t="n"/>
+      <c r="K83" s="150" t="n"/>
     </row>
     <row r="84" ht="15" customHeight="1" s="236">
-      <c r="B84" s="152" t="n"/>
+      <c r="B84" s="151" t="n"/>
       <c r="C84" s="299" t="inlineStr">
         <is>
           <t>Valor venal:</t>
@@ -6928,13 +6928,13 @@
         <v>12396.69421487603</v>
       </c>
       <c r="I84" s="241" t="n"/>
-      <c r="J84" s="174">
+      <c r="J84" s="173">
         <f>H84*4.84</f>
         <v/>
       </c>
     </row>
     <row r="85" ht="15" customHeight="1" s="236">
-      <c r="B85" s="153" t="n"/>
+      <c r="B85" s="152" t="n"/>
       <c r="C85" s="299" t="inlineStr">
         <is>
           <t>Negociação:</t>
@@ -6957,7 +6957,7 @@
       <c r="I85" s="241" t="n"/>
     </row>
     <row r="86" ht="15" customHeight="1" s="236">
-      <c r="B86" s="153" t="n"/>
+      <c r="B86" s="152" t="n"/>
       <c r="C86" s="299" t="inlineStr">
         <is>
           <t>Hidrografia:</t>
@@ -6973,7 +6973,7 @@
           <t>Outros:</t>
         </is>
       </c>
-      <c r="H86" s="297" t="n"/>
+      <c r="H86" s="296" t="n"/>
       <c r="I86" s="241" t="n"/>
     </row>
     <row r="87" ht="15" customHeight="1" s="236">
@@ -6990,22 +6990,22 @@
           <t>Classe de Solo</t>
         </is>
       </c>
-      <c r="E88" s="296" t="inlineStr">
+      <c r="E88" s="297" t="inlineStr">
         <is>
           <t>Área (ha)</t>
         </is>
       </c>
-      <c r="F88" s="296" t="inlineStr">
+      <c r="F88" s="297" t="inlineStr">
         <is>
           <t>% do Imóvel</t>
         </is>
       </c>
-      <c r="G88" s="296" t="inlineStr">
+      <c r="G88" s="297" t="inlineStr">
         <is>
           <t>Nota Agronômica</t>
         </is>
       </c>
-      <c r="I88" s="154" t="n"/>
+      <c r="I88" s="153" t="n"/>
     </row>
     <row r="89" ht="15" customHeight="1" s="236">
       <c r="B89" s="303" t="inlineStr">
@@ -7013,18 +7013,18 @@
           <t>IV</t>
         </is>
       </c>
-      <c r="E89" s="176">
+      <c r="E89" s="175">
         <f>E83*0.723145</f>
         <v/>
       </c>
-      <c r="F89" s="155">
+      <c r="F89" s="154">
         <f>E89/E83</f>
         <v/>
       </c>
       <c r="G89" s="310" t="n">
         <v>1</v>
       </c>
-      <c r="I89" s="154" t="n"/>
+      <c r="I89" s="153" t="n"/>
     </row>
     <row r="90" ht="15" customHeight="1" s="236">
       <c r="B90" s="303" t="inlineStr">
@@ -7032,19 +7032,19 @@
           <t>VIII</t>
         </is>
       </c>
-      <c r="E90" s="176">
+      <c r="E90" s="175">
         <f>E83-E89</f>
         <v/>
       </c>
-      <c r="F90" s="155">
+      <c r="F90" s="154">
         <f>E90/E83</f>
         <v/>
       </c>
       <c r="G90" s="310" t="n">
         <v>0.6</v>
       </c>
-      <c r="I90" s="154" t="n"/>
-      <c r="L90" s="142" t="n"/>
+      <c r="I90" s="153" t="n"/>
+      <c r="L90" s="141" t="n"/>
     </row>
     <row r="91" ht="15" customHeight="1" s="236">
       <c r="B91" s="317" t="inlineStr">
@@ -7054,33 +7054,33 @@
       </c>
       <c r="C91" s="251" t="n"/>
       <c r="D91" s="251" t="n"/>
-      <c r="E91" s="172" t="n">
+      <c r="E91" s="171" t="n">
         <v>6098.4</v>
       </c>
-      <c r="F91" s="123" t="n">
+      <c r="F91" s="122" t="n">
         <v>1</v>
       </c>
       <c r="G91" s="308" t="n">
         <v>0.86</v>
       </c>
       <c r="H91" s="251" t="n"/>
-      <c r="I91" s="156" t="n"/>
-      <c r="L91" s="142" t="n"/>
+      <c r="I91" s="155" t="n"/>
+      <c r="L91" s="141" t="n"/>
     </row>
     <row r="92" ht="15" customHeight="1" s="236">
-      <c r="B92" s="125" t="n"/>
-      <c r="C92" s="125" t="n"/>
-      <c r="D92" s="125" t="n"/>
-      <c r="E92" s="125" t="n"/>
-      <c r="F92" s="125" t="n"/>
-      <c r="G92" s="125" t="n"/>
-      <c r="H92" s="125" t="n"/>
-      <c r="I92" s="125" t="n"/>
-      <c r="K92" s="142">
+      <c r="B92" s="124" t="n"/>
+      <c r="C92" s="124" t="n"/>
+      <c r="D92" s="124" t="n"/>
+      <c r="E92" s="124" t="n"/>
+      <c r="F92" s="124" t="n"/>
+      <c r="G92" s="124" t="n"/>
+      <c r="H92" s="124" t="n"/>
+      <c r="I92" s="124" t="n"/>
+      <c r="K92" s="141">
         <f>60*4.84</f>
         <v/>
       </c>
-      <c r="L92" s="142" t="n"/>
+      <c r="L92" s="141" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="191">
@@ -7089,9 +7089,9 @@
     <mergeCell ref="B57:D57"/>
     <mergeCell ref="B54:I54"/>
     <mergeCell ref="E71:F71"/>
-    <mergeCell ref="G23:H23"/>
     <mergeCell ref="B44:D44"/>
     <mergeCell ref="H55:I55"/>
+    <mergeCell ref="G23:H23"/>
     <mergeCell ref="E8:F8"/>
     <mergeCell ref="C73:D73"/>
     <mergeCell ref="L3:M3"/>
@@ -7120,9 +7120,9 @@
     <mergeCell ref="E55:F55"/>
     <mergeCell ref="B17:D17"/>
     <mergeCell ref="E5:F5"/>
+    <mergeCell ref="B88:D88"/>
     <mergeCell ref="C45:D45"/>
     <mergeCell ref="B22:I22"/>
-    <mergeCell ref="B88:D88"/>
     <mergeCell ref="B82:D82"/>
     <mergeCell ref="C4:D4"/>
     <mergeCell ref="H56:I56"/>
@@ -7189,10 +7189,10 @@
     <mergeCell ref="C84:D84"/>
     <mergeCell ref="E69:F69"/>
     <mergeCell ref="E84:F84"/>
+    <mergeCell ref="G13:H13"/>
     <mergeCell ref="B65:D65"/>
     <mergeCell ref="B61:I61"/>
     <mergeCell ref="B67:I67"/>
-    <mergeCell ref="G13:H13"/>
     <mergeCell ref="G78:H78"/>
     <mergeCell ref="B51:D51"/>
     <mergeCell ref="E31:F31"/>
@@ -7201,10 +7201,10 @@
     <mergeCell ref="E6:F6"/>
     <mergeCell ref="C46:D46"/>
     <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E46:F46"/>
     <mergeCell ref="B63:D63"/>
+    <mergeCell ref="E86:F86"/>
     <mergeCell ref="H16:I16"/>
-    <mergeCell ref="E86:F86"/>
-    <mergeCell ref="E46:F46"/>
     <mergeCell ref="B50:D50"/>
     <mergeCell ref="H57:I57"/>
     <mergeCell ref="G89:H89"/>
@@ -7308,8 +7308,8 @@
     <col width="10.7109375" customWidth="1" style="272" min="10" max="10"/>
     <col width="30.7109375" customWidth="1" style="272" min="11" max="11"/>
     <col width="17.42578125" bestFit="1" customWidth="1" style="272" min="12" max="12"/>
-    <col width="9.140625" customWidth="1" style="272" min="13" max="80"/>
-    <col width="9.140625" customWidth="1" style="272" min="81" max="16384"/>
+    <col width="9.140625" customWidth="1" style="272" min="13" max="86"/>
+    <col width="9.140625" customWidth="1" style="272" min="87" max="16384"/>
   </cols>
   <sheetData>
     <row r="3" ht="13.5" customHeight="1" s="236">
@@ -7323,7 +7323,7 @@
           <t>ÁREA (ha)</t>
         </is>
       </c>
-      <c r="D3" s="126" t="inlineStr">
+      <c r="D3" s="125" t="inlineStr">
         <is>
           <t>VT (R$)</t>
         </is>
@@ -7333,7 +7333,7 @@
           <t>VT(R$/ha)</t>
         </is>
       </c>
-      <c r="F3" s="126" t="inlineStr">
+      <c r="F3" s="125" t="inlineStr">
         <is>
           <t xml:space="preserve">CLASSE </t>
         </is>
@@ -7343,12 +7343,12 @@
           <t>SITUAÇÃO</t>
         </is>
       </c>
-      <c r="H3" s="126" t="inlineStr">
+      <c r="H3" s="125" t="inlineStr">
         <is>
           <t>BENFEITORIAS</t>
         </is>
       </c>
-      <c r="I3" s="126" t="inlineStr">
+      <c r="I3" s="125" t="inlineStr">
         <is>
           <t>HIDROGRAFIA</t>
         </is>
@@ -7358,12 +7358,12 @@
           <t>FONTE</t>
         </is>
       </c>
-      <c r="K3" s="126" t="inlineStr">
+      <c r="K3" s="125" t="inlineStr">
         <is>
           <t>INFORMANTE</t>
         </is>
       </c>
-      <c r="L3" s="146" t="inlineStr">
+      <c r="L3" s="145" t="inlineStr">
         <is>
           <t>CONTATO</t>
         </is>
@@ -7373,7 +7373,7 @@
       <c r="B4" s="277" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="178">
+      <c r="C4" s="177">
         <f>AMOSTRAS!E18</f>
         <v/>
       </c>
@@ -7385,23 +7385,23 @@
         <f>D4/C4</f>
         <v/>
       </c>
-      <c r="F4" s="179">
+      <c r="F4" s="178">
         <f>AMOSTRAS!G26</f>
         <v/>
       </c>
-      <c r="G4" s="129" t="n">
+      <c r="G4" s="128" t="n">
         <v>1</v>
       </c>
-      <c r="H4" s="129" t="n">
+      <c r="H4" s="128" t="n">
         <v>0.8</v>
       </c>
-      <c r="I4" s="129" t="n">
+      <c r="I4" s="128" t="n">
         <v>1</v>
       </c>
-      <c r="J4" s="129" t="n">
+      <c r="J4" s="128" t="n">
         <v>0.9</v>
       </c>
-      <c r="K4" s="145">
+      <c r="K4" s="144">
         <f>AMOSTRAS!E16</f>
         <v/>
       </c>
@@ -7409,13 +7409,13 @@
         <f>AMOSTRAS!H16</f>
         <v/>
       </c>
-      <c r="M4" s="141" t="n"/>
+      <c r="M4" s="140" t="n"/>
     </row>
     <row r="5">
       <c r="B5" s="277" t="n">
         <v>2</v>
       </c>
-      <c r="C5" s="178">
+      <c r="C5" s="177">
         <f>AMOSTRAS!E31</f>
         <v/>
       </c>
@@ -7427,23 +7427,23 @@
         <f>D5/C5</f>
         <v/>
       </c>
-      <c r="F5" s="179">
+      <c r="F5" s="178">
         <f>AMOSTRAS!G39</f>
         <v/>
       </c>
-      <c r="G5" s="129" t="n">
+      <c r="G5" s="128" t="n">
         <v>1</v>
       </c>
-      <c r="H5" s="129" t="n">
+      <c r="H5" s="128" t="n">
         <v>0.8</v>
       </c>
-      <c r="I5" s="129" t="n">
+      <c r="I5" s="128" t="n">
         <v>1</v>
       </c>
-      <c r="J5" s="129" t="n">
+      <c r="J5" s="128" t="n">
         <v>0.9</v>
       </c>
-      <c r="K5" s="145">
+      <c r="K5" s="144">
         <f>AMOSTRAS!E29</f>
         <v/>
       </c>
@@ -7451,13 +7451,13 @@
         <f>AMOSTRAS!H29</f>
         <v/>
       </c>
-      <c r="M5" s="141" t="n"/>
+      <c r="M5" s="140" t="n"/>
     </row>
     <row r="6">
       <c r="B6" s="277" t="n">
         <v>3</v>
       </c>
-      <c r="C6" s="178">
+      <c r="C6" s="177">
         <f>AMOSTRAS!E44</f>
         <v/>
       </c>
@@ -7469,23 +7469,23 @@
         <f>D6/C6</f>
         <v/>
       </c>
-      <c r="F6" s="179">
+      <c r="F6" s="178">
         <f>AMOSTRAS!G52</f>
         <v/>
       </c>
-      <c r="G6" s="129" t="n">
+      <c r="G6" s="128" t="n">
         <v>1</v>
       </c>
-      <c r="H6" s="129" t="n">
+      <c r="H6" s="128" t="n">
         <v>0.8</v>
       </c>
-      <c r="I6" s="129" t="n">
+      <c r="I6" s="128" t="n">
         <v>1</v>
       </c>
-      <c r="J6" s="129" t="n">
+      <c r="J6" s="128" t="n">
         <v>0.9</v>
       </c>
-      <c r="K6" s="145">
+      <c r="K6" s="144">
         <f>AMOSTRAS!E42</f>
         <v/>
       </c>
@@ -7493,13 +7493,13 @@
         <f>AMOSTRAS!H42</f>
         <v/>
       </c>
-      <c r="M6" s="141" t="n"/>
+      <c r="M6" s="140" t="n"/>
     </row>
     <row r="7">
       <c r="B7" s="277" t="n">
         <v>4</v>
       </c>
-      <c r="C7" s="178">
+      <c r="C7" s="177">
         <f>AMOSTRAS!E57</f>
         <v/>
       </c>
@@ -7511,23 +7511,23 @@
         <f>D7/C7</f>
         <v/>
       </c>
-      <c r="F7" s="179">
+      <c r="F7" s="178">
         <f>AMOSTRAS!G65</f>
         <v/>
       </c>
-      <c r="G7" s="129" t="n">
+      <c r="G7" s="128" t="n">
         <v>1</v>
       </c>
-      <c r="H7" s="129" t="n">
+      <c r="H7" s="128" t="n">
         <v>0.8</v>
       </c>
-      <c r="I7" s="129" t="n">
+      <c r="I7" s="128" t="n">
         <v>1</v>
       </c>
-      <c r="J7" s="129" t="n">
+      <c r="J7" s="128" t="n">
         <v>0.9</v>
       </c>
-      <c r="K7" s="145">
+      <c r="K7" s="144">
         <f>AMOSTRAS!E55</f>
         <v/>
       </c>
@@ -7535,13 +7535,13 @@
         <f>AMOSTRAS!H55</f>
         <v/>
       </c>
-      <c r="M7" s="141" t="n"/>
+      <c r="M7" s="140" t="n"/>
     </row>
     <row r="8">
       <c r="B8" s="277" t="n">
         <v>5</v>
       </c>
-      <c r="C8" s="178">
+      <c r="C8" s="177">
         <f>AMOSTRAS!E70</f>
         <v/>
       </c>
@@ -7553,23 +7553,23 @@
         <f>D8/C8</f>
         <v/>
       </c>
-      <c r="F8" s="179">
+      <c r="F8" s="178">
         <f>AMOSTRAS!G78</f>
         <v/>
       </c>
-      <c r="G8" s="129" t="n">
+      <c r="G8" s="128" t="n">
         <v>1</v>
       </c>
-      <c r="H8" s="129" t="n">
+      <c r="H8" s="128" t="n">
         <v>0.8</v>
       </c>
-      <c r="I8" s="129" t="n">
+      <c r="I8" s="128" t="n">
         <v>1</v>
       </c>
-      <c r="J8" s="129" t="n">
+      <c r="J8" s="128" t="n">
         <v>0.9</v>
       </c>
-      <c r="K8" s="145">
+      <c r="K8" s="144">
         <f>AMOSTRAS!E68</f>
         <v/>
       </c>
@@ -7577,13 +7577,13 @@
         <f>AMOSTRAS!H68</f>
         <v/>
       </c>
-      <c r="M8" s="141" t="n"/>
+      <c r="M8" s="140" t="n"/>
     </row>
     <row r="9">
       <c r="B9" s="277" t="n">
         <v>6</v>
       </c>
-      <c r="C9" s="178">
+      <c r="C9" s="177">
         <f>AMOSTRAS!E83</f>
         <v/>
       </c>
@@ -7595,23 +7595,23 @@
         <f>D9/C9</f>
         <v/>
       </c>
-      <c r="F9" s="179">
+      <c r="F9" s="178">
         <f>AMOSTRAS!G91</f>
         <v/>
       </c>
-      <c r="G9" s="129" t="n">
+      <c r="G9" s="128" t="n">
         <v>1</v>
       </c>
-      <c r="H9" s="129" t="n">
+      <c r="H9" s="128" t="n">
         <v>0.8</v>
       </c>
-      <c r="I9" s="129" t="n">
+      <c r="I9" s="128" t="n">
         <v>1</v>
       </c>
-      <c r="J9" s="129" t="n">
+      <c r="J9" s="128" t="n">
         <v>0.9</v>
       </c>
-      <c r="K9" s="145">
+      <c r="K9" s="144">
         <f>AMOSTRAS!E81</f>
         <v/>
       </c>
@@ -7651,8 +7651,8 @@
     <col width="20.7109375" customWidth="1" style="331" min="16" max="16"/>
     <col width="19.140625" bestFit="1" customWidth="1" style="331" min="17" max="17"/>
     <col width="15.85546875" bestFit="1" customWidth="1" style="331" min="18" max="18"/>
-    <col width="9.140625" customWidth="1" style="331" min="19" max="86"/>
-    <col width="9.140625" customWidth="1" style="331" min="87" max="16384"/>
+    <col width="9.140625" customWidth="1" style="331" min="19" max="92"/>
+    <col width="9.140625" customWidth="1" style="331" min="93" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1" s="236">
@@ -7768,51 +7768,51 @@
         <f>AMOSTRAS!E19</f>
         <v/>
       </c>
-      <c r="E4" s="180">
+      <c r="E4" s="179">
         <f>AMOSTRAS!E18</f>
         <v/>
       </c>
-      <c r="F4" s="127">
+      <c r="F4" s="126">
         <f>D4/E4</f>
         <v/>
       </c>
-      <c r="G4" s="181">
+      <c r="G4" s="180">
         <f>AMOSTRAS!G26</f>
         <v/>
       </c>
-      <c r="H4" s="182">
+      <c r="H4" s="181">
         <f>IF(G10=" ","",$G$10-G4+1)</f>
         <v/>
       </c>
-      <c r="I4" s="181">
+      <c r="I4" s="180">
         <f>QUADRO!G4</f>
         <v/>
       </c>
-      <c r="J4" s="183">
+      <c r="J4" s="182">
         <f>IF(I10=" ","",$I$10-I4+1)</f>
         <v/>
       </c>
-      <c r="K4" s="181">
+      <c r="K4" s="180">
         <f>QUADRO!H4</f>
         <v/>
       </c>
-      <c r="L4" s="183">
+      <c r="L4" s="182">
         <f>IF(K10=" ","",$K$10-K4+1)</f>
         <v/>
       </c>
-      <c r="M4" s="181">
+      <c r="M4" s="180">
         <f>QUADRO!I4</f>
         <v/>
       </c>
-      <c r="N4" s="182">
+      <c r="N4" s="181">
         <f>IF(M10=" ","",$M$10-M4+1)</f>
         <v/>
       </c>
-      <c r="O4" s="181">
+      <c r="O4" s="180">
         <f>QUADRO!J4</f>
         <v/>
       </c>
-      <c r="P4" s="182">
+      <c r="P4" s="181">
         <f>TRUNC(IF(O4=" ","",H4*J4*L4*N4*O4),4)</f>
         <v/>
       </c>
@@ -7820,7 +7820,7 @@
         <f>TRUNC(IF(F4="","",F4*P4),2)</f>
         <v/>
       </c>
-      <c r="R4" s="128">
+      <c r="R4" s="127">
         <f>IF(AND(Q4&lt;=$Q$12+$Q$13,Q4&gt;=$Q$12-$Q$13),Q4,"*")</f>
         <v/>
       </c>
@@ -7842,51 +7842,51 @@
         <f>AMOSTRAS!E32</f>
         <v/>
       </c>
-      <c r="E5" s="180">
+      <c r="E5" s="179">
         <f>AMOSTRAS!E31</f>
         <v/>
       </c>
-      <c r="F5" s="127">
+      <c r="F5" s="126">
         <f>D5/E5</f>
         <v/>
       </c>
-      <c r="G5" s="181">
+      <c r="G5" s="180">
         <f>AMOSTRAS!G39</f>
         <v/>
       </c>
-      <c r="H5" s="182">
+      <c r="H5" s="181">
         <f>IF(G10=" ","",$G$10-G5+1)</f>
         <v/>
       </c>
-      <c r="I5" s="181">
+      <c r="I5" s="180">
         <f>QUADRO!G5</f>
         <v/>
       </c>
-      <c r="J5" s="183">
+      <c r="J5" s="182">
         <f>IF(I10=" ","",$I$10-I5+1)</f>
         <v/>
       </c>
-      <c r="K5" s="181">
+      <c r="K5" s="180">
         <f>QUADRO!H5</f>
         <v/>
       </c>
-      <c r="L5" s="183">
+      <c r="L5" s="182">
         <f>IF(K10=" ","",$K$10-K5+1)</f>
         <v/>
       </c>
-      <c r="M5" s="181">
+      <c r="M5" s="180">
         <f>QUADRO!I5</f>
         <v/>
       </c>
-      <c r="N5" s="182">
+      <c r="N5" s="181">
         <f>IF(M10=" ","",$M$10-M5+1)</f>
         <v/>
       </c>
-      <c r="O5" s="181">
+      <c r="O5" s="180">
         <f>QUADRO!J5</f>
         <v/>
       </c>
-      <c r="P5" s="182">
+      <c r="P5" s="181">
         <f>TRUNC(IF(O5=" ","",H5*J5*L5*N5*O5),4)</f>
         <v/>
       </c>
@@ -7894,7 +7894,7 @@
         <f>TRUNC(IF(F5="","",F5*P5),2)</f>
         <v/>
       </c>
-      <c r="R5" s="128">
+      <c r="R5" s="127">
         <f>IF(AND(Q5&lt;=$Q$12+$Q$13,Q5&gt;=$Q$12-$Q$13),Q5,"*")</f>
         <v/>
       </c>
@@ -7916,51 +7916,51 @@
         <f>AMOSTRAS!E45</f>
         <v/>
       </c>
-      <c r="E6" s="180">
+      <c r="E6" s="179">
         <f>AMOSTRAS!E44</f>
         <v/>
       </c>
-      <c r="F6" s="127">
+      <c r="F6" s="126">
         <f>D6/E6</f>
         <v/>
       </c>
-      <c r="G6" s="181">
+      <c r="G6" s="180">
         <f>AMOSTRAS!G52</f>
         <v/>
       </c>
-      <c r="H6" s="182">
+      <c r="H6" s="181">
         <f>IF(G10=" ","",$G$10-G6+1)</f>
         <v/>
       </c>
-      <c r="I6" s="181">
+      <c r="I6" s="180">
         <f>QUADRO!G6</f>
         <v/>
       </c>
-      <c r="J6" s="183">
+      <c r="J6" s="182">
         <f>IF(I10=" ","",$I$10-I6+1)</f>
         <v/>
       </c>
-      <c r="K6" s="181">
+      <c r="K6" s="180">
         <f>QUADRO!H6</f>
         <v/>
       </c>
-      <c r="L6" s="183">
+      <c r="L6" s="182">
         <f>IF(K10=" ","",$K$10-K6+1)</f>
         <v/>
       </c>
-      <c r="M6" s="181">
+      <c r="M6" s="180">
         <f>QUADRO!I6</f>
         <v/>
       </c>
-      <c r="N6" s="182">
+      <c r="N6" s="181">
         <f>IF(M10=" ","",$M$10-M6+1)</f>
         <v/>
       </c>
-      <c r="O6" s="181">
+      <c r="O6" s="180">
         <f>QUADRO!J6</f>
         <v/>
       </c>
-      <c r="P6" s="182">
+      <c r="P6" s="181">
         <f>TRUNC(IF(O6=" ","",H6*J6*L6*N6*O6),4)</f>
         <v/>
       </c>
@@ -7968,7 +7968,7 @@
         <f>TRUNC(IF(F6="","",F6*P6),2)</f>
         <v/>
       </c>
-      <c r="R6" s="128">
+      <c r="R6" s="127">
         <f>IF(AND(Q6&lt;=$Q$12+$Q$13,Q6&gt;=$Q$12-$Q$13),Q6,"*")</f>
         <v/>
       </c>
@@ -7990,51 +7990,51 @@
         <f>AMOSTRAS!E58</f>
         <v/>
       </c>
-      <c r="E7" s="180">
+      <c r="E7" s="179">
         <f>AMOSTRAS!E57</f>
         <v/>
       </c>
-      <c r="F7" s="127">
+      <c r="F7" s="126">
         <f>D7/E7</f>
         <v/>
       </c>
-      <c r="G7" s="181">
+      <c r="G7" s="180">
         <f>AMOSTRAS!G65</f>
         <v/>
       </c>
-      <c r="H7" s="182">
+      <c r="H7" s="181">
         <f>IF(G11=" ","",$G$10-G7+1)</f>
         <v/>
       </c>
-      <c r="I7" s="181">
+      <c r="I7" s="180">
         <f>QUADRO!G7</f>
         <v/>
       </c>
-      <c r="J7" s="183">
+      <c r="J7" s="182">
         <f>IF(I11=" ","",$I$10-I7+1)</f>
         <v/>
       </c>
-      <c r="K7" s="181">
+      <c r="K7" s="180">
         <f>QUADRO!H7</f>
         <v/>
       </c>
-      <c r="L7" s="183">
+      <c r="L7" s="182">
         <f>IF(K11=" ","",$K$10-K7+1)</f>
         <v/>
       </c>
-      <c r="M7" s="181">
+      <c r="M7" s="180">
         <f>QUADRO!I7</f>
         <v/>
       </c>
-      <c r="N7" s="182">
+      <c r="N7" s="181">
         <f>IF(M11=" ","",$M$10-M7+1)</f>
         <v/>
       </c>
-      <c r="O7" s="181">
+      <c r="O7" s="180">
         <f>QUADRO!J7</f>
         <v/>
       </c>
-      <c r="P7" s="182">
+      <c r="P7" s="181">
         <f>TRUNC(IF(O7=" ","",H7*J7*L7*N7*O7),4)</f>
         <v/>
       </c>
@@ -8042,7 +8042,7 @@
         <f>TRUNC(IF(F7="","",F7*P7),2)</f>
         <v/>
       </c>
-      <c r="R7" s="128">
+      <c r="R7" s="127">
         <f>IF(AND(Q7&lt;=$Q$12+$Q$13,Q7&gt;=$Q$12-$Q$13),Q7,"*")</f>
         <v/>
       </c>
@@ -8064,51 +8064,51 @@
         <f>AMOSTRAS!E71</f>
         <v/>
       </c>
-      <c r="E8" s="180">
+      <c r="E8" s="179">
         <f>AMOSTRAS!E70</f>
         <v/>
       </c>
-      <c r="F8" s="127">
+      <c r="F8" s="126">
         <f>D8/E8</f>
         <v/>
       </c>
-      <c r="G8" s="181">
+      <c r="G8" s="180">
         <f>AMOSTRAS!G78</f>
         <v/>
       </c>
-      <c r="H8" s="182">
+      <c r="H8" s="181">
         <f>IF(G12=" ","",$G$10-G8+1)</f>
         <v/>
       </c>
-      <c r="I8" s="181">
+      <c r="I8" s="180">
         <f>QUADRO!G8</f>
         <v/>
       </c>
-      <c r="J8" s="183">
+      <c r="J8" s="182">
         <f>IF(I12=" ","",$I$10-I8+1)</f>
         <v/>
       </c>
-      <c r="K8" s="181">
+      <c r="K8" s="180">
         <f>QUADRO!H8</f>
         <v/>
       </c>
-      <c r="L8" s="183">
+      <c r="L8" s="182">
         <f>IF(K12=" ","",$K$10-K8+1)</f>
         <v/>
       </c>
-      <c r="M8" s="181">
+      <c r="M8" s="180">
         <f>QUADRO!I8</f>
         <v/>
       </c>
-      <c r="N8" s="182">
+      <c r="N8" s="181">
         <f>IF(M12=" ","",$M$10-M8+1)</f>
         <v/>
       </c>
-      <c r="O8" s="181">
+      <c r="O8" s="180">
         <f>QUADRO!J8</f>
         <v/>
       </c>
-      <c r="P8" s="182">
+      <c r="P8" s="181">
         <f>TRUNC(IF(O8=" ","",H8*J8*L8*N8*O8),4)</f>
         <v/>
       </c>
@@ -8116,7 +8116,7 @@
         <f>TRUNC(IF(F8="","",F8*P8),2)</f>
         <v/>
       </c>
-      <c r="R8" s="128">
+      <c r="R8" s="127">
         <f>IF(AND(Q8&lt;=$Q$12+$Q$13,Q8&gt;=$Q$12-$Q$13),Q8,"*")</f>
         <v/>
       </c>
@@ -8138,51 +8138,51 @@
         <f>AMOSTRAS!E84</f>
         <v/>
       </c>
-      <c r="E9" s="180">
+      <c r="E9" s="179">
         <f>AMOSTRAS!E83</f>
         <v/>
       </c>
-      <c r="F9" s="127">
+      <c r="F9" s="126">
         <f>D9/E9</f>
         <v/>
       </c>
-      <c r="G9" s="181">
+      <c r="G9" s="180">
         <f>AMOSTRAS!G91</f>
         <v/>
       </c>
-      <c r="H9" s="182">
+      <c r="H9" s="181">
         <f>IF(G13=" ","",$G$10-G9+1)</f>
         <v/>
       </c>
-      <c r="I9" s="181">
+      <c r="I9" s="180">
         <f>QUADRO!G9</f>
         <v/>
       </c>
-      <c r="J9" s="183">
+      <c r="J9" s="182">
         <f>IF(I13=" ","",$I$10-I9+1)</f>
         <v/>
       </c>
-      <c r="K9" s="181">
+      <c r="K9" s="180">
         <f>QUADRO!H9</f>
         <v/>
       </c>
-      <c r="L9" s="183">
+      <c r="L9" s="182">
         <f>IF(K13=" ","",$K$10-K9+1)</f>
         <v/>
       </c>
-      <c r="M9" s="181">
+      <c r="M9" s="180">
         <f>QUADRO!I9</f>
         <v/>
       </c>
-      <c r="N9" s="182">
+      <c r="N9" s="181">
         <f>IF(M13=" ","",$M$10-M9+1)</f>
         <v/>
       </c>
-      <c r="O9" s="181">
+      <c r="O9" s="180">
         <f>QUADRO!J9</f>
         <v/>
       </c>
-      <c r="P9" s="182">
+      <c r="P9" s="181">
         <f>TRUNC(IF(O9=" ","",H9*J9*L9*N9*O9),4)</f>
         <v/>
       </c>
@@ -8190,7 +8190,7 @@
         <f>TRUNC(IF(F9="","",F9*P9),2)</f>
         <v/>
       </c>
-      <c r="R9" s="128">
+      <c r="R9" s="127">
         <f>IF(AND(Q9&lt;=$Q$12+$Q$13,Q9&gt;=$Q$12-$Q$13),Q9,"*")</f>
         <v/>
       </c>
@@ -8201,37 +8201,37 @@
           <t>Avaliando</t>
         </is>
       </c>
-      <c r="B10" s="163">
+      <c r="B10" s="162">
         <f>AMOSTRAS!E5</f>
         <v/>
       </c>
-      <c r="C10" s="163" t="inlineStr">
+      <c r="C10" s="162" t="inlineStr">
         <is>
           <t>AVALIANDA</t>
         </is>
       </c>
       <c r="D10" s="104" t="n"/>
-      <c r="E10" s="184" t="n"/>
+      <c r="E10" s="183" t="n"/>
       <c r="F10" s="100" t="n"/>
-      <c r="G10" s="181">
+      <c r="G10" s="180">
         <f>AMOSTRAS!G13</f>
         <v/>
       </c>
-      <c r="H10" s="185" t="n"/>
-      <c r="I10" s="181" t="n">
+      <c r="H10" s="184" t="n"/>
+      <c r="I10" s="180" t="n">
         <v>0.9</v>
       </c>
-      <c r="J10" s="186" t="n"/>
-      <c r="K10" s="181" t="n">
+      <c r="J10" s="185" t="n"/>
+      <c r="K10" s="180" t="n">
         <v>0.7</v>
       </c>
-      <c r="L10" s="186" t="n"/>
-      <c r="M10" s="181" t="n">
+      <c r="L10" s="185" t="n"/>
+      <c r="M10" s="180" t="n">
         <v>1.1</v>
       </c>
-      <c r="N10" s="187" t="n"/>
-      <c r="O10" s="184" t="n"/>
-      <c r="P10" s="184" t="n"/>
+      <c r="N10" s="186" t="n"/>
+      <c r="O10" s="183" t="n"/>
+      <c r="P10" s="183" t="n"/>
       <c r="Q10" s="101" t="n"/>
       <c r="R10" s="102" t="n"/>
     </row>
@@ -8409,7 +8409,7 @@
           <t>Média após Saneamento</t>
         </is>
       </c>
-      <c r="Q17" s="188">
+      <c r="Q17" s="187">
         <f>TRUNC(AVERAGE(R4:R9),2)</f>
         <v/>
       </c>
@@ -8489,7 +8489,7 @@
           <t>Fator para I.C.</t>
         </is>
       </c>
-      <c r="Q20" s="134">
+      <c r="Q20" s="133">
         <f>TRUNC(N18*(Q19/(SQRT(N17))),2)</f>
         <v/>
       </c>
@@ -8511,7 +8511,7 @@
       <c r="M21" s="104" t="n"/>
       <c r="N21" s="104" t="n"/>
       <c r="O21" s="104" t="n"/>
-      <c r="P21" s="109" t="inlineStr">
+      <c r="P21" s="108" t="inlineStr">
         <is>
           <t>I.C. Superior</t>
         </is>
@@ -8592,7 +8592,7 @@
           <t>Coeficiente de Variação %</t>
         </is>
       </c>
-      <c r="Q24" s="108">
+      <c r="Q24" s="190">
         <f>IF(Q17="","",(Q23/Q17)*100)</f>
         <v/>
       </c>
@@ -8638,20 +8638,20 @@
       <c r="I26" s="339" t="n"/>
       <c r="J26" s="339" t="n"/>
       <c r="K26" s="339" t="n"/>
-      <c r="L26" s="110" t="n"/>
-      <c r="M26" s="110" t="n"/>
-      <c r="N26" s="110" t="n"/>
-      <c r="O26" s="110" t="n"/>
-      <c r="P26" s="110" t="n"/>
-      <c r="Q26" s="110" t="n"/>
-      <c r="R26" s="111" t="n"/>
+      <c r="L26" s="109" t="n"/>
+      <c r="M26" s="109" t="n"/>
+      <c r="N26" s="109" t="n"/>
+      <c r="O26" s="109" t="n"/>
+      <c r="P26" s="109" t="n"/>
+      <c r="Q26" s="109" t="n"/>
+      <c r="R26" s="110" t="n"/>
     </row>
     <row r="28">
-      <c r="Q28" s="144" t="n"/>
-      <c r="R28" s="189" t="n"/>
+      <c r="Q28" s="143" t="n"/>
+      <c r="R28" s="188" t="n"/>
     </row>
     <row r="29">
-      <c r="P29" s="190">
+      <c r="P29" s="189">
         <f>Q17*4.84</f>
         <v/>
       </c>
@@ -9100,12 +9100,12 @@
     <mergeCell ref="F34:H34"/>
     <mergeCell ref="C15:H15"/>
     <mergeCell ref="F10:H10"/>
-    <mergeCell ref="C24:H24"/>
+    <mergeCell ref="C33:E33"/>
     <mergeCell ref="C14:E14"/>
     <mergeCell ref="J14:L14"/>
     <mergeCell ref="F19:H19"/>
     <mergeCell ref="F6:H6"/>
-    <mergeCell ref="C33:E33"/>
+    <mergeCell ref="C24:H24"/>
     <mergeCell ref="C5:H5"/>
     <mergeCell ref="C26:E26"/>
     <mergeCell ref="C4:H4"/>
@@ -9207,11 +9207,11 @@
       </c>
       <c r="G11" s="243" t="n"/>
       <c r="H11" s="244" t="n"/>
-      <c r="K11" s="133" t="n"/>
+      <c r="K11" s="132" t="n"/>
       <c r="M11" s="414" t="n"/>
     </row>
     <row r="12" ht="15" customHeight="1" s="236">
-      <c r="K12" s="133" t="n"/>
+      <c r="K12" s="132" t="n"/>
       <c r="M12" s="414" t="n"/>
     </row>
     <row r="13">
@@ -9220,7 +9220,7 @@
           <t>CÁLCULO DE VALOR DE LIQUIDAÇÃO FORÇADA</t>
         </is>
       </c>
-      <c r="K13" s="132" t="n"/>
+      <c r="K13" s="131" t="n"/>
       <c r="M13" s="415" t="n"/>
     </row>
     <row r="14">
@@ -9348,8 +9348,8 @@
     <col width="12.85546875" customWidth="1" style="364" min="33" max="33"/>
     <col width="3.7109375" customWidth="1" style="364" min="34" max="34"/>
     <col width="3" customWidth="1" style="364" min="35" max="36"/>
-    <col width="9.140625" customWidth="1" style="364" min="37" max="104"/>
-    <col width="9.140625" customWidth="1" style="364" min="105" max="16384"/>
+    <col width="9.140625" customWidth="1" style="364" min="37" max="110"/>
+    <col width="9.140625" customWidth="1" style="364" min="111" max="16384"/>
   </cols>
   <sheetData>
     <row r="2" ht="17.1" customFormat="1" customHeight="1" s="375">
